--- a/emprical study.xlsx
+++ b/emprical study.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1619,10 +1619,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H202"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:K202"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,8 +1638,14 @@
       <c r="F1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="J1">
+        <v>9800</v>
+      </c>
+      <c r="K1">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1658,8 +1664,14 @@
       <c r="H2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="J2">
+        <v>138</v>
+      </c>
+      <c r="K2">
+        <v>141724</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1675,8 +1687,14 @@
       <c r="F3">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="J3">
+        <v>9800</v>
+      </c>
+      <c r="K3">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1692,8 +1710,14 @@
       <c r="F4">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="J4">
+        <v>9800</v>
+      </c>
+      <c r="K4">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1703,8 +1727,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="J5">
+        <v>9800</v>
+      </c>
+      <c r="K5">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,8 +1744,14 @@
       <c r="C6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="J6">
+        <v>9800</v>
+      </c>
+      <c r="K6">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1725,8 +1761,14 @@
       <c r="C7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="J7">
+        <v>9800</v>
+      </c>
+      <c r="K7">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1736,8 +1778,14 @@
       <c r="C8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="J8">
+        <v>159</v>
+      </c>
+      <c r="K8">
+        <v>320962</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1747,8 +1795,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="J9">
+        <v>654</v>
+      </c>
+      <c r="K9">
+        <v>6932</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1762,8 +1816,14 @@
         <f>COUNTIF(B:B,2)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="J10">
+        <v>9800</v>
+      </c>
+      <c r="K10">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1773,8 +1833,14 @@
       <c r="C11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="J11">
+        <v>9800</v>
+      </c>
+      <c r="K11">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1784,8 +1850,14 @@
       <c r="C12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="J12">
+        <v>9800</v>
+      </c>
+      <c r="K12">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1795,8 +1867,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="J13">
+        <v>294</v>
+      </c>
+      <c r="K13">
+        <v>715765</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -1806,8 +1884,14 @@
       <c r="C14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="J14">
+        <v>9800</v>
+      </c>
+      <c r="K14">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1817,8 +1901,14 @@
       <c r="C15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="J15">
+        <v>9800</v>
+      </c>
+      <c r="K15">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -1828,8 +1918,14 @@
       <c r="C16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="J16">
+        <v>2000</v>
+      </c>
+      <c r="K16">
+        <v>80752</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -1839,8 +1935,14 @@
       <c r="C17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="J17">
+        <v>2600</v>
+      </c>
+      <c r="K17">
+        <v>168638</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -1850,8 +1952,14 @@
       <c r="C18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="J18">
+        <v>4400</v>
+      </c>
+      <c r="K18">
+        <v>9951</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -1861,8 +1969,14 @@
       <c r="C19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="J19">
+        <v>9800</v>
+      </c>
+      <c r="K19">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -1872,8 +1986,14 @@
       <c r="C20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="J20">
+        <v>9800</v>
+      </c>
+      <c r="K20">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1883,8 +2003,14 @@
       <c r="C21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="J21">
+        <v>9800</v>
+      </c>
+      <c r="K21">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -1894,8 +2020,14 @@
       <c r="C22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="J22">
+        <v>2700</v>
+      </c>
+      <c r="K22">
+        <v>382040</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -1905,8 +2037,14 @@
       <c r="C23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="J23">
+        <v>9800</v>
+      </c>
+      <c r="K23">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -1916,8 +2054,14 @@
       <c r="C24">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="J24">
+        <v>9800</v>
+      </c>
+      <c r="K24">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -1927,8 +2071,14 @@
       <c r="C25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="J25">
+        <v>9800</v>
+      </c>
+      <c r="K25">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -1938,8 +2088,14 @@
       <c r="C26">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="J26">
+        <v>1600</v>
+      </c>
+      <c r="K26">
+        <v>152797</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -1949,8 +2105,14 @@
       <c r="C27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="J27">
+        <v>9800</v>
+      </c>
+      <c r="K27">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -1960,8 +2122,14 @@
       <c r="C28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="J28">
+        <v>2600</v>
+      </c>
+      <c r="K28">
+        <v>168638</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -1971,8 +2139,14 @@
       <c r="C29">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="J29">
+        <v>9800</v>
+      </c>
+      <c r="K29">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -1982,8 +2156,14 @@
       <c r="C30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="J30">
+        <v>132</v>
+      </c>
+      <c r="K30">
+        <v>164048</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -1993,8 +2173,14 @@
       <c r="C31">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="J31">
+        <v>9800</v>
+      </c>
+      <c r="K31">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -2004,8 +2190,14 @@
       <c r="C32">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="J32">
+        <v>477</v>
+      </c>
+      <c r="K32">
+        <v>428009</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -2015,8 +2207,14 @@
       <c r="C33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="J33">
+        <v>2700</v>
+      </c>
+      <c r="K33">
+        <v>382040</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -2026,8 +2224,14 @@
       <c r="C34">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="J34">
+        <v>320</v>
+      </c>
+      <c r="K34">
+        <v>326855</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
         <v>43</v>
       </c>
@@ -2037,8 +2241,14 @@
       <c r="C35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="J35">
+        <v>9800</v>
+      </c>
+      <c r="K35">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
@@ -2048,8 +2258,14 @@
       <c r="C36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="J36">
+        <v>294</v>
+      </c>
+      <c r="K36">
+        <v>715765</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
@@ -2059,8 +2275,14 @@
       <c r="C37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="J37">
+        <v>1100</v>
+      </c>
+      <c r="K37">
+        <v>145271</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -2070,8 +2292,14 @@
       <c r="C38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="J38">
+        <v>9800</v>
+      </c>
+      <c r="K38">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -2081,8 +2309,14 @@
       <c r="C39">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="J39">
+        <v>2700</v>
+      </c>
+      <c r="K39">
+        <v>382040</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -2092,8 +2326,14 @@
       <c r="C40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="J40">
+        <v>9800</v>
+      </c>
+      <c r="K40">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
@@ -2103,8 +2343,14 @@
       <c r="C41">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="J41">
+        <v>9800</v>
+      </c>
+      <c r="K41">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
@@ -2114,8 +2360,14 @@
       <c r="C42">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="J42">
+        <v>9800</v>
+      </c>
+      <c r="K42">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
@@ -2125,8 +2377,14 @@
       <c r="C43">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="J43">
+        <v>437</v>
+      </c>
+      <c r="K43">
+        <v>181814</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
@@ -2136,8 +2394,14 @@
       <c r="C44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="J44">
+        <v>9800</v>
+      </c>
+      <c r="K44">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
@@ -2147,8 +2411,14 @@
       <c r="C45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="J45">
+        <v>9800</v>
+      </c>
+      <c r="K45">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
@@ -2158,8 +2428,14 @@
       <c r="C46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="J46">
+        <v>9800</v>
+      </c>
+      <c r="K46">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
@@ -2169,8 +2445,14 @@
       <c r="C47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="J47">
+        <v>416</v>
+      </c>
+      <c r="K47">
+        <v>108107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -2180,8 +2462,14 @@
       <c r="C48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="J48">
+        <v>9800</v>
+      </c>
+      <c r="K48">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -2191,8 +2479,14 @@
       <c r="C49">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="J49">
+        <v>7600</v>
+      </c>
+      <c r="K49">
+        <v>361663</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="2" t="s">
         <v>58</v>
       </c>
@@ -2202,8 +2496,14 @@
       <c r="C50">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="J50">
+        <v>9800</v>
+      </c>
+      <c r="K50">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="2" t="s">
         <v>59</v>
       </c>
@@ -2213,8 +2513,14 @@
       <c r="C51">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="J51">
+        <v>491</v>
+      </c>
+      <c r="K51">
+        <v>42193</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
         <v>60</v>
       </c>
@@ -2224,8 +2530,14 @@
       <c r="C52">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="J52">
+        <v>2700</v>
+      </c>
+      <c r="K52">
+        <v>382040</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,8 +2547,14 @@
       <c r="C53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="J53">
+        <v>9800</v>
+      </c>
+      <c r="K53">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="2" t="s">
         <v>62</v>
       </c>
@@ -2249,8 +2567,14 @@
       <c r="E54" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="J54">
+        <v>7600</v>
+      </c>
+      <c r="K54">
+        <v>146939</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
         <v>64</v>
       </c>
@@ -2260,8 +2584,14 @@
       <c r="C55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="J55">
+        <v>7600</v>
+      </c>
+      <c r="K55">
+        <v>146939</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
         <v>65</v>
       </c>
@@ -2271,8 +2601,14 @@
       <c r="C56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="J56">
+        <v>5800</v>
+      </c>
+      <c r="K56">
+        <v>184252</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
         <v>66</v>
       </c>
@@ -2282,8 +2618,14 @@
       <c r="C57">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="J57">
+        <v>5800</v>
+      </c>
+      <c r="K57">
+        <v>184252</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
         <v>67</v>
       </c>
@@ -2293,8 +2635,14 @@
       <c r="C58">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="J58">
+        <v>3100</v>
+      </c>
+      <c r="K58">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="1" t="s">
         <v>68</v>
       </c>
@@ -2304,8 +2652,14 @@
       <c r="C59">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="J59">
+        <v>3100</v>
+      </c>
+      <c r="K59">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="1" t="s">
         <v>69</v>
       </c>
@@ -2315,8 +2669,14 @@
       <c r="C60">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="J60">
+        <v>7600</v>
+      </c>
+      <c r="K60">
+        <v>146939</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
         <v>70</v>
       </c>
@@ -2326,8 +2686,14 @@
       <c r="C61">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="J61">
+        <v>3100</v>
+      </c>
+      <c r="K61">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="1" t="s">
         <v>71</v>
       </c>
@@ -2337,8 +2703,14 @@
       <c r="C62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="J62">
+        <v>155</v>
+      </c>
+      <c r="K62">
+        <v>63107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" s="2" t="s">
         <v>72</v>
       </c>
@@ -2351,8 +2723,14 @@
       <c r="E63" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="J63">
+        <v>3100</v>
+      </c>
+      <c r="K63">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
         <v>73</v>
       </c>
@@ -2362,8 +2740,14 @@
       <c r="C64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="J64">
+        <v>5800</v>
+      </c>
+      <c r="K64">
+        <v>184252</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" s="2" t="s">
         <v>74</v>
       </c>
@@ -2373,8 +2757,14 @@
       <c r="C65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="J65">
+        <v>3100</v>
+      </c>
+      <c r="K65">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
         <v>75</v>
       </c>
@@ -2384,8 +2774,14 @@
       <c r="C66">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="J66">
+        <v>3100</v>
+      </c>
+      <c r="K66">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" s="1" t="s">
         <v>76</v>
       </c>
@@ -2395,8 +2791,14 @@
       <c r="C67">
         <v>3</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="J67">
+        <v>12300</v>
+      </c>
+      <c r="K67">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
         <v>77</v>
       </c>
@@ -2406,8 +2808,14 @@
       <c r="C68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="J68">
+        <v>9800</v>
+      </c>
+      <c r="K68">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="1" t="s">
         <v>79</v>
       </c>
@@ -2417,8 +2825,14 @@
       <c r="C69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="J69">
+        <v>717</v>
+      </c>
+      <c r="K69">
+        <v>10514</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="1" t="s">
         <v>80</v>
       </c>
@@ -2428,8 +2842,14 @@
       <c r="C70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="J70">
+        <v>3100</v>
+      </c>
+      <c r="K70">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="1" t="s">
         <v>81</v>
       </c>
@@ -2439,8 +2859,14 @@
       <c r="C71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="J71">
+        <v>10200</v>
+      </c>
+      <c r="K71">
+        <v>88762</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="1" t="s">
         <v>82</v>
       </c>
@@ -2450,8 +2876,14 @@
       <c r="C72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="J72">
+        <v>3100</v>
+      </c>
+      <c r="K72">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="1" t="s">
         <v>83</v>
       </c>
@@ -2461,8 +2893,14 @@
       <c r="C73">
         <v>3</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="J73">
+        <v>3100</v>
+      </c>
+      <c r="K73">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="1" t="s">
         <v>84</v>
       </c>
@@ -2472,8 +2910,14 @@
       <c r="C74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="J74">
+        <v>3100</v>
+      </c>
+      <c r="K74">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
         <v>85</v>
       </c>
@@ -2483,8 +2927,14 @@
       <c r="C75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="J75">
+        <v>9800</v>
+      </c>
+      <c r="K75">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
         <v>86</v>
       </c>
@@ -2494,8 +2944,14 @@
       <c r="C76">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="J76">
+        <v>6233</v>
+      </c>
+      <c r="K76">
+        <v>371029</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
         <v>87</v>
       </c>
@@ -2505,8 +2961,14 @@
       <c r="C77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="J77">
+        <v>2700</v>
+      </c>
+      <c r="K77">
+        <v>306479</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
         <v>88</v>
       </c>
@@ -2516,8 +2978,14 @@
       <c r="C78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="J78">
+        <v>1800</v>
+      </c>
+      <c r="K78">
+        <v>900774</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
         <v>89</v>
       </c>
@@ -2527,8 +2995,14 @@
       <c r="C79">
         <v>3</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="J79">
+        <v>6233</v>
+      </c>
+      <c r="K79">
+        <v>371029</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
         <v>90</v>
       </c>
@@ -2538,8 +3012,14 @@
       <c r="C80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="J80">
+        <v>1000</v>
+      </c>
+      <c r="K80">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
         <v>91</v>
       </c>
@@ -2549,8 +3029,14 @@
       <c r="C81">
         <v>2</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="J81">
+        <v>7600</v>
+      </c>
+      <c r="K81">
+        <v>146939</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
         <v>92</v>
       </c>
@@ -2560,8 +3046,14 @@
       <c r="C82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="J82">
+        <v>270</v>
+      </c>
+      <c r="K82">
+        <v>434997</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
         <v>93</v>
       </c>
@@ -2571,8 +3063,14 @@
       <c r="C83">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="J83">
+        <v>3100</v>
+      </c>
+      <c r="K83">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" s="1" t="s">
         <v>94</v>
       </c>
@@ -2582,8 +3080,14 @@
       <c r="C84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="J84">
+        <v>9800</v>
+      </c>
+      <c r="K84">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85" s="1" t="s">
         <v>95</v>
       </c>
@@ -2593,8 +3097,14 @@
       <c r="C85">
         <v>2</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="J85">
+        <v>632</v>
+      </c>
+      <c r="K85">
+        <v>126889</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" s="1" t="s">
         <v>96</v>
       </c>
@@ -2604,8 +3114,14 @@
       <c r="C86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="J86">
+        <v>2700</v>
+      </c>
+      <c r="K86">
+        <v>306479</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" s="1" t="s">
         <v>97</v>
       </c>
@@ -2615,8 +3131,14 @@
       <c r="C87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="J87">
+        <v>368</v>
+      </c>
+      <c r="K87">
+        <v>11953</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
         <v>98</v>
       </c>
@@ -2626,8 +3148,14 @@
       <c r="C88">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="J88">
+        <v>3600</v>
+      </c>
+      <c r="K88">
+        <v>33430</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
         <v>99</v>
       </c>
@@ -2637,8 +3165,14 @@
       <c r="C89">
         <v>2</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="J89">
+        <v>1800</v>
+      </c>
+      <c r="K89">
+        <v>900774</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
         <v>100</v>
       </c>
@@ -2648,8 +3182,14 @@
       <c r="C90">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="J90">
+        <v>363</v>
+      </c>
+      <c r="K90">
+        <v>92101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
         <v>101</v>
       </c>
@@ -2659,8 +3199,14 @@
       <c r="C91">
         <v>2</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="J91">
+        <v>1800</v>
+      </c>
+      <c r="K91">
+        <v>900774</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
         <v>102</v>
       </c>
@@ -2670,8 +3216,14 @@
       <c r="C92">
         <v>3</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="J92">
+        <v>12300</v>
+      </c>
+      <c r="K92">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93" s="1" t="s">
         <v>103</v>
       </c>
@@ -2681,8 +3233,14 @@
       <c r="C93">
         <v>3</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="J93">
+        <v>12300</v>
+      </c>
+      <c r="K93">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
         <v>104</v>
       </c>
@@ -2692,8 +3250,14 @@
       <c r="C94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="J94">
+        <v>351</v>
+      </c>
+      <c r="K94">
+        <v>417757</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
         <v>105</v>
       </c>
@@ -2703,8 +3267,14 @@
       <c r="C95">
         <v>3</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="J95">
+        <v>12300</v>
+      </c>
+      <c r="K95">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
         <v>106</v>
       </c>
@@ -2714,8 +3284,14 @@
       <c r="C96">
         <v>2</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="J96">
+        <v>3000</v>
+      </c>
+      <c r="K96">
+        <v>143120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
         <v>107</v>
       </c>
@@ -2725,8 +3301,14 @@
       <c r="C97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="J97">
+        <v>351</v>
+      </c>
+      <c r="K97">
+        <v>417757</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
         <v>108</v>
       </c>
@@ -2736,8 +3318,14 @@
       <c r="C98">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="J98">
+        <v>988</v>
+      </c>
+      <c r="K98">
+        <v>9347</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
         <v>109</v>
       </c>
@@ -2747,8 +3335,14 @@
       <c r="C99">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="J99">
+        <v>212</v>
+      </c>
+      <c r="K99">
+        <v>89542</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
         <v>110</v>
       </c>
@@ -2758,8 +3352,14 @@
       <c r="C100">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
+      <c r="J100">
+        <v>10200</v>
+      </c>
+      <c r="K100">
+        <v>88762</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
         <v>111</v>
       </c>
@@ -2769,8 +3369,14 @@
       <c r="C101">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="J101">
+        <v>3100</v>
+      </c>
+      <c r="K101">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
         <v>112</v>
       </c>
@@ -2780,8 +3386,14 @@
       <c r="C102">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
+      <c r="J102">
+        <v>628</v>
+      </c>
+      <c r="K102">
+        <v>51513</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103" s="2" t="s">
         <v>113</v>
       </c>
@@ -2791,8 +3403,14 @@
       <c r="C103">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="J103">
+        <v>3100</v>
+      </c>
+      <c r="K103">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
         <v>114</v>
       </c>
@@ -2802,8 +3420,14 @@
       <c r="C104">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3">
+      <c r="J104">
+        <v>12300</v>
+      </c>
+      <c r="K104">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
         <v>115</v>
       </c>
@@ -2813,8 +3437,14 @@
       <c r="C105">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3">
+      <c r="J105">
+        <v>294</v>
+      </c>
+      <c r="K105">
+        <v>715765</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
         <v>116</v>
       </c>
@@ -2824,8 +3454,14 @@
       <c r="C106">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="J106">
+        <v>1300</v>
+      </c>
+      <c r="K106">
+        <v>212043</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
         <v>117</v>
       </c>
@@ -2835,8 +3471,14 @@
       <c r="C107">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
+      <c r="J107">
+        <v>3100</v>
+      </c>
+      <c r="K107">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
       <c r="A108" s="1" t="s">
         <v>118</v>
       </c>
@@ -2846,8 +3488,14 @@
       <c r="C108">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:3">
+      <c r="J108">
+        <v>181</v>
+      </c>
+      <c r="K108">
+        <v>203060</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
       <c r="A109" s="1" t="s">
         <v>119</v>
       </c>
@@ -2857,8 +3505,14 @@
       <c r="C109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
+      <c r="J109">
+        <v>2900</v>
+      </c>
+      <c r="K109">
+        <v>110253</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110" s="1" t="s">
         <v>120</v>
       </c>
@@ -2868,8 +3522,14 @@
       <c r="C110">
         <v>3</v>
       </c>
-    </row>
-    <row r="111" spans="1:3">
+      <c r="J110">
+        <v>3100</v>
+      </c>
+      <c r="K110">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
       <c r="A111" s="1" t="s">
         <v>121</v>
       </c>
@@ -2879,8 +3539,14 @@
       <c r="C111">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3">
+      <c r="J111">
+        <v>208</v>
+      </c>
+      <c r="K111">
+        <v>47602</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
       <c r="A112" s="1" t="s">
         <v>122</v>
       </c>
@@ -2890,8 +3556,14 @@
       <c r="C112">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="J112">
+        <v>9800</v>
+      </c>
+      <c r="K112">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
       <c r="A113" s="1" t="s">
         <v>123</v>
       </c>
@@ -2901,8 +3573,14 @@
       <c r="C113">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
+      <c r="J113">
+        <v>2900</v>
+      </c>
+      <c r="K113">
+        <v>110253</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
       <c r="A114" s="1" t="s">
         <v>124</v>
       </c>
@@ -2912,8 +3590,14 @@
       <c r="C114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
+      <c r="J114">
+        <v>12300</v>
+      </c>
+      <c r="K114">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115" s="1" t="s">
         <v>125</v>
       </c>
@@ -2923,8 +3607,14 @@
       <c r="C115">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
+      <c r="J115">
+        <v>110</v>
+      </c>
+      <c r="K115">
+        <v>12918</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116" s="1" t="s">
         <v>126</v>
       </c>
@@ -2934,8 +3624,14 @@
       <c r="C116">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
+      <c r="J116">
+        <v>2900</v>
+      </c>
+      <c r="K116">
+        <v>110253</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
       <c r="A117" s="1" t="s">
         <v>127</v>
       </c>
@@ -2945,8 +3641,14 @@
       <c r="C117">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
+      <c r="J117">
+        <v>2700</v>
+      </c>
+      <c r="K117">
+        <v>382040</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
       <c r="A118" s="1" t="s">
         <v>128</v>
       </c>
@@ -2956,8 +3658,14 @@
       <c r="C118">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
+      <c r="J118">
+        <v>836</v>
+      </c>
+      <c r="K118">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
       <c r="A119" s="1" t="s">
         <v>129</v>
       </c>
@@ -2967,8 +3675,14 @@
       <c r="C119">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
+      <c r="J119">
+        <v>2700</v>
+      </c>
+      <c r="K119">
+        <v>382040</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120" s="1" t="s">
         <v>130</v>
       </c>
@@ -2978,8 +3692,14 @@
       <c r="C120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
+      <c r="J120">
+        <v>9800</v>
+      </c>
+      <c r="K120">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121" s="1" t="s">
         <v>131</v>
       </c>
@@ -2989,8 +3709,14 @@
       <c r="C121">
         <v>2</v>
       </c>
-    </row>
-    <row r="122" spans="1:3">
+      <c r="J121">
+        <v>3100</v>
+      </c>
+      <c r="K121">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
       <c r="A122" s="1" t="s">
         <v>132</v>
       </c>
@@ -3000,8 +3726,14 @@
       <c r="C122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3">
+      <c r="J122">
+        <v>351</v>
+      </c>
+      <c r="K122">
+        <v>417757</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
       <c r="A123" s="1" t="s">
         <v>133</v>
       </c>
@@ -3011,8 +3743,14 @@
       <c r="C123">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
+      <c r="J123">
+        <v>351</v>
+      </c>
+      <c r="K123">
+        <v>417757</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
       <c r="A124" s="1" t="s">
         <v>134</v>
       </c>
@@ -3022,8 +3760,14 @@
       <c r="C124">
         <v>3</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
+      <c r="J124">
+        <v>3500</v>
+      </c>
+      <c r="K124">
+        <v>446442</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
       <c r="A125" s="1" t="s">
         <v>135</v>
       </c>
@@ -3033,8 +3777,14 @@
       <c r="C125">
         <v>3</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
+      <c r="J125">
+        <v>294</v>
+      </c>
+      <c r="K125">
+        <v>715765</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126" s="1" t="s">
         <v>136</v>
       </c>
@@ -3044,8 +3794,14 @@
       <c r="C126">
         <v>2</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
+      <c r="J126">
+        <v>274</v>
+      </c>
+      <c r="K126">
+        <v>105449</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
       <c r="A127" s="1" t="s">
         <v>137</v>
       </c>
@@ -3055,8 +3811,14 @@
       <c r="C127">
         <v>3</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
+      <c r="J127">
+        <v>2900</v>
+      </c>
+      <c r="K127">
+        <v>110253</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
       <c r="A128" s="1" t="s">
         <v>138</v>
       </c>
@@ -3066,8 +3828,14 @@
       <c r="C128">
         <v>3</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
+      <c r="J128">
+        <v>9800</v>
+      </c>
+      <c r="K128">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
       <c r="A129" s="1" t="s">
         <v>139</v>
       </c>
@@ -3077,8 +3845,14 @@
       <c r="C129">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
+      <c r="J129">
+        <v>836</v>
+      </c>
+      <c r="K129">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
       <c r="A130" s="1" t="s">
         <v>140</v>
       </c>
@@ -3088,8 +3862,14 @@
       <c r="C130">
         <v>3</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
+      <c r="J130">
+        <v>3500</v>
+      </c>
+      <c r="K130">
+        <v>446442</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
       <c r="A131" s="1" t="s">
         <v>141</v>
       </c>
@@ -3099,8 +3879,14 @@
       <c r="C131">
         <v>3</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
+      <c r="J131">
+        <v>3500</v>
+      </c>
+      <c r="K131">
+        <v>446442</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
       <c r="A132" s="1" t="s">
         <v>142</v>
       </c>
@@ -3110,8 +3896,14 @@
       <c r="C132">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
+      <c r="J132">
+        <v>836</v>
+      </c>
+      <c r="K132">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
       <c r="A133" s="1" t="s">
         <v>143</v>
       </c>
@@ -3121,8 +3913,14 @@
       <c r="C133">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="J133">
+        <v>836</v>
+      </c>
+      <c r="K133">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
       <c r="A134" s="1" t="s">
         <v>144</v>
       </c>
@@ -3132,8 +3930,14 @@
       <c r="C134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
+      <c r="J134">
+        <v>836</v>
+      </c>
+      <c r="K134">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
       <c r="A135" s="1" t="s">
         <v>145</v>
       </c>
@@ -3143,8 +3947,14 @@
       <c r="C135">
         <v>3</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
+      <c r="J135">
+        <v>836</v>
+      </c>
+      <c r="K135">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
       <c r="A136" s="1" t="s">
         <v>146</v>
       </c>
@@ -3154,8 +3964,14 @@
       <c r="C136">
         <v>2</v>
       </c>
-    </row>
-    <row r="137" spans="1:3">
+      <c r="J136">
+        <v>1600</v>
+      </c>
+      <c r="K136">
+        <v>342821</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
       <c r="A137" s="1" t="s">
         <v>147</v>
       </c>
@@ -3165,8 +3981,14 @@
       <c r="C137">
         <v>3</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
+      <c r="J137">
+        <v>836</v>
+      </c>
+      <c r="K137">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
       <c r="A138" s="1" t="s">
         <v>148</v>
       </c>
@@ -3176,8 +3998,14 @@
       <c r="C138">
         <v>3</v>
       </c>
-    </row>
-    <row r="139" spans="1:3">
+      <c r="J138">
+        <v>836</v>
+      </c>
+      <c r="K138">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
       <c r="A139" s="1" t="s">
         <v>149</v>
       </c>
@@ -3187,8 +4015,14 @@
       <c r="C139">
         <v>3</v>
       </c>
-    </row>
-    <row r="140" spans="1:3">
+      <c r="J139">
+        <v>836</v>
+      </c>
+      <c r="K139">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
       <c r="A140" s="1" t="s">
         <v>150</v>
       </c>
@@ -3198,8 +4032,14 @@
       <c r="C140">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
+      <c r="J140">
+        <v>160</v>
+      </c>
+      <c r="K140">
+        <v>15801</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
       <c r="A141" s="1" t="s">
         <v>151</v>
       </c>
@@ -3209,8 +4049,14 @@
       <c r="C141">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3">
+      <c r="J141">
+        <v>836</v>
+      </c>
+      <c r="K141">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
       <c r="A142" s="1" t="s">
         <v>152</v>
       </c>
@@ -3220,8 +4066,14 @@
       <c r="C142">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:3">
+      <c r="J142">
+        <v>593</v>
+      </c>
+      <c r="K142">
+        <v>36366</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
       <c r="A143" s="1" t="s">
         <v>153</v>
       </c>
@@ -3231,8 +4083,14 @@
       <c r="C143">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
+      <c r="J143">
+        <v>405</v>
+      </c>
+      <c r="K143">
+        <v>19396</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
       <c r="A144" s="2" t="s">
         <v>154</v>
       </c>
@@ -3242,8 +4100,14 @@
       <c r="C144">
         <v>3</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
+      <c r="J144">
+        <v>836</v>
+      </c>
+      <c r="K144">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
       <c r="A145" s="2" t="s">
         <v>155</v>
       </c>
@@ -3253,8 +4117,14 @@
       <c r="C145">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
+      <c r="J145">
+        <v>2000</v>
+      </c>
+      <c r="K145">
+        <v>154610</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
       <c r="A146" s="2" t="s">
         <v>156</v>
       </c>
@@ -3264,8 +4134,14 @@
       <c r="C146">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
+      <c r="J146">
+        <v>2000</v>
+      </c>
+      <c r="K146">
+        <v>154610</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
       <c r="A147" s="2" t="s">
         <v>157</v>
       </c>
@@ -3275,8 +4151,14 @@
       <c r="C147">
         <v>3</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
+      <c r="J147">
+        <v>1000</v>
+      </c>
+      <c r="K147">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
@@ -3286,8 +4168,14 @@
       <c r="C148">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
+      <c r="J148">
+        <v>516</v>
+      </c>
+      <c r="K148">
+        <v>119284</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
       <c r="A149" s="2" t="s">
         <v>159</v>
       </c>
@@ -3297,8 +4185,14 @@
       <c r="C149">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:3">
+      <c r="J149">
+        <v>516</v>
+      </c>
+      <c r="K149">
+        <v>119284</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
       <c r="A150" s="1" t="s">
         <v>160</v>
       </c>
@@ -3308,8 +4202,14 @@
       <c r="C150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
+      <c r="J150">
+        <v>1000</v>
+      </c>
+      <c r="K150">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
       <c r="A151" s="1" t="s">
         <v>161</v>
       </c>
@@ -3319,8 +4219,14 @@
       <c r="C151">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:3">
+      <c r="J151">
+        <v>294</v>
+      </c>
+      <c r="K151">
+        <v>715765</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
       <c r="A152" s="1" t="s">
         <v>162</v>
       </c>
@@ -3330,8 +4236,14 @@
       <c r="C152">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
+      <c r="J152">
+        <v>6233</v>
+      </c>
+      <c r="K152">
+        <v>371029</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
       <c r="A153" s="1" t="s">
         <v>163</v>
       </c>
@@ -3341,8 +4253,14 @@
       <c r="C153">
         <v>2</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
+      <c r="J153">
+        <v>110</v>
+      </c>
+      <c r="K153">
+        <v>16185</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
       <c r="A154" s="2" t="s">
         <v>164</v>
       </c>
@@ -3352,8 +4270,14 @@
       <c r="C154">
         <v>2</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
+      <c r="J154">
+        <v>851</v>
+      </c>
+      <c r="K154">
+        <v>54894</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
       <c r="A155" s="2" t="s">
         <v>165</v>
       </c>
@@ -3363,8 +4287,14 @@
       <c r="C155">
         <v>3</v>
       </c>
-    </row>
-    <row r="156" spans="1:3">
+      <c r="J155">
+        <v>9800</v>
+      </c>
+      <c r="K155">
+        <v>273644</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
       <c r="A156" s="2" t="s">
         <v>166</v>
       </c>
@@ -3374,8 +4304,14 @@
       <c r="C156">
         <v>2</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
+      <c r="J156">
+        <v>12300</v>
+      </c>
+      <c r="K156">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
       <c r="A157" s="2" t="s">
         <v>76</v>
       </c>
@@ -3385,8 +4321,14 @@
       <c r="C157">
         <v>3</v>
       </c>
-    </row>
-    <row r="158" spans="1:3">
+      <c r="J157">
+        <v>12300</v>
+      </c>
+      <c r="K157">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
       <c r="A158" s="1" t="s">
         <v>168</v>
       </c>
@@ -3396,8 +4338,14 @@
       <c r="C158">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3">
+      <c r="J158">
+        <v>27300</v>
+      </c>
+      <c r="K158">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
       <c r="A159" s="1" t="s">
         <v>169</v>
       </c>
@@ -3407,8 +4355,14 @@
       <c r="C159">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3">
+      <c r="J159">
+        <v>27300</v>
+      </c>
+      <c r="K159">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
       <c r="A160" s="1" t="s">
         <v>170</v>
       </c>
@@ -3418,8 +4372,14 @@
       <c r="C160">
         <v>3</v>
       </c>
-    </row>
-    <row r="161" spans="1:3">
+      <c r="J160">
+        <v>1000</v>
+      </c>
+      <c r="K160">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
       <c r="A161" s="1" t="s">
         <v>171</v>
       </c>
@@ -3429,8 +4389,14 @@
       <c r="C161">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="1:3">
+      <c r="J161">
+        <v>3000</v>
+      </c>
+      <c r="K161">
+        <v>1890734</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
       <c r="A162" s="1" t="s">
         <v>172</v>
       </c>
@@ -3440,8 +4406,14 @@
       <c r="C162">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:3">
+      <c r="J162">
+        <v>1100</v>
+      </c>
+      <c r="K162">
+        <v>145271</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
       <c r="A163" s="1" t="s">
         <v>173</v>
       </c>
@@ -3451,8 +4423,14 @@
       <c r="C163">
         <v>2</v>
       </c>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="J163">
+        <v>1100</v>
+      </c>
+      <c r="K163">
+        <v>145271</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
       <c r="A164" s="1" t="s">
         <v>174</v>
       </c>
@@ -3472,8 +4450,14 @@
       <c r="G164" s="4">
         <v>0.7129</v>
       </c>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="J164">
+        <v>1100</v>
+      </c>
+      <c r="K164">
+        <v>145271</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
       <c r="A165" s="1" t="s">
         <v>176</v>
       </c>
@@ -3486,8 +4470,14 @@
       <c r="F165" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="J165">
+        <v>2300</v>
+      </c>
+      <c r="K165">
+        <v>90748</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
       <c r="A166" s="1" t="s">
         <v>178</v>
       </c>
@@ -3500,8 +4490,14 @@
       <c r="F166" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="167" spans="1:3">
+      <c r="J166">
+        <v>1100</v>
+      </c>
+      <c r="K166">
+        <v>40036</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
       <c r="A167" s="1" t="s">
         <v>180</v>
       </c>
@@ -3511,8 +4507,14 @@
       <c r="C167">
         <v>2</v>
       </c>
-    </row>
-    <row r="168" spans="1:3">
+      <c r="J167">
+        <v>12300</v>
+      </c>
+      <c r="K167">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
       <c r="A168" s="1" t="s">
         <v>181</v>
       </c>
@@ -3522,8 +4524,14 @@
       <c r="C168">
         <v>2</v>
       </c>
-    </row>
-    <row r="169" spans="1:3">
+      <c r="J168">
+        <v>12300</v>
+      </c>
+      <c r="K168">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
       <c r="A169" s="1" t="s">
         <v>182</v>
       </c>
@@ -3533,8 +4541,14 @@
       <c r="C169">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3">
+      <c r="J169">
+        <v>1000</v>
+      </c>
+      <c r="K169">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
       <c r="A170" s="1" t="s">
         <v>183</v>
       </c>
@@ -3544,8 +4558,14 @@
       <c r="C170">
         <v>3</v>
       </c>
-    </row>
-    <row r="171" spans="1:3">
+      <c r="J170">
+        <v>1000</v>
+      </c>
+      <c r="K170">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
       <c r="A171" s="1" t="s">
         <v>184</v>
       </c>
@@ -3555,8 +4575,14 @@
       <c r="C171">
         <v>3</v>
       </c>
-    </row>
-    <row r="172" spans="1:3">
+      <c r="J171">
+        <v>1000</v>
+      </c>
+      <c r="K171">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
       <c r="A172" s="1" t="s">
         <v>185</v>
       </c>
@@ -3566,8 +4592,14 @@
       <c r="C172">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3">
+      <c r="J172">
+        <v>1000</v>
+      </c>
+      <c r="K172">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
       <c r="A173" s="1" t="s">
         <v>186</v>
       </c>
@@ -3577,8 +4609,14 @@
       <c r="C173">
         <v>2</v>
       </c>
-    </row>
-    <row r="174" spans="1:3">
+      <c r="J173">
+        <v>1000</v>
+      </c>
+      <c r="K173">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
       <c r="A174" s="1" t="s">
         <v>187</v>
       </c>
@@ -3588,8 +4626,14 @@
       <c r="C174">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:3">
+      <c r="J174">
+        <v>1000</v>
+      </c>
+      <c r="K174">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
       <c r="A175" s="1" t="s">
         <v>188</v>
       </c>
@@ -3599,8 +4643,14 @@
       <c r="C175">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:3">
+      <c r="J175">
+        <v>1000</v>
+      </c>
+      <c r="K175">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
       <c r="A176" s="1" t="s">
         <v>189</v>
       </c>
@@ -3610,8 +4660,14 @@
       <c r="C176">
         <v>3</v>
       </c>
-    </row>
-    <row r="177" spans="1:3">
+      <c r="J176">
+        <v>1000</v>
+      </c>
+      <c r="K176">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
       <c r="A177" s="1" t="s">
         <v>190</v>
       </c>
@@ -3621,8 +4677,14 @@
       <c r="C177">
         <v>3</v>
       </c>
-    </row>
-    <row r="178" spans="1:3">
+      <c r="J177">
+        <v>1000</v>
+      </c>
+      <c r="K177">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
       <c r="A178" s="1" t="s">
         <v>191</v>
       </c>
@@ -3632,8 +4694,14 @@
       <c r="C178">
         <v>1</v>
       </c>
-    </row>
-    <row r="179" spans="1:3">
+      <c r="J178">
+        <v>1000</v>
+      </c>
+      <c r="K178">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
       <c r="A179" s="1" t="s">
         <v>192</v>
       </c>
@@ -3643,8 +4711,14 @@
       <c r="C179">
         <v>3</v>
       </c>
-    </row>
-    <row r="180" spans="1:3">
+      <c r="J179">
+        <v>1000</v>
+      </c>
+      <c r="K179">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
       <c r="A180" s="1" t="s">
         <v>193</v>
       </c>
@@ -3654,8 +4728,14 @@
       <c r="C180">
         <v>3</v>
       </c>
-    </row>
-    <row r="181" spans="1:3">
+      <c r="J180">
+        <v>1000</v>
+      </c>
+      <c r="K180">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
       <c r="A181" s="1" t="s">
         <v>194</v>
       </c>
@@ -3665,8 +4745,14 @@
       <c r="C181">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:3">
+      <c r="J181">
+        <v>1000</v>
+      </c>
+      <c r="K181">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
       <c r="A182" s="1" t="s">
         <v>195</v>
       </c>
@@ -3676,8 +4762,14 @@
       <c r="C182">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:3">
+      <c r="J182">
+        <v>1000</v>
+      </c>
+      <c r="K182">
+        <v>79258</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
       <c r="A183" s="1" t="s">
         <v>196</v>
       </c>
@@ -3687,8 +4779,14 @@
       <c r="C183">
         <v>2</v>
       </c>
-    </row>
-    <row r="184" spans="1:3">
+      <c r="J183">
+        <v>50400</v>
+      </c>
+      <c r="K183">
+        <v>1074744</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
       <c r="A184" s="1" t="s">
         <v>197</v>
       </c>
@@ -3698,8 +4796,14 @@
       <c r="C184">
         <v>2</v>
       </c>
-    </row>
-    <row r="185" spans="1:3">
+      <c r="J184">
+        <v>181</v>
+      </c>
+      <c r="K184">
+        <v>39197</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
       <c r="A185" s="1" t="s">
         <v>198</v>
       </c>
@@ -3709,8 +4813,14 @@
       <c r="C185">
         <v>3</v>
       </c>
-    </row>
-    <row r="186" spans="1:3">
+      <c r="J185">
+        <v>27300</v>
+      </c>
+      <c r="K185">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
       <c r="A186" s="1" t="s">
         <v>199</v>
       </c>
@@ -3720,8 +4830,14 @@
       <c r="C186">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:3">
+      <c r="J186">
+        <v>27300</v>
+      </c>
+      <c r="K186">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
       <c r="A187" s="1" t="s">
         <v>200</v>
       </c>
@@ -3731,8 +4847,14 @@
       <c r="C187">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:3">
+      <c r="J187">
+        <v>27300</v>
+      </c>
+      <c r="K187">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
       <c r="A188" s="1" t="s">
         <v>201</v>
       </c>
@@ -3742,8 +4864,14 @@
       <c r="C188">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:3">
+      <c r="J188">
+        <v>27300</v>
+      </c>
+      <c r="K188">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
       <c r="A189" s="1" t="s">
         <v>202</v>
       </c>
@@ -3753,8 +4881,14 @@
       <c r="C189">
         <v>3</v>
       </c>
-    </row>
-    <row r="190" spans="1:3">
+      <c r="J189">
+        <v>27300</v>
+      </c>
+      <c r="K189">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
       <c r="A190" s="2" t="s">
         <v>203</v>
       </c>
@@ -3764,8 +4898,14 @@
       <c r="C190">
         <v>2</v>
       </c>
-    </row>
-    <row r="191" spans="1:3">
+      <c r="J190">
+        <v>27300</v>
+      </c>
+      <c r="K190">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
       <c r="A191" s="1" t="s">
         <v>204</v>
       </c>
@@ -3775,8 +4915,14 @@
       <c r="C191">
         <v>3</v>
       </c>
-    </row>
-    <row r="192" spans="1:3">
+      <c r="J191">
+        <v>27300</v>
+      </c>
+      <c r="K191">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
       <c r="A192" s="1" t="s">
         <v>205</v>
       </c>
@@ -3786,8 +4932,14 @@
       <c r="C192">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:3">
+      <c r="J192">
+        <v>27300</v>
+      </c>
+      <c r="K192">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
       <c r="A193" s="1" t="s">
         <v>206</v>
       </c>
@@ -3797,8 +4949,14 @@
       <c r="C193">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:3">
+      <c r="J193">
+        <v>27300</v>
+      </c>
+      <c r="K193">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
       <c r="A194" s="1" t="s">
         <v>207</v>
       </c>
@@ -3808,8 +4966,14 @@
       <c r="C194">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:3">
+      <c r="J194">
+        <v>27300</v>
+      </c>
+      <c r="K194">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
       <c r="A195" s="1" t="s">
         <v>208</v>
       </c>
@@ -3819,8 +4983,14 @@
       <c r="C195">
         <v>3</v>
       </c>
-    </row>
-    <row r="196" spans="1:3">
+      <c r="J195">
+        <v>27300</v>
+      </c>
+      <c r="K195">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
       <c r="A196" s="1" t="s">
         <v>209</v>
       </c>
@@ -3830,8 +5000,14 @@
       <c r="C196">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:3">
+      <c r="J196">
+        <v>27300</v>
+      </c>
+      <c r="K196">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
       <c r="A197" s="1" t="s">
         <v>210</v>
       </c>
@@ -3841,8 +5017,14 @@
       <c r="C197">
         <v>3</v>
       </c>
-    </row>
-    <row r="198" spans="1:3">
+      <c r="J197">
+        <v>27300</v>
+      </c>
+      <c r="K197">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
       <c r="A198" s="1" t="s">
         <v>211</v>
       </c>
@@ -3852,8 +5034,14 @@
       <c r="C198">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:3">
+      <c r="J198">
+        <v>27300</v>
+      </c>
+      <c r="K198">
+        <v>1026294</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
       <c r="A199" s="1" t="s">
         <v>212</v>
       </c>
@@ -3863,8 +5051,14 @@
       <c r="C199">
         <v>3</v>
       </c>
-    </row>
-    <row r="200" spans="1:3">
+      <c r="J199">
+        <v>294</v>
+      </c>
+      <c r="K199">
+        <v>715765</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
       <c r="A200" s="1" t="s">
         <v>213</v>
       </c>
@@ -3874,8 +5068,14 @@
       <c r="C200">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:3">
+      <c r="J200">
+        <v>294</v>
+      </c>
+      <c r="K200">
+        <v>715765</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
       <c r="A201" s="1" t="s">
         <v>214</v>
       </c>
@@ -3885,8 +5085,14 @@
       <c r="C201">
         <v>3</v>
       </c>
-    </row>
-    <row r="202" spans="1:3">
+      <c r="J201">
+        <v>2500</v>
+      </c>
+      <c r="K201">
+        <v>31584</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
       <c r="A202" s="2" t="s">
         <v>215</v>
       </c>
@@ -3895,6 +5101,12 @@
       </c>
       <c r="C202">
         <v>1</v>
+      </c>
+      <c r="J202">
+        <v>1000</v>
+      </c>
+      <c r="K202">
+        <v>79258</v>
       </c>
     </row>
   </sheetData>
@@ -4112,7 +5324,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4124,7 +5336,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/emprical study.xlsx
+++ b/emprical study.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="241">
   <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/17743</t>
   </si>
@@ -40,6 +40,9 @@
     <t>39+90 = 129</t>
   </si>
   <si>
+    <t>9.8k</t>
+  </si>
+  <si>
     <t>https://github.com/HedvigInsurance/android/pull/2464</t>
   </si>
   <si>
@@ -106,12 +109,21 @@
     <t>https://github.com/mostafaalagamy/Metrolist/pull/327</t>
   </si>
   <si>
+    <t>2.0k</t>
+  </si>
+  <si>
     <t>https://github.com/tuskyapp/Tusky/pull/1286</t>
   </si>
   <si>
+    <t>2.6k</t>
+  </si>
+  <si>
     <t>https://github.com/simondankelmann/Bluetooth-LE-Spam/pull/356</t>
   </si>
   <si>
+    <t>4.4k</t>
+  </si>
+  <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/15842</t>
   </si>
   <si>
@@ -124,6 +136,9 @@
     <t>https://github.com/Automattic/pocket-casts-android/pull/3698</t>
   </si>
   <si>
+    <t>2.7k</t>
+  </si>
+  <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/17724</t>
   </si>
   <si>
@@ -136,6 +151,9 @@
     <t>https://github.com/HabitRPG/habitica-android/issues/2104</t>
   </si>
   <si>
+    <t>1.6k</t>
+  </si>
+  <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/14041</t>
   </si>
   <si>
@@ -169,6 +187,9 @@
     <t>https://github.com/commons-app/apps-android-commons/pull/6120</t>
   </si>
   <si>
+    <t>1.1k</t>
+  </si>
+  <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/13123</t>
   </si>
   <si>
@@ -205,6 +226,9 @@
     <t>https://github.com/bitwarden/android/pull/4065</t>
   </si>
   <si>
+    <t>7.6k</t>
+  </si>
+  <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/6807/files</t>
   </si>
   <si>
@@ -229,12 +253,18 @@
     <t>https://github.com/kickstarter/android-oss/pull/1054</t>
   </si>
   <si>
+    <t>5.8k</t>
+  </si>
+  <si>
     <t>https://github.com/kickstarter/android-oss/pull/603</t>
   </si>
   <si>
     <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9761</t>
   </si>
   <si>
+    <t>3.1k</t>
+  </si>
+  <si>
     <t>https://github.com/wordpress-mobile/WordPress-Android/pull/19771</t>
   </si>
   <si>
@@ -262,6 +292,9 @@
     <t>https://github.com/thunderbird/thunderbird-android/pull/7872</t>
   </si>
   <si>
+    <t>12.3k</t>
+  </si>
+  <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/4242</t>
   </si>
   <si>
@@ -277,6 +310,9 @@
     <t>https://github.com/libre-tube/LibreTube/pull/5761#discussioncomment-8787935</t>
   </si>
   <si>
+    <t>10.2k</t>
+  </si>
+  <si>
     <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9711</t>
   </si>
   <si>
@@ -292,18 +328,27 @@
     <t>https://github.com/whitescent/Mastify/pull/39</t>
   </si>
   <si>
+    <t>6.2k</t>
+  </si>
+  <si>
     <t>https://github.com/wikimedia/apps-android-wikipedia/pull/4442</t>
   </si>
   <si>
     <t>https://github.com/mozilla-mobile/firefox-android/pull/6077</t>
   </si>
   <si>
+    <t>1.8k</t>
+  </si>
+  <si>
     <t>https://github.com/whitescent/Mastify/pull/33</t>
   </si>
   <si>
     <t>https://github.com/kiwix/kiwix-android/pull/3823</t>
   </si>
   <si>
+    <t>1k</t>
+  </si>
+  <si>
     <t>https://github.com/breezy-weather/breezy-weather/pull/713</t>
   </si>
   <si>
@@ -328,6 +373,9 @@
     <t>https://github.com/osfans/trime/pull/1193</t>
   </si>
   <si>
+    <t>3.6k</t>
+  </si>
+  <si>
     <t>https://github.com/mozilla-mobile/firefox-android/pull/3826</t>
   </si>
   <si>
@@ -352,6 +400,9 @@
     <t>https://github.com/ismartcoding/plain-app/pull/82</t>
   </si>
   <si>
+    <t>3k</t>
+  </si>
+  <si>
     <t>https://github.com/oppia/oppia-android/pull/5144</t>
   </si>
   <si>
@@ -382,6 +433,9 @@
     <t>https://github.com/vitorpamplona/amethyst/pull/90</t>
   </si>
   <si>
+    <t>1.3k</t>
+  </si>
+  <si>
     <t>https://github.com/wordpress-mobile/WordPress-Android/pull/17863</t>
   </si>
   <si>
@@ -391,6 +445,9 @@
     <t>https://github.com/home-assistant/android/pull/2988</t>
   </si>
   <si>
+    <t>2.9k</t>
+  </si>
+  <si>
     <t>https://github.com/wordpress-mobile/WordPress-Android/pull/16812</t>
   </si>
   <si>
@@ -436,6 +493,9 @@
     <t>https://github.com/element-hq/element-android/pull/7015/files</t>
   </si>
   <si>
+    <t>3.5k</t>
+  </si>
+  <si>
     <t>https://github.com/woocommerce/woocommerce-android/pull/7188/files</t>
   </si>
   <si>
@@ -499,6 +559,9 @@
     <t>https://github.com/kylecorry31/Trail-Sense/pull/947</t>
   </si>
   <si>
+    <t>2k</t>
+  </si>
+  <si>
     <t>https://github.com/kylecorry31/Trail-Sense/pull/948</t>
   </si>
   <si>
@@ -538,6 +601,9 @@
     <t>https://github.com/signalapp/Signal-Android/issues/7252</t>
   </si>
   <si>
+    <t>27.3k</t>
+  </si>
+  <si>
     <t>https://github.com/signalapp/Signal-Android/issues/7578</t>
   </si>
   <si>
@@ -565,6 +631,9 @@
     <t>kt:58</t>
   </si>
   <si>
+    <t>2.3k</t>
+  </si>
+  <si>
     <t>https://github.com/grote/Transportr/issues/491</t>
   </si>
   <si>
@@ -622,6 +691,9 @@
     <t>https://github.com/laurent22/joplin/issues/2695</t>
   </si>
   <si>
+    <t>50.4k</t>
+  </si>
+  <si>
     <t>https://github.com/openmrs/openmrs-contrib-android-client/pull/620</t>
   </si>
   <si>
@@ -674,6 +746,9 @@
   </si>
   <si>
     <t>https://github.com/yeriomin/YalpStore/issues/372</t>
+  </si>
+  <si>
+    <t>2.5k</t>
   </si>
   <si>
     <t>https://github.com/kiwix/kiwix-android/issues/630</t>
@@ -1292,7 +1367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1304,6 +1379,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -1638,8 +1716,8 @@
       <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="J1">
-        <v>9800</v>
+      <c r="J1" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K1">
         <v>273644</v>
@@ -1647,7 +1725,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -1656,15 +1734,15 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4">
         <v>138</v>
       </c>
       <c r="K2">
@@ -1673,7 +1751,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>1.2</v>
@@ -1682,13 +1760,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>34</v>
       </c>
-      <c r="J3">
-        <v>9800</v>
+      <c r="J3" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K3">
         <v>273644</v>
@@ -1696,22 +1774,22 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>18</v>
       </c>
-      <c r="J4">
-        <v>9800</v>
+      <c r="J4" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K4">
         <v>273644</v>
@@ -1719,16 +1797,16 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>9800</v>
+      <c r="J5" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K5">
         <v>273644</v>
@@ -1736,7 +1814,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>1.2</v>
@@ -1744,8 +1822,8 @@
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>9800</v>
+      <c r="J6" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K6">
         <v>273644</v>
@@ -1753,16 +1831,16 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>9800</v>
+      <c r="J7" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K7">
         <v>273644</v>
@@ -1770,7 +1848,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -1778,7 +1856,7 @@
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="4">
         <v>159</v>
       </c>
       <c r="K8">
@@ -1787,15 +1865,15 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="4">
         <v>654</v>
       </c>
       <c r="K9">
@@ -1804,7 +1882,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>1.2</v>
@@ -1816,8 +1894,8 @@
         <f>COUNTIF(B:B,2)</f>
         <v>34</v>
       </c>
-      <c r="J10">
-        <v>9800</v>
+      <c r="J10" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K10">
         <v>273644</v>
@@ -1825,16 +1903,16 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
-      <c r="J11">
-        <v>9800</v>
+      <c r="J11" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K11">
         <v>273644</v>
@@ -1842,16 +1920,16 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="J12">
-        <v>9800</v>
+      <c r="J12" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K12">
         <v>273644</v>
@@ -1859,7 +1937,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1867,7 +1945,7 @@
       <c r="C13">
         <v>3</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="4">
         <v>294</v>
       </c>
       <c r="K13">
@@ -1876,16 +1954,16 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
-      <c r="J14">
-        <v>9800</v>
+      <c r="J14" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K14">
         <v>273644</v>
@@ -1893,7 +1971,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -1901,8 +1979,8 @@
       <c r="C15">
         <v>2</v>
       </c>
-      <c r="J15">
-        <v>9800</v>
+      <c r="J15" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K15">
         <v>273644</v>
@@ -1910,7 +1988,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>1.2</v>
@@ -1918,8 +1996,8 @@
       <c r="C16">
         <v>1</v>
       </c>
-      <c r="J16">
-        <v>2000</v>
+      <c r="J16" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="K16">
         <v>80752</v>
@@ -1927,7 +2005,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>1.2</v>
@@ -1935,8 +2013,8 @@
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="J17">
-        <v>2600</v>
+      <c r="J17" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="K17">
         <v>168638</v>
@@ -1944,7 +2022,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -1952,8 +2030,8 @@
       <c r="C18">
         <v>1</v>
       </c>
-      <c r="J18">
-        <v>4400</v>
+      <c r="J18" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="K18">
         <v>9951</v>
@@ -1961,16 +2039,16 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
-      <c r="J19">
-        <v>9800</v>
+      <c r="J19" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K19">
         <v>273644</v>
@@ -1978,7 +2056,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>1.2</v>
@@ -1986,8 +2064,8 @@
       <c r="C20">
         <v>1</v>
       </c>
-      <c r="J20">
-        <v>9800</v>
+      <c r="J20" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K20">
         <v>273644</v>
@@ -1995,16 +2073,16 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
-      <c r="J21">
-        <v>9800</v>
+      <c r="J21" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K21">
         <v>273644</v>
@@ -2012,16 +2090,16 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
-      <c r="J22">
-        <v>2700</v>
+      <c r="J22" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K22">
         <v>382040</v>
@@ -2029,16 +2107,16 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
-      <c r="J23">
-        <v>9800</v>
+      <c r="J23" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K23">
         <v>273644</v>
@@ -2046,7 +2124,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>1.2</v>
@@ -2054,8 +2132,8 @@
       <c r="C24">
         <v>3</v>
       </c>
-      <c r="J24">
-        <v>9800</v>
+      <c r="J24" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K24">
         <v>273644</v>
@@ -2063,16 +2141,16 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
-      <c r="J25">
-        <v>9800</v>
+      <c r="J25" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K25">
         <v>273644</v>
@@ -2080,7 +2158,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B26">
         <v>1.2</v>
@@ -2088,8 +2166,8 @@
       <c r="C26">
         <v>2</v>
       </c>
-      <c r="J26">
-        <v>1600</v>
+      <c r="J26" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K26">
         <v>152797</v>
@@ -2097,16 +2175,16 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
-      <c r="J27">
-        <v>9800</v>
+      <c r="J27" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K27">
         <v>273644</v>
@@ -2114,7 +2192,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B28">
         <v>1.2</v>
@@ -2122,8 +2200,8 @@
       <c r="C28">
         <v>2</v>
       </c>
-      <c r="J28">
-        <v>2600</v>
+      <c r="J28" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="K28">
         <v>168638</v>
@@ -2131,7 +2209,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -2139,8 +2217,8 @@
       <c r="C29">
         <v>3</v>
       </c>
-      <c r="J29">
-        <v>9800</v>
+      <c r="J29" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K29">
         <v>273644</v>
@@ -2148,7 +2226,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -2156,7 +2234,7 @@
       <c r="C30">
         <v>2</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="4">
         <v>132</v>
       </c>
       <c r="K30">
@@ -2165,7 +2243,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B31">
         <v>1.2</v>
@@ -2173,8 +2251,8 @@
       <c r="C31">
         <v>3</v>
       </c>
-      <c r="J31">
-        <v>9800</v>
+      <c r="J31" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K31">
         <v>273644</v>
@@ -2182,15 +2260,15 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="4">
         <v>477</v>
       </c>
       <c r="K32">
@@ -2199,7 +2277,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -2207,8 +2285,8 @@
       <c r="C33">
         <v>1</v>
       </c>
-      <c r="J33">
-        <v>2700</v>
+      <c r="J33" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K33">
         <v>382040</v>
@@ -2216,15 +2294,15 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="4">
         <v>320</v>
       </c>
       <c r="K34">
@@ -2233,16 +2311,16 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
-      <c r="J35">
-        <v>9800</v>
+      <c r="J35" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K35">
         <v>273644</v>
@@ -2250,15 +2328,15 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="4">
         <v>294</v>
       </c>
       <c r="K36">
@@ -2267,16 +2345,16 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
-      <c r="J37">
-        <v>1100</v>
+      <c r="J37" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="K37">
         <v>145271</v>
@@ -2284,16 +2362,16 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
-      <c r="J38">
-        <v>9800</v>
+      <c r="J38" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K38">
         <v>273644</v>
@@ -2301,16 +2379,16 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
-      <c r="J39">
-        <v>2700</v>
+      <c r="J39" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K39">
         <v>382040</v>
@@ -2318,16 +2396,16 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
-      <c r="J40">
-        <v>9800</v>
+      <c r="J40" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K40">
         <v>273644</v>
@@ -2335,16 +2413,16 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
-      <c r="J41">
-        <v>9800</v>
+      <c r="J41" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K41">
         <v>273644</v>
@@ -2352,16 +2430,16 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
-      <c r="J42">
-        <v>9800</v>
+      <c r="J42" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K42">
         <v>273644</v>
@@ -2369,7 +2447,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B43">
         <v>1.2</v>
@@ -2377,7 +2455,7 @@
       <c r="C43">
         <v>2</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="4">
         <v>437</v>
       </c>
       <c r="K43">
@@ -2386,7 +2464,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -2394,8 +2472,8 @@
       <c r="C44">
         <v>1</v>
       </c>
-      <c r="J44">
-        <v>9800</v>
+      <c r="J44" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K44">
         <v>273644</v>
@@ -2403,16 +2481,16 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
-      <c r="J45">
-        <v>9800</v>
+      <c r="J45" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K45">
         <v>273644</v>
@@ -2420,16 +2498,16 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
-      <c r="J46">
-        <v>9800</v>
+      <c r="J46" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K46">
         <v>273644</v>
@@ -2437,15 +2515,15 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="4">
         <v>416</v>
       </c>
       <c r="K47">
@@ -2454,16 +2532,16 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
-      <c r="J48">
-        <v>9800</v>
+      <c r="J48" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K48">
         <v>273644</v>
@@ -2471,16 +2549,16 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
-      <c r="J49">
-        <v>7600</v>
+      <c r="J49" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="K49">
         <v>361663</v>
@@ -2488,7 +2566,7 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B50">
         <v>2</v>
@@ -2496,8 +2574,8 @@
       <c r="C50">
         <v>3</v>
       </c>
-      <c r="J50">
-        <v>9800</v>
+      <c r="J50" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K50">
         <v>273644</v>
@@ -2505,7 +2583,7 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2513,7 +2591,7 @@
       <c r="C51">
         <v>2</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="4">
         <v>491</v>
       </c>
       <c r="K51">
@@ -2522,16 +2600,16 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
-      <c r="J52">
-        <v>2700</v>
+      <c r="J52" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K52">
         <v>382040</v>
@@ -2539,7 +2617,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -2547,8 +2625,8 @@
       <c r="C53">
         <v>2</v>
       </c>
-      <c r="J53">
-        <v>9800</v>
+      <c r="J53" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K53">
         <v>273644</v>
@@ -2556,7 +2634,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B54">
         <v>3</v>
@@ -2565,10 +2643,10 @@
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>63</v>
-      </c>
-      <c r="J54">
-        <v>7600</v>
+        <v>71</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="K54">
         <v>146939</v>
@@ -2576,7 +2654,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B55">
         <v>3</v>
@@ -2584,8 +2662,8 @@
       <c r="C55">
         <v>2</v>
       </c>
-      <c r="J55">
-        <v>7600</v>
+      <c r="J55" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="K55">
         <v>146939</v>
@@ -2593,7 +2671,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -2601,8 +2679,8 @@
       <c r="C56">
         <v>1</v>
       </c>
-      <c r="J56">
-        <v>5800</v>
+      <c r="J56" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="K56">
         <v>184252</v>
@@ -2610,16 +2688,16 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
-      <c r="J57">
-        <v>5800</v>
+      <c r="J57" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="K57">
         <v>184252</v>
@@ -2627,7 +2705,7 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B58">
         <v>1.1</v>
@@ -2635,8 +2713,8 @@
       <c r="C58">
         <v>3</v>
       </c>
-      <c r="J58">
-        <v>3100</v>
+      <c r="J58" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K58">
         <v>750760</v>
@@ -2644,7 +2722,7 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B59">
         <v>1.1</v>
@@ -2652,8 +2730,8 @@
       <c r="C59">
         <v>3</v>
       </c>
-      <c r="J59">
-        <v>3100</v>
+      <c r="J59" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K59">
         <v>750760</v>
@@ -2661,16 +2739,16 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
-      <c r="J60">
-        <v>7600</v>
+      <c r="J60" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="K60">
         <v>146939</v>
@@ -2678,16 +2756,16 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
-      <c r="J61">
-        <v>3100</v>
+      <c r="J61" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K61">
         <v>750760</v>
@@ -2695,7 +2773,7 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B62">
         <v>1.1</v>
@@ -2703,7 +2781,7 @@
       <c r="C62">
         <v>1</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="4">
         <v>155</v>
       </c>
       <c r="K62">
@@ -2712,7 +2790,7 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -2721,10 +2799,10 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>63</v>
-      </c>
-      <c r="J63">
-        <v>3100</v>
+        <v>71</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K63">
         <v>750760</v>
@@ -2732,16 +2810,16 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
-      <c r="J64">
-        <v>5800</v>
+      <c r="J64" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="K64">
         <v>184252</v>
@@ -2749,16 +2827,16 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65">
         <v>2</v>
       </c>
-      <c r="J65">
-        <v>3100</v>
+      <c r="J65" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K65">
         <v>750760</v>
@@ -2766,16 +2844,16 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
-      <c r="J66">
-        <v>3100</v>
+      <c r="J66" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K66">
         <v>750760</v>
@@ -2783,7 +2861,7 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B67">
         <v>1.1</v>
@@ -2791,8 +2869,8 @@
       <c r="C67">
         <v>3</v>
       </c>
-      <c r="J67">
-        <v>12300</v>
+      <c r="J67" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K67">
         <v>303600</v>
@@ -2800,16 +2878,16 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
-      <c r="J68">
-        <v>9800</v>
+      <c r="J68" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K68">
         <v>273644</v>
@@ -2817,7 +2895,7 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B69">
         <v>1.1</v>
@@ -2825,7 +2903,7 @@
       <c r="C69">
         <v>1</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="4">
         <v>717</v>
       </c>
       <c r="K69">
@@ -2834,16 +2912,16 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
-      <c r="J70">
-        <v>3100</v>
+      <c r="J70" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K70">
         <v>750760</v>
@@ -2851,7 +2929,7 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B71">
         <v>1.1</v>
@@ -2859,8 +2937,8 @@
       <c r="C71">
         <v>1</v>
       </c>
-      <c r="J71">
-        <v>10200</v>
+      <c r="J71" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="K71">
         <v>88762</v>
@@ -2868,16 +2946,16 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
-      <c r="J72">
-        <v>3100</v>
+      <c r="J72" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K72">
         <v>750760</v>
@@ -2885,7 +2963,7 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B73">
         <v>3</v>
@@ -2893,8 +2971,8 @@
       <c r="C73">
         <v>3</v>
       </c>
-      <c r="J73">
-        <v>3100</v>
+      <c r="J73" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K73">
         <v>750760</v>
@@ -2902,16 +2980,16 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
-      <c r="J74">
-        <v>3100</v>
+      <c r="J74" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K74">
         <v>750760</v>
@@ -2919,16 +2997,16 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
-      <c r="J75">
-        <v>9800</v>
+      <c r="J75" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K75">
         <v>273644</v>
@@ -2936,16 +3014,16 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
-      <c r="J76">
-        <v>6233</v>
+      <c r="J76" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="K76">
         <v>371029</v>
@@ -2953,7 +3031,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B77">
         <v>1.1</v>
@@ -2961,8 +3039,8 @@
       <c r="C77">
         <v>1</v>
       </c>
-      <c r="J77">
-        <v>2700</v>
+      <c r="J77" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K77">
         <v>306479</v>
@@ -2970,7 +3048,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -2978,8 +3056,8 @@
       <c r="C78">
         <v>1</v>
       </c>
-      <c r="J78">
-        <v>1800</v>
+      <c r="J78" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="K78">
         <v>900774</v>
@@ -2987,7 +3065,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B79">
         <v>1.1</v>
@@ -2995,8 +3073,8 @@
       <c r="C79">
         <v>3</v>
       </c>
-      <c r="J79">
-        <v>6233</v>
+      <c r="J79" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="K79">
         <v>371029</v>
@@ -3004,16 +3082,16 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
-      <c r="J80">
-        <v>1000</v>
+      <c r="J80" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K80">
         <v>79258</v>
@@ -3021,7 +3099,7 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B81">
         <v>1.1</v>
@@ -3029,8 +3107,8 @@
       <c r="C81">
         <v>2</v>
       </c>
-      <c r="J81">
-        <v>7600</v>
+      <c r="J81" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="K81">
         <v>146939</v>
@@ -3038,15 +3116,15 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="4">
         <v>270</v>
       </c>
       <c r="K82">
@@ -3055,7 +3133,7 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -3063,8 +3141,8 @@
       <c r="C83">
         <v>3</v>
       </c>
-      <c r="J83">
-        <v>3100</v>
+      <c r="J83" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K83">
         <v>750760</v>
@@ -3072,7 +3150,7 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B84">
         <v>1.1</v>
@@ -3080,8 +3158,8 @@
       <c r="C84">
         <v>1</v>
       </c>
-      <c r="J84">
-        <v>9800</v>
+      <c r="J84" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K84">
         <v>273644</v>
@@ -3089,15 +3167,15 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="4">
         <v>632</v>
       </c>
       <c r="K85">
@@ -3106,16 +3184,16 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
-      <c r="J86">
-        <v>2700</v>
+      <c r="J86" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K86">
         <v>306479</v>
@@ -3123,7 +3201,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B87">
         <v>1.1</v>
@@ -3131,7 +3209,7 @@
       <c r="C87">
         <v>1</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="4">
         <v>368</v>
       </c>
       <c r="K87">
@@ -3140,7 +3218,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -3148,8 +3226,8 @@
       <c r="C88">
         <v>2</v>
       </c>
-      <c r="J88">
-        <v>3600</v>
+      <c r="J88" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="K88">
         <v>33430</v>
@@ -3157,7 +3235,7 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B89">
         <v>1.1</v>
@@ -3165,8 +3243,8 @@
       <c r="C89">
         <v>2</v>
       </c>
-      <c r="J89">
-        <v>1800</v>
+      <c r="J89" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="K89">
         <v>900774</v>
@@ -3174,7 +3252,7 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B90">
         <v>1.1</v>
@@ -3182,7 +3260,7 @@
       <c r="C90">
         <v>2</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="4">
         <v>363</v>
       </c>
       <c r="K90">
@@ -3191,16 +3269,16 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
-      <c r="J91">
-        <v>1800</v>
+      <c r="J91" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="K91">
         <v>900774</v>
@@ -3208,16 +3286,16 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C92">
         <v>3</v>
       </c>
-      <c r="J92">
-        <v>12300</v>
+      <c r="J92" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K92">
         <v>303600</v>
@@ -3225,7 +3303,7 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B93">
         <v>1.1</v>
@@ -3233,8 +3311,8 @@
       <c r="C93">
         <v>3</v>
       </c>
-      <c r="J93">
-        <v>12300</v>
+      <c r="J93" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K93">
         <v>303600</v>
@@ -3242,7 +3320,7 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B94">
         <v>1.1</v>
@@ -3250,7 +3328,7 @@
       <c r="C94">
         <v>1</v>
       </c>
-      <c r="J94">
+      <c r="J94" s="4">
         <v>351</v>
       </c>
       <c r="K94">
@@ -3259,7 +3337,7 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -3267,8 +3345,8 @@
       <c r="C95">
         <v>3</v>
       </c>
-      <c r="J95">
-        <v>12300</v>
+      <c r="J95" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K95">
         <v>303600</v>
@@ -3276,16 +3354,16 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
-      <c r="J96">
-        <v>3000</v>
+      <c r="J96" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="K96">
         <v>143120</v>
@@ -3293,15 +3371,15 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
-      <c r="J97">
+      <c r="J97" s="4">
         <v>351</v>
       </c>
       <c r="K97">
@@ -3310,7 +3388,7 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -3318,7 +3396,7 @@
       <c r="C98">
         <v>2</v>
       </c>
-      <c r="J98">
+      <c r="J98" s="4">
         <v>988</v>
       </c>
       <c r="K98">
@@ -3327,7 +3405,7 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B99">
         <v>1.1</v>
@@ -3335,7 +3413,7 @@
       <c r="C99">
         <v>2</v>
       </c>
-      <c r="J99">
+      <c r="J99" s="4">
         <v>212</v>
       </c>
       <c r="K99">
@@ -3344,16 +3422,16 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
-      <c r="J100">
-        <v>10200</v>
+      <c r="J100" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="K100">
         <v>88762</v>
@@ -3361,7 +3439,7 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -3369,8 +3447,8 @@
       <c r="C101">
         <v>2</v>
       </c>
-      <c r="J101">
-        <v>3100</v>
+      <c r="J101" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K101">
         <v>750760</v>
@@ -3378,7 +3456,7 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -3386,7 +3464,7 @@
       <c r="C102">
         <v>1</v>
       </c>
-      <c r="J102">
+      <c r="J102" s="4">
         <v>628</v>
       </c>
       <c r="K102">
@@ -3395,7 +3473,7 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B103">
         <v>1.1</v>
@@ -3403,8 +3481,8 @@
       <c r="C103">
         <v>2</v>
       </c>
-      <c r="J103">
-        <v>3100</v>
+      <c r="J103" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K103">
         <v>750760</v>
@@ -3412,16 +3490,16 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
-      <c r="J104">
-        <v>12300</v>
+      <c r="J104" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K104">
         <v>303600</v>
@@ -3429,15 +3507,15 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B105" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C105">
         <v>1</v>
       </c>
-      <c r="J105">
+      <c r="J105" s="4">
         <v>294</v>
       </c>
       <c r="K105">
@@ -3446,7 +3524,7 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B106">
         <v>1.1</v>
@@ -3454,8 +3532,8 @@
       <c r="C106">
         <v>2</v>
       </c>
-      <c r="J106">
-        <v>1300</v>
+      <c r="J106" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="K106">
         <v>212043</v>
@@ -3463,7 +3541,7 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B107">
         <v>3</v>
@@ -3471,8 +3549,8 @@
       <c r="C107">
         <v>1</v>
       </c>
-      <c r="J107">
-        <v>3100</v>
+      <c r="J107" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K107">
         <v>750760</v>
@@ -3480,15 +3558,15 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B108" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
-      <c r="J108">
+      <c r="J108" s="4">
         <v>181</v>
       </c>
       <c r="K108">
@@ -3497,7 +3575,7 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="1" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B109">
         <v>1.1</v>
@@ -3505,8 +3583,8 @@
       <c r="C109">
         <v>1</v>
       </c>
-      <c r="J109">
-        <v>2900</v>
+      <c r="J109" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="K109">
         <v>110253</v>
@@ -3514,16 +3592,16 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C110">
         <v>3</v>
       </c>
-      <c r="J110">
-        <v>3100</v>
+      <c r="J110" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K110">
         <v>750760</v>
@@ -3531,15 +3609,15 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
-      <c r="J111">
+      <c r="J111" s="4">
         <v>208</v>
       </c>
       <c r="K111">
@@ -3548,7 +3626,7 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="B112">
         <v>2</v>
@@ -3556,8 +3634,8 @@
       <c r="C112">
         <v>1</v>
       </c>
-      <c r="J112">
-        <v>9800</v>
+      <c r="J112" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K112">
         <v>273644</v>
@@ -3565,16 +3643,16 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
-      <c r="J113">
-        <v>2900</v>
+      <c r="J113" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="K113">
         <v>110253</v>
@@ -3582,7 +3660,7 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="B114">
         <v>1.1</v>
@@ -3590,8 +3668,8 @@
       <c r="C114">
         <v>1</v>
       </c>
-      <c r="J114">
-        <v>12300</v>
+      <c r="J114" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K114">
         <v>303600</v>
@@ -3599,7 +3677,7 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="B115">
         <v>1.1</v>
@@ -3607,7 +3685,7 @@
       <c r="C115">
         <v>2</v>
       </c>
-      <c r="J115">
+      <c r="J115" s="4">
         <v>110</v>
       </c>
       <c r="K115">
@@ -3616,7 +3694,7 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B116">
         <v>1.1</v>
@@ -3624,8 +3702,8 @@
       <c r="C116">
         <v>1</v>
       </c>
-      <c r="J116">
-        <v>2900</v>
+      <c r="J116" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="K116">
         <v>110253</v>
@@ -3633,16 +3711,16 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="1" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
-      <c r="J117">
-        <v>2700</v>
+      <c r="J117" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K117">
         <v>382040</v>
@@ -3650,7 +3728,7 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B118">
         <v>1.1</v>
@@ -3658,7 +3736,7 @@
       <c r="C118">
         <v>1</v>
       </c>
-      <c r="J118">
+      <c r="J118" s="4">
         <v>836</v>
       </c>
       <c r="K118">
@@ -3667,7 +3745,7 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="B119">
         <v>2</v>
@@ -3675,8 +3753,8 @@
       <c r="C119">
         <v>2</v>
       </c>
-      <c r="J119">
-        <v>2700</v>
+      <c r="J119" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="K119">
         <v>382040</v>
@@ -3684,16 +3762,16 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
-      <c r="J120">
-        <v>9800</v>
+      <c r="J120" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K120">
         <v>273644</v>
@@ -3701,7 +3779,7 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="1" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="B121">
         <v>3</v>
@@ -3709,8 +3787,8 @@
       <c r="C121">
         <v>2</v>
       </c>
-      <c r="J121">
-        <v>3100</v>
+      <c r="J121" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K121">
         <v>750760</v>
@@ -3718,7 +3796,7 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -3726,7 +3804,7 @@
       <c r="C122">
         <v>1</v>
       </c>
-      <c r="J122">
+      <c r="J122" s="4">
         <v>351</v>
       </c>
       <c r="K122">
@@ -3735,7 +3813,7 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -3743,7 +3821,7 @@
       <c r="C123">
         <v>1</v>
       </c>
-      <c r="J123">
+      <c r="J123" s="4">
         <v>351</v>
       </c>
       <c r="K123">
@@ -3752,7 +3830,7 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -3760,8 +3838,8 @@
       <c r="C124">
         <v>3</v>
       </c>
-      <c r="J124">
-        <v>3500</v>
+      <c r="J124" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="K124">
         <v>446442</v>
@@ -3769,7 +3847,7 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="1" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -3777,7 +3855,7 @@
       <c r="C125">
         <v>3</v>
       </c>
-      <c r="J125">
+      <c r="J125" s="4">
         <v>294</v>
       </c>
       <c r="K125">
@@ -3786,15 +3864,15 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="1" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C126">
         <v>2</v>
       </c>
-      <c r="J126">
+      <c r="J126" s="4">
         <v>274</v>
       </c>
       <c r="K126">
@@ -3803,16 +3881,16 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C127">
         <v>3</v>
       </c>
-      <c r="J127">
-        <v>2900</v>
+      <c r="J127" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="K127">
         <v>110253</v>
@@ -3820,16 +3898,16 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C128">
         <v>3</v>
       </c>
-      <c r="J128">
-        <v>9800</v>
+      <c r="J128" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K128">
         <v>273644</v>
@@ -3837,7 +3915,7 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="B129">
         <v>1.1</v>
@@ -3845,7 +3923,7 @@
       <c r="C129">
         <v>1</v>
       </c>
-      <c r="J129">
+      <c r="J129" s="4">
         <v>836</v>
       </c>
       <c r="K129">
@@ -3854,7 +3932,7 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="1" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B130">
         <v>2</v>
@@ -3862,8 +3940,8 @@
       <c r="C130">
         <v>3</v>
       </c>
-      <c r="J130">
-        <v>3500</v>
+      <c r="J130" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="K130">
         <v>446442</v>
@@ -3871,16 +3949,16 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C131">
         <v>3</v>
       </c>
-      <c r="J131">
-        <v>3500</v>
+      <c r="J131" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="K131">
         <v>446442</v>
@@ -3888,7 +3966,7 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B132">
         <v>2</v>
@@ -3896,7 +3974,7 @@
       <c r="C132">
         <v>1</v>
       </c>
-      <c r="J132">
+      <c r="J132" s="4">
         <v>836</v>
       </c>
       <c r="K132">
@@ -3905,15 +3983,15 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="B133" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C133">
         <v>1</v>
       </c>
-      <c r="J133">
+      <c r="J133" s="4">
         <v>836</v>
       </c>
       <c r="K133">
@@ -3922,7 +4000,7 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B134">
         <v>1.1</v>
@@ -3930,7 +4008,7 @@
       <c r="C134">
         <v>1</v>
       </c>
-      <c r="J134">
+      <c r="J134" s="4">
         <v>836</v>
       </c>
       <c r="K134">
@@ -3939,15 +4017,15 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B135" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C135">
         <v>3</v>
       </c>
-      <c r="J135">
+      <c r="J135" s="4">
         <v>836</v>
       </c>
       <c r="K135">
@@ -3956,7 +4034,7 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="1" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="B136">
         <v>3</v>
@@ -3964,8 +4042,8 @@
       <c r="C136">
         <v>2</v>
       </c>
-      <c r="J136">
-        <v>1600</v>
+      <c r="J136" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K136">
         <v>342821</v>
@@ -3973,15 +4051,15 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="1" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C137">
         <v>3</v>
       </c>
-      <c r="J137">
+      <c r="J137" s="4">
         <v>836</v>
       </c>
       <c r="K137">
@@ -3990,7 +4068,7 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="1" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B138">
         <v>3</v>
@@ -3998,7 +4076,7 @@
       <c r="C138">
         <v>3</v>
       </c>
-      <c r="J138">
+      <c r="J138" s="4">
         <v>836</v>
       </c>
       <c r="K138">
@@ -4007,7 +4085,7 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="B139">
         <v>1.1</v>
@@ -4015,7 +4093,7 @@
       <c r="C139">
         <v>3</v>
       </c>
-      <c r="J139">
+      <c r="J139" s="4">
         <v>836</v>
       </c>
       <c r="K139">
@@ -4024,15 +4102,15 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="1" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B140" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
-      <c r="J140">
+      <c r="J140" s="4">
         <v>160</v>
       </c>
       <c r="K140">
@@ -4041,7 +4119,7 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="1" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="B141">
         <v>2</v>
@@ -4049,7 +4127,7 @@
       <c r="C141">
         <v>1</v>
       </c>
-      <c r="J141">
+      <c r="J141" s="4">
         <v>836</v>
       </c>
       <c r="K141">
@@ -4058,15 +4136,15 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="1" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B142" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C142">
         <v>2</v>
       </c>
-      <c r="J142">
+      <c r="J142" s="4">
         <v>593</v>
       </c>
       <c r="K142">
@@ -4075,7 +4153,7 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="1" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="B143">
         <v>3</v>
@@ -4083,7 +4161,7 @@
       <c r="C143">
         <v>1</v>
       </c>
-      <c r="J143">
+      <c r="J143" s="4">
         <v>405</v>
       </c>
       <c r="K143">
@@ -4092,15 +4170,15 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C144">
         <v>3</v>
       </c>
-      <c r="J144">
+      <c r="J144" s="4">
         <v>836</v>
       </c>
       <c r="K144">
@@ -4109,7 +4187,7 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B145">
         <v>3</v>
@@ -4117,8 +4195,8 @@
       <c r="C145">
         <v>1</v>
       </c>
-      <c r="J145">
-        <v>2000</v>
+      <c r="J145" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="K145">
         <v>154610</v>
@@ -4126,16 +4204,16 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="2" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="B146" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
-      <c r="J146">
-        <v>2000</v>
+      <c r="J146" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="K146">
         <v>154610</v>
@@ -4143,7 +4221,7 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="B147">
         <v>2</v>
@@ -4151,8 +4229,8 @@
       <c r="C147">
         <v>3</v>
       </c>
-      <c r="J147">
-        <v>1000</v>
+      <c r="J147" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K147">
         <v>79258</v>
@@ -4160,7 +4238,7 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="B148">
         <v>1.1</v>
@@ -4168,7 +4246,7 @@
       <c r="C148">
         <v>1</v>
       </c>
-      <c r="J148">
+      <c r="J148" s="4">
         <v>516</v>
       </c>
       <c r="K148">
@@ -4177,15 +4255,15 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="2" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
-      <c r="J149">
+      <c r="J149" s="4">
         <v>516</v>
       </c>
       <c r="K149">
@@ -4194,7 +4272,7 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="1" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="B150">
         <v>2</v>
@@ -4202,8 +4280,8 @@
       <c r="C150">
         <v>1</v>
       </c>
-      <c r="J150">
-        <v>1000</v>
+      <c r="J150" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K150">
         <v>79258</v>
@@ -4211,15 +4289,15 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="1" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
-      <c r="J151">
+      <c r="J151" s="4">
         <v>294</v>
       </c>
       <c r="K151">
@@ -4228,7 +4306,7 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="1" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B152">
         <v>3</v>
@@ -4236,8 +4314,8 @@
       <c r="C152">
         <v>1</v>
       </c>
-      <c r="J152">
-        <v>6233</v>
+      <c r="J152" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="K152">
         <v>371029</v>
@@ -4245,7 +4323,7 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="1" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B153">
         <v>3</v>
@@ -4253,7 +4331,7 @@
       <c r="C153">
         <v>2</v>
       </c>
-      <c r="J153">
+      <c r="J153" s="4">
         <v>110</v>
       </c>
       <c r="K153">
@@ -4262,7 +4340,7 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="2" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="B154">
         <v>1.1</v>
@@ -4270,7 +4348,7 @@
       <c r="C154">
         <v>2</v>
       </c>
-      <c r="J154">
+      <c r="J154" s="4">
         <v>851</v>
       </c>
       <c r="K154">
@@ -4279,16 +4357,16 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="2" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="B155" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C155">
         <v>3</v>
       </c>
-      <c r="J155">
-        <v>9800</v>
+      <c r="J155" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="K155">
         <v>273644</v>
@@ -4296,16 +4374,16 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C156">
         <v>2</v>
       </c>
-      <c r="J156">
-        <v>12300</v>
+      <c r="J156" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K156">
         <v>303600</v>
@@ -4313,16 +4391,16 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B157" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C157">
         <v>3</v>
       </c>
-      <c r="J157">
-        <v>12300</v>
+      <c r="J157" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K157">
         <v>303600</v>
@@ -4330,7 +4408,7 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="1" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B158">
         <v>2</v>
@@ -4338,8 +4416,8 @@
       <c r="C158">
         <v>1</v>
       </c>
-      <c r="J158">
-        <v>27300</v>
+      <c r="J158" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K158">
         <v>1026294</v>
@@ -4347,7 +4425,7 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="1" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B159">
         <v>1.1</v>
@@ -4355,8 +4433,8 @@
       <c r="C159">
         <v>1</v>
       </c>
-      <c r="J159">
-        <v>27300</v>
+      <c r="J159" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K159">
         <v>1026294</v>
@@ -4364,7 +4442,7 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="1" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B160">
         <v>3</v>
@@ -4372,8 +4450,8 @@
       <c r="C160">
         <v>3</v>
       </c>
-      <c r="J160">
-        <v>1000</v>
+      <c r="J160" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K160">
         <v>79258</v>
@@ -4381,16 +4459,16 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="1" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C161">
         <v>2</v>
       </c>
-      <c r="J161">
-        <v>3000</v>
+      <c r="J161" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="K161">
         <v>1890734</v>
@@ -4398,16 +4476,16 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="1" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="B162" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
-      <c r="J162">
-        <v>1100</v>
+      <c r="J162" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="K162">
         <v>145271</v>
@@ -4415,16 +4493,16 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B163" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C163">
         <v>2</v>
       </c>
-      <c r="J163">
-        <v>1100</v>
+      <c r="J163" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="K163">
         <v>145271</v>
@@ -4432,7 +4510,7 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="1" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="B164">
         <v>2</v>
@@ -4445,13 +4523,13 @@
         <v>90</v>
       </c>
       <c r="F164" t="s">
-        <v>175</v>
-      </c>
-      <c r="G164" s="4">
+        <v>197</v>
+      </c>
+      <c r="G164" s="5">
         <v>0.7129</v>
       </c>
-      <c r="J164">
-        <v>1100</v>
+      <c r="J164" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="K164">
         <v>145271</v>
@@ -4459,7 +4537,7 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="1" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="B165">
         <v>1.1</v>
@@ -4468,10 +4546,10 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>177</v>
-      </c>
-      <c r="J165">
-        <v>2300</v>
+        <v>199</v>
+      </c>
+      <c r="J165" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="K165">
         <v>90748</v>
@@ -4479,7 +4557,7 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="1" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B166">
         <v>1.1</v>
@@ -4488,10 +4566,10 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>179</v>
-      </c>
-      <c r="J166">
-        <v>1100</v>
+        <v>202</v>
+      </c>
+      <c r="J166" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="K166">
         <v>40036</v>
@@ -4499,16 +4577,16 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="B167" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C167">
         <v>2</v>
       </c>
-      <c r="J167">
-        <v>12300</v>
+      <c r="J167" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K167">
         <v>303600</v>
@@ -4516,16 +4594,16 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="1" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="B168" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C168">
         <v>2</v>
       </c>
-      <c r="J168">
-        <v>12300</v>
+      <c r="J168" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="K168">
         <v>303600</v>
@@ -4533,16 +4611,16 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="1" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C169">
         <v>1</v>
       </c>
-      <c r="J169">
-        <v>1000</v>
+      <c r="J169" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K169">
         <v>79258</v>
@@ -4550,16 +4628,16 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="1" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="B170" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C170">
         <v>3</v>
       </c>
-      <c r="J170">
-        <v>1000</v>
+      <c r="J170" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K170">
         <v>79258</v>
@@ -4567,16 +4645,16 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="1" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="B171" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C171">
         <v>3</v>
       </c>
-      <c r="J171">
-        <v>1000</v>
+      <c r="J171" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K171">
         <v>79258</v>
@@ -4584,16 +4662,16 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="1" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
-      <c r="J172">
-        <v>1000</v>
+      <c r="J172" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K172">
         <v>79258</v>
@@ -4601,16 +4679,16 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="1" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B173" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C173">
         <v>2</v>
       </c>
-      <c r="J173">
-        <v>1000</v>
+      <c r="J173" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K173">
         <v>79258</v>
@@ -4618,7 +4696,7 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="1" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="B174">
         <v>2</v>
@@ -4626,8 +4704,8 @@
       <c r="C174">
         <v>1</v>
       </c>
-      <c r="J174">
-        <v>1000</v>
+      <c r="J174" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K174">
         <v>79258</v>
@@ -4635,16 +4713,16 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="1" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="B175" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
-      <c r="J175">
-        <v>1000</v>
+      <c r="J175" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K175">
         <v>79258</v>
@@ -4652,7 +4730,7 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="1" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B176">
         <v>2</v>
@@ -4660,8 +4738,8 @@
       <c r="C176">
         <v>3</v>
       </c>
-      <c r="J176">
-        <v>1000</v>
+      <c r="J176" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K176">
         <v>79258</v>
@@ -4669,16 +4747,16 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="1" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="B177" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C177">
         <v>3</v>
       </c>
-      <c r="J177">
-        <v>1000</v>
+      <c r="J177" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K177">
         <v>79258</v>
@@ -4686,7 +4764,7 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="1" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="B178">
         <v>1.1</v>
@@ -4694,8 +4772,8 @@
       <c r="C178">
         <v>1</v>
       </c>
-      <c r="J178">
-        <v>1000</v>
+      <c r="J178" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K178">
         <v>79258</v>
@@ -4703,7 +4781,7 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="1" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="B179">
         <v>2</v>
@@ -4711,8 +4789,8 @@
       <c r="C179">
         <v>3</v>
       </c>
-      <c r="J179">
-        <v>1000</v>
+      <c r="J179" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K179">
         <v>79258</v>
@@ -4720,7 +4798,7 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="1" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="B180">
         <v>1.1</v>
@@ -4728,8 +4806,8 @@
       <c r="C180">
         <v>3</v>
       </c>
-      <c r="J180">
-        <v>1000</v>
+      <c r="J180" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K180">
         <v>79258</v>
@@ -4737,16 +4815,16 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="1" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="B181" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C181">
         <v>2</v>
       </c>
-      <c r="J181">
-        <v>1000</v>
+      <c r="J181" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K181">
         <v>79258</v>
@@ -4754,7 +4832,7 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="1" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="B182">
         <v>2</v>
@@ -4762,8 +4840,8 @@
       <c r="C182">
         <v>1</v>
       </c>
-      <c r="J182">
-        <v>1000</v>
+      <c r="J182" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K182">
         <v>79258</v>
@@ -4771,16 +4849,16 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="1" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="B183" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C183">
         <v>2</v>
       </c>
-      <c r="J183">
-        <v>50400</v>
+      <c r="J183" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="K183">
         <v>1074744</v>
@@ -4788,7 +4866,7 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="1" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="B184">
         <v>1.1</v>
@@ -4796,7 +4874,7 @@
       <c r="C184">
         <v>2</v>
       </c>
-      <c r="J184">
+      <c r="J184" s="4">
         <v>181</v>
       </c>
       <c r="K184">
@@ -4805,7 +4883,7 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="1" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="B185">
         <v>1.1</v>
@@ -4813,8 +4891,8 @@
       <c r="C185">
         <v>3</v>
       </c>
-      <c r="J185">
-        <v>27300</v>
+      <c r="J185" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K185">
         <v>1026294</v>
@@ -4822,16 +4900,16 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="1" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="B186" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
-      <c r="J186">
-        <v>27300</v>
+      <c r="J186" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K186">
         <v>1026294</v>
@@ -4839,7 +4917,7 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="1" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="B187">
         <v>1.1</v>
@@ -4847,8 +4925,8 @@
       <c r="C187">
         <v>1</v>
       </c>
-      <c r="J187">
-        <v>27300</v>
+      <c r="J187" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K187">
         <v>1026294</v>
@@ -4856,16 +4934,16 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="1" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="B188" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
-      <c r="J188">
-        <v>27300</v>
+      <c r="J188" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K188">
         <v>1026294</v>
@@ -4873,7 +4951,7 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="1" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="B189">
         <v>1.1</v>
@@ -4881,8 +4959,8 @@
       <c r="C189">
         <v>3</v>
       </c>
-      <c r="J189">
-        <v>27300</v>
+      <c r="J189" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K189">
         <v>1026294</v>
@@ -4890,7 +4968,7 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="B190">
         <v>2</v>
@@ -4898,8 +4976,8 @@
       <c r="C190">
         <v>2</v>
       </c>
-      <c r="J190">
-        <v>27300</v>
+      <c r="J190" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K190">
         <v>1026294</v>
@@ -4907,7 +4985,7 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="1" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="B191">
         <v>3</v>
@@ -4915,8 +4993,8 @@
       <c r="C191">
         <v>3</v>
       </c>
-      <c r="J191">
-        <v>27300</v>
+      <c r="J191" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K191">
         <v>1026294</v>
@@ -4924,16 +5002,16 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="1" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="B192" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
-      <c r="J192">
-        <v>27300</v>
+      <c r="J192" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K192">
         <v>1026294</v>
@@ -4941,16 +5019,16 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="1" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="B193" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
-      <c r="J193">
-        <v>27300</v>
+      <c r="J193" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K193">
         <v>1026294</v>
@@ -4958,7 +5036,7 @@
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="1" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="B194">
         <v>1.1</v>
@@ -4966,8 +5044,8 @@
       <c r="C194">
         <v>1</v>
       </c>
-      <c r="J194">
-        <v>27300</v>
+      <c r="J194" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K194">
         <v>1026294</v>
@@ -4975,16 +5053,16 @@
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="1" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="B195" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C195">
         <v>3</v>
       </c>
-      <c r="J195">
-        <v>27300</v>
+      <c r="J195" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K195">
         <v>1026294</v>
@@ -4992,7 +5070,7 @@
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="1" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="B196">
         <v>1.1</v>
@@ -5000,8 +5078,8 @@
       <c r="C196">
         <v>1</v>
       </c>
-      <c r="J196">
-        <v>27300</v>
+      <c r="J196" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K196">
         <v>1026294</v>
@@ -5009,7 +5087,7 @@
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="1" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="B197">
         <v>1.2</v>
@@ -5017,8 +5095,8 @@
       <c r="C197">
         <v>3</v>
       </c>
-      <c r="J197">
-        <v>27300</v>
+      <c r="J197" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K197">
         <v>1026294</v>
@@ -5026,16 +5104,16 @@
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="1" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="B198" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
-      <c r="J198">
-        <v>27300</v>
+      <c r="J198" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="K198">
         <v>1026294</v>
@@ -5043,15 +5121,15 @@
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="1" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="B199" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C199">
         <v>3</v>
       </c>
-      <c r="J199">
+      <c r="J199" s="4">
         <v>294</v>
       </c>
       <c r="K199">
@@ -5060,15 +5138,15 @@
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="1" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B200" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
-      <c r="J200">
+      <c r="J200" s="4">
         <v>294</v>
       </c>
       <c r="K200">
@@ -5077,16 +5155,16 @@
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="1" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="B201" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C201">
         <v>3</v>
       </c>
-      <c r="J201">
-        <v>2500</v>
+      <c r="J201" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="K201">
         <v>31584</v>
@@ -5094,7 +5172,7 @@
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="B202">
         <v>1.2</v>
@@ -5102,8 +5180,8 @@
       <c r="C202">
         <v>1</v>
       </c>
-      <c r="J202">
-        <v>1000</v>
+      <c r="J202" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K202">
         <v>79258</v>

--- a/emprical study.xlsx
+++ b/emprical study.xlsx
@@ -29,729 +29,696 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="230">
+  <si>
+    <t>https://github.com/Automattic/pocket-casts-android/pull/432</t>
+  </si>
+  <si>
+    <t>1.1+1.2</t>
+  </si>
+  <si>
+    <t>2.7k</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/14041</t>
+  </si>
+  <si>
+    <t>9.8k</t>
+  </si>
+  <si>
+    <t>https://github.com/breezy-weather/breezy-weather/pull/931</t>
+  </si>
+  <si>
+    <t>7.6k</t>
+  </si>
+  <si>
+    <t>https://github.com/wikimedia/apps-android-wikipedia/pull/573</t>
+  </si>
+  <si>
+    <t>1？</t>
+  </si>
+  <si>
+    <t>https://github.com/ismartcoding/plain-app/pull/82</t>
+  </si>
+  <si>
+    <t>3k</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/15683</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/pull/3823</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>https://github.com/tuskyapp/Tusky/pull/4864</t>
+  </si>
+  <si>
+    <t>2.6k</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1503</t>
+  </si>
+  <si>
+    <t>https://github.com/mostafaalagamy/Metrolist/pull/327</t>
+  </si>
+  <si>
+    <t>2.0k</t>
+  </si>
+  <si>
+    <t>https://github.com/breezy-weather/breezy-weather/pull/938</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/14894</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/pull/9225</t>
+  </si>
+  <si>
+    <t>2？</t>
+  </si>
+  <si>
+    <t>12.3k</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/17204</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9711</t>
+  </si>
+  <si>
+    <t>3.1k</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1525</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/16549</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/7999</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7252</t>
+  </si>
+  <si>
+    <t>27.3k</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/4242</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/18022</t>
+  </si>
+  <si>
+    <t>https://github.com/kirmanak/Mealient/pull/20</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1573</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7614</t>
+  </si>
+  <si>
+    <t>https://github.com/mozilla-mobile/firefox-android/pull/6077</t>
+  </si>
+  <si>
+    <t>1.8k</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7644</t>
+  </si>
+  <si>
+    <t>https://github.com/grote/Transportr/issues/491</t>
+  </si>
+  <si>
+    <t>1.1k</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1611</t>
+  </si>
+  <si>
+    <t>https://github.com/OneBusAway/onebusaway-android/pull/1117</t>
+  </si>
+  <si>
+    <t>https://github.com/kickstarter/android-oss/pull/2017</t>
+  </si>
+  <si>
+    <t>5.8k</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/pull/7876</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/17165</t>
+  </si>
+  <si>
+    <t>1?</t>
+  </si>
+  <si>
+    <t>https://github.com/TUM-Dev/Campus-Android/pull/1496</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1707</t>
+  </si>
+  <si>
+    <t>https://github.com/GetStream/stream-chat-android/pull/2716</t>
+  </si>
+  <si>
+    <t>1.6k</t>
+  </si>
   <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/17743</t>
   </si>
   <si>
-    <t>numT1.1</t>
-  </si>
-  <si>
-    <t>39+90 = 129</t>
-  </si>
-  <si>
-    <t>9.8k</t>
+    <t>https://github.com/Automattic/pocket-casts-android/pull/3698</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1559</t>
+  </si>
+  <si>
+    <t>https://github.com/MixinNetwork/android-app/pull/5165</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7705</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/16648</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7821</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1702</t>
+  </si>
+  <si>
+    <t>https://github.com/woocommerce/woocommerce-android/pull/13486</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/13235</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/8266</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/10727</t>
+  </si>
+  <si>
+    <t>https://github.com/oppia/oppia-android/pull/5116</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/14879</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/17932</t>
+  </si>
+  <si>
+    <t>https://github.com/Automattic/pocket-casts-android/pull/3460</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/17146</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1705</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/13844</t>
+  </si>
+  <si>
+    <t>https://github.com/HabitRPG/habitica-android/issues/2104</t>
+  </si>
+  <si>
+    <t>https://github.com/Sharingang/Sharingang-Android/pull/252</t>
+  </si>
+  <si>
+    <t>6.2k</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/pull/6723</t>
+  </si>
+  <si>
+    <t>https://github.com/libre-tube/LibreTube/pull/4043</t>
+  </si>
+  <si>
+    <t>10.2k</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/pull/6489</t>
+  </si>
+  <si>
+    <t>https://github.com/SimpleMobileTools/Simple-Commons/pull/1787</t>
+  </si>
+  <si>
+    <t>https://github.com/rozPierog/Cofi/pull/21</t>
+  </si>
+  <si>
+    <t>https://github.com/OneBusAway/onebusaway-android/pull/1178</t>
+  </si>
+  <si>
+    <t>https://github.com/Infomaniak/android-kDrive/pull/1507</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/20561</t>
+  </si>
+  <si>
+    <t>https://github.com/element-hq/element-android/pull/7015/files</t>
+  </si>
+  <si>
+    <t>3.5k</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/532</t>
+  </si>
+  <si>
+    <t>https://github.com/commons-app/apps-android-commons/issues/2573</t>
+  </si>
+  <si>
+    <t>https://github.com/Infomaniak/android-kMail/pull/1938</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1847</t>
+  </si>
+  <si>
+    <t>https://github.com/Visual-Code-Space/Visual-Code-Space/pull/130</t>
+  </si>
+  <si>
+    <t>https://github.com/Etar-Group/Etar-Calendar/issues/489</t>
+  </si>
+  <si>
+    <t>2.3k</t>
+  </si>
+  <si>
+    <t>https://github.com/openmrs/openmrs-contrib-android-client/pull/620</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/16812</t>
+  </si>
+  <si>
+    <t>https://github.com/libre-tube/LibreTube/pull/5761#discussioncomment-8787935</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1412</t>
+  </si>
+  <si>
+    <t>https://github.com/bitwarden/android/pull/4065</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/11659</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/11479</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1607</t>
+  </si>
+  <si>
+    <t>https://github.com/oppia/oppia-android/pull/5144</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/424</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/8758</t>
+  </si>
+  <si>
+    <t>https://github.com/home-assistant/android/pull/1043</t>
+  </si>
+  <si>
+    <t>2.9k</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/14805</t>
+  </si>
+  <si>
+    <t>https://github.com/home-assistant/android/pull/1994</t>
+  </si>
+  <si>
+    <t>https://github.com/element-hq/element-android/pull/5456</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/pull/7872</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/14208</t>
+  </si>
+  <si>
+    <t>https://github.com/kickstarter/android-oss/pull/603</t>
+  </si>
+  <si>
+    <t>https://github.com/breezy-weather/breezy-weather/pull/981</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1748</t>
+  </si>
+  <si>
+    <t>https://github.com/commons-app/apps-android-commons/issues/2107</t>
+  </si>
+  <si>
+    <t>https://github.com/JetBrains/jewel/pull/262</t>
+  </si>
+  <si>
+    <t>https://github.com/whitescent/Mastify/pull/33</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/17863</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/8253</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9761</t>
+  </si>
+  <si>
+    <t>https://github.com/oppia/oppia-android/pull/4616/files</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/16775</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/issues/10923</t>
+  </si>
+  <si>
+    <t>https://github.com/wireapp/wire-android/pull/1777</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/pull/1789</t>
+  </si>
+  <si>
+    <t>https://github.com/Automattic/pocket-casts-android/pull/2432</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/20482</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/issues/2065</t>
+  </si>
+  <si>
+    <t>https://github.com/shosetsuorg/shosetsu/pull/169</t>
   </si>
   <si>
     <t>https://github.com/HedvigInsurance/android/pull/2464</t>
   </si>
   <si>
-    <t>numT1.2</t>
-  </si>
-  <si>
-    <t>14+90 = 104</t>
-  </si>
-  <si>
-    <t>202-34-18=150</t>
+    <t>https://github.com/kiwix/kiwix-android/issues/472</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/pull/3456</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/issues/1930</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1907</t>
+  </si>
+  <si>
+    <t>https://github.com/vitorpamplona/amethyst/pull/90</t>
+  </si>
+  <si>
+    <t>1.3k</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/5759</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/13737</t>
+  </si>
+  <si>
+    <t>https://github.com/osfans/trime/pull/1193</t>
+  </si>
+  <si>
+    <t>3.6k</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/8995</t>
+  </si>
+  <si>
+    <t>https://github.com/whitescent/Mastify/pull/39</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/5128</t>
+  </si>
+  <si>
+    <t>https://github.com/tuskyapp/Tusky/pull/1286</t>
+  </si>
+  <si>
+    <t>https://github.com/thunderbird/thunderbird-android/pull/5865</t>
+  </si>
+  <si>
+    <t>https://github.com/mozilla-mobile/firefox-android/pull/1868</t>
+  </si>
+  <si>
+    <t>https://github.com/commons-app/apps-android-commons/issues/1948</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/1740</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/13123</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/9054</t>
+  </si>
+  <si>
+    <t>https://github.com/hannibal002/SkyHanni/pull/2257</t>
+  </si>
+  <si>
+    <t>https://github.com/home-assistant/android/pull/749</t>
+  </si>
+  <si>
+    <t>https://github.com/droidconKE/droidconKeKotlin/pull/205</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/16568</t>
+  </si>
+  <si>
+    <t>https://github.com/home-assistant/android/pull/2988</t>
+  </si>
+  <si>
+    <t>https://github.com/nightscout/AndroidAPS/pull/351</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/15014</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1531</t>
+  </si>
+  <si>
+    <t>https://github.com/PhilKes/NotallyX/pull/349</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1792</t>
+  </si>
+  <si>
+    <t>https://github.com/woocommerce/woocommerce-android/pull/4678</t>
+  </si>
+  <si>
+    <t>https://github.com/breezy-weather/breezy-weather/pull/713</t>
+  </si>
+  <si>
+    <t>https://github.com/yeriomin/YalpStore/issues/372</t>
+  </si>
+  <si>
+    <t>2.5k</t>
+  </si>
+  <si>
+    <t>https://github.com/woocommerce/woocommerce-android/issues/2313</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/17086</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/6807/files</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/12971</t>
+  </si>
+  <si>
+    <t>https://github.com/iTaysonLab/jetisteam/pull/2</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/8168</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9546</t>
+  </si>
+  <si>
+    <t>https://github.com/microsoft/fluentui-android/pull/539</t>
+  </si>
+  <si>
+    <t>https://github.com/openhab/openhab-android/pull/3227</t>
+  </si>
+  <si>
+    <t>https://github.com/kylecorry31/Trail-Sense/pull/947</t>
+  </si>
+  <si>
+    <t>2k</t>
+  </si>
+  <si>
+    <t>https://github.com/Decathlon/vitamin-compose/pull/39</t>
+  </si>
+  <si>
+    <t>https://github.com/woocommerce/woocommerce-android/pull/8844</t>
+  </si>
+  <si>
+    <t>https://github.com/kickstarter/android-oss/pull/1054</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/19771</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/13961</t>
+  </si>
+  <si>
+    <t>https://github.com/oppia/oppia-android/pull/4617</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/5417</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1301</t>
+  </si>
+  <si>
+    <t>https://github.com/woocommerce/woocommerce-android/pull/13316</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7578</t>
+  </si>
+  <si>
+    <t>https://github.com/woocommerce/woocommerce-android/pull/7188/files</t>
+  </si>
+  <si>
+    <t>https://github.com/wikimedia/apps-android-wikipedia/pull/4442</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/5387</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/15151</t>
+  </si>
+  <si>
+    <t>https://github.com/AnySoftKeyboard/AnySoftKeyboard/issues/858</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/13467</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/pull/542</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/618</t>
+  </si>
+  <si>
+    <t>https://github.com/simondankelmann/Bluetooth-LE-Spam/pull/356</t>
+  </si>
+  <si>
+    <t>4.4k</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/15842</t>
+  </si>
+  <si>
+    <t>https://github.com/laurent22/joplin/issues/2695</t>
+  </si>
+  <si>
+    <t>50.4k</t>
+  </si>
+  <si>
+    <t>https://github.com/commons-app/apps-android-commons/pull/6120</t>
+  </si>
+  <si>
+    <t>https://github.com/openMF/mobile-wallet/pull/1515</t>
+  </si>
+  <si>
+    <t>https://github.com/SagerNet/sing-box-for-android/pull/25/files</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/552</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/18098</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/1047</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/17286</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/11687</t>
+  </si>
+  <si>
+    <t>https://github.com/Automattic/pocket-casts-android/pull/215/files</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/630</t>
+  </si>
+  <si>
+    <t>https://github.com/element-hq/element-android/pull/7436</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/15333</t>
+  </si>
+  <si>
+    <t>https://github.com/ankidroid/Anki-Android/pull/17985</t>
+  </si>
+  <si>
+    <t>https://github.com/jkuester/unlauncher/pull/195</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/18145</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7036</t>
+  </si>
+  <si>
+    <t>https://github.com/mozilla-mobile/firefox-android/pull/3826</t>
+  </si>
+  <si>
+    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/14849</t>
+  </si>
+  <si>
+    <t>https://github.com/ehsannarmani/ComposeCharts/pull/73</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/issues/425</t>
+  </si>
+  <si>
+    <t>https://github.com/openMF/android-client/pull/1957</t>
+  </si>
+  <si>
+    <t>https://github.com/kiwix/kiwix-android/pull/1975</t>
+  </si>
+  <si>
+    <t>https://github.com/Automattic/pocket-casts-android/pull/3154</t>
+  </si>
+  <si>
+    <t>https://github.com/dinbtechit/vscode-theme/pull/68</t>
+  </si>
+  <si>
+    <t>https://github.com/signalapp/Signal-Android/issues/7024</t>
+  </si>
+  <si>
+    <t>https://github.com/woocommerce/woocommerce-android/issues/2384</t>
+  </si>
+  <si>
+    <t>https://github.com/kylecorry31/Trail-Sense/pull/948</t>
   </si>
   <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/17672</t>
   </si>
   <si>
-    <t>num2</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/16775</t>
-  </si>
-  <si>
-    <t>1.1+1.2</t>
-  </si>
-  <si>
-    <t>num3</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/17165</t>
-  </si>
-  <si>
-    <t>1?</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/16568</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/16549</t>
-  </si>
-  <si>
     <t>https://github.com/Catappult/appcoins-wallet-android/pull/1207</t>
   </si>
   <si>
-    <t>https://github.com/ehsannarmani/ComposeCharts/pull/73</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/14879</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/17985</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/18022</t>
-  </si>
-  <si>
-    <t>https://github.com/woocommerce/woocommerce-android/pull/13486</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/15333</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/17932</t>
-  </si>
-  <si>
-    <t>https://github.com/mostafaalagamy/Metrolist/pull/327</t>
-  </si>
-  <si>
-    <t>2.0k</t>
-  </si>
-  <si>
-    <t>https://github.com/tuskyapp/Tusky/pull/1286</t>
-  </si>
-  <si>
-    <t>2.6k</t>
-  </si>
-  <si>
-    <t>https://github.com/simondankelmann/Bluetooth-LE-Spam/pull/356</t>
-  </si>
-  <si>
-    <t>4.4k</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/15842</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/15683</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/14894</t>
-  </si>
-  <si>
-    <t>https://github.com/Automattic/pocket-casts-android/pull/3698</t>
-  </si>
-  <si>
-    <t>2.7k</t>
-  </si>
-  <si>
     <t>https://github.com/ankidroid/Anki-Android/pull/17724</t>
   </si>
   <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/17204</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/13844</t>
-  </si>
-  <si>
-    <t>https://github.com/HabitRPG/habitica-android/issues/2104</t>
-  </si>
-  <si>
-    <t>1.6k</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/14041</t>
-  </si>
-  <si>
-    <t>https://github.com/tuskyapp/Tusky/pull/4864</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/14805</t>
-  </si>
-  <si>
-    <t>https://github.com/Infomaniak/android-kDrive/pull/1507</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/13737</t>
-  </si>
-  <si>
-    <t>https://github.com/MixinNetwork/android-app/pull/5165</t>
-  </si>
-  <si>
-    <t>https://github.com/Automattic/pocket-casts-android/pull/3154</t>
-  </si>
-  <si>
-    <t>https://github.com/PhilKes/NotallyX/pull/349</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/15014</t>
-  </si>
-  <si>
-    <t>https://github.com/woocommerce/woocommerce-android/pull/13316</t>
-  </si>
-  <si>
-    <t>https://github.com/commons-app/apps-android-commons/pull/6120</t>
-  </si>
-  <si>
-    <t>1.1k</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/13123</t>
-  </si>
-  <si>
-    <t>https://github.com/Automattic/pocket-casts-android/pull/3460</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/10727</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/11479</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/16648</t>
-  </si>
-  <si>
-    <t>https://github.com/hannibal002/SkyHanni/pull/2257</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/8168</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/13235</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/17146</t>
-  </si>
-  <si>
-    <t>https://github.com/Visual-Code-Space/Visual-Code-Space/pull/130</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/11687</t>
-  </si>
-  <si>
-    <t>https://github.com/bitwarden/android/pull/4065</t>
-  </si>
-  <si>
-    <t>7.6k</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/6807/files</t>
-  </si>
-  <si>
     <t>https://github.com/DroidKaigi/conference-app-2024/pull/640</t>
   </si>
   <si>
-    <t>https://github.com/Automattic/pocket-casts-android/pull/2432</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/5128</t>
-  </si>
-  <si>
-    <t>https://github.com/breezy-weather/breezy-weather/pull/938</t>
-  </si>
-  <si>
-    <t>cite</t>
-  </si>
-  <si>
-    <t>https://github.com/breezy-weather/breezy-weather/pull/931</t>
-  </si>
-  <si>
-    <t>https://github.com/kickstarter/android-oss/pull/1054</t>
-  </si>
-  <si>
-    <t>5.8k</t>
-  </si>
-  <si>
-    <t>https://github.com/kickstarter/android-oss/pull/603</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9761</t>
-  </si>
-  <si>
-    <t>3.1k</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/19771</t>
-  </si>
-  <si>
-    <t>https://github.com/breezy-weather/breezy-weather/pull/981</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/17086</t>
-  </si>
-  <si>
-    <t>https://github.com/Infomaniak/android-kMail/pull/1938</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/14849</t>
-  </si>
-  <si>
-    <t>https://github.com/kickstarter/android-oss/pull/2017</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/13467</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/issues/10923</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/pull/7872</t>
-  </si>
-  <si>
-    <t>12.3k</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/4242</t>
-  </si>
-  <si>
-    <t>1？</t>
-  </si>
-  <si>
-    <t>https://github.com/SagerNet/sing-box-for-android/pull/25/files</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/20561</t>
-  </si>
-  <si>
-    <t>https://github.com/libre-tube/LibreTube/pull/5761#discussioncomment-8787935</t>
-  </si>
-  <si>
-    <t>10.2k</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9711</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/9546</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/20482</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/14208</t>
-  </si>
-  <si>
-    <t>https://github.com/whitescent/Mastify/pull/39</t>
-  </si>
-  <si>
-    <t>6.2k</t>
-  </si>
-  <si>
-    <t>https://github.com/wikimedia/apps-android-wikipedia/pull/4442</t>
-  </si>
-  <si>
-    <t>https://github.com/mozilla-mobile/firefox-android/pull/6077</t>
-  </si>
-  <si>
-    <t>1.8k</t>
-  </si>
-  <si>
-    <t>https://github.com/whitescent/Mastify/pull/33</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/pull/3823</t>
-  </si>
-  <si>
-    <t>1k</t>
-  </si>
-  <si>
-    <t>https://github.com/breezy-weather/breezy-weather/pull/713</t>
-  </si>
-  <si>
-    <t>https://github.com/openMF/mobile-wallet/pull/1515</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/7999</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/15151</t>
-  </si>
-  <si>
-    <t>https://github.com/microsoft/fluentui-android/pull/539</t>
-  </si>
-  <si>
-    <t>https://github.com/wikimedia/apps-android-wikipedia/pull/573</t>
-  </si>
-  <si>
-    <t>https://github.com/jkuester/unlauncher/pull/195</t>
-  </si>
-  <si>
-    <t>https://github.com/osfans/trime/pull/1193</t>
-  </si>
-  <si>
-    <t>3.6k</t>
-  </si>
-  <si>
-    <t>https://github.com/mozilla-mobile/firefox-android/pull/3826</t>
-  </si>
-  <si>
-    <t>https://github.com/SimpleMobileTools/Simple-Commons/pull/1787</t>
-  </si>
-  <si>
-    <t>https://github.com/mozilla-mobile/firefox-android/pull/1868</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/pull/7876</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/pull/6723</t>
-  </si>
-  <si>
-    <t>https://github.com/oppia/oppia-android/pull/5116</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/pull/5865</t>
-  </si>
-  <si>
-    <t>https://github.com/ismartcoding/plain-app/pull/82</t>
-  </si>
-  <si>
-    <t>3k</t>
-  </si>
-  <si>
-    <t>https://github.com/oppia/oppia-android/pull/5144</t>
-  </si>
-  <si>
-    <t>https://github.com/dinbtechit/vscode-theme/pull/68</t>
-  </si>
-  <si>
-    <t>https://github.com/openMF/android-client/pull/1957</t>
-  </si>
-  <si>
-    <t>https://github.com/libre-tube/LibreTube/pull/4043</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/18098</t>
-  </si>
-  <si>
-    <t>https://github.com/openhab/openhab-android/pull/3227</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/18145</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/pull/3456</t>
-  </si>
-  <si>
-    <t>https://github.com/woocommerce/woocommerce-android/pull/8844</t>
-  </si>
-  <si>
-    <t>https://github.com/vitorpamplona/amethyst/pull/90</t>
-  </si>
-  <si>
-    <t>1.3k</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/17863</t>
-  </si>
-  <si>
-    <t>https://github.com/wireapp/wire-android/pull/1777</t>
-  </si>
-  <si>
-    <t>https://github.com/home-assistant/android/pull/2988</t>
-  </si>
-  <si>
-    <t>2.9k</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/16812</t>
-  </si>
-  <si>
-    <t>https://github.com/TUM-Dev/Campus-Android/pull/1496</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/12971</t>
-  </si>
-  <si>
-    <t>https://github.com/home-assistant/android/pull/1994</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/pull/6489</t>
-  </si>
-  <si>
-    <t>https://github.com/iTaysonLab/jetisteam/pull/2</t>
-  </si>
-  <si>
-    <t>https://github.com/home-assistant/android/pull/1043</t>
-  </si>
-  <si>
-    <t>https://github.com/Automattic/pocket-casts-android/pull/432</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1847</t>
-  </si>
-  <si>
-    <t>https://github.com/Automattic/pocket-casts-android/pull/215/files</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/5417</t>
-  </si>
-  <si>
-    <t>https://github.com/wordpress-mobile/WordPress-Android/pull/17286</t>
-  </si>
-  <si>
-    <t>https://github.com/oppia/oppia-android/pull/4617</t>
-  </si>
-  <si>
-    <t>https://github.com/oppia/oppia-android/pull/4616/files</t>
-  </si>
-  <si>
-    <t>https://github.com/element-hq/element-android/pull/7015/files</t>
-  </si>
-  <si>
-    <t>3.5k</t>
-  </si>
-  <si>
-    <t>https://github.com/woocommerce/woocommerce-android/pull/7188/files</t>
-  </si>
-  <si>
-    <t>https://github.com/Decathlon/vitamin-compose/pull/39</t>
-  </si>
-  <si>
-    <t>https://github.com/home-assistant/android/pull/749</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/11659</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1907</t>
-  </si>
-  <si>
-    <t>https://github.com/element-hq/element-android/pull/7436</t>
-  </si>
-  <si>
-    <t>https://github.com/element-hq/element-android/pull/5456</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1705</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1740</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1525</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1559</t>
-  </si>
-  <si>
-    <t>https://github.com/GetStream/stream-chat-android/pull/2716</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1503</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1412</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1607</t>
-  </si>
-  <si>
-    <t>https://github.com/kirmanak/Mealient/pull/20</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/1611</t>
-  </si>
-  <si>
-    <t>https://github.com/shosetsuorg/shosetsu/pull/169</t>
-  </si>
-  <si>
-    <t>https://github.com/rozPierog/Cofi/pull/21</t>
-  </si>
-  <si>
-    <t>https://github.com/nightscout/AndroidAPS/pull/351</t>
-  </si>
-  <si>
-    <t>https://github.com/kylecorry31/Trail-Sense/pull/947</t>
-  </si>
-  <si>
-    <t>2k</t>
-  </si>
-  <si>
-    <t>https://github.com/kylecorry31/Trail-Sense/pull/948</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/pull/1975</t>
-  </si>
-  <si>
-    <t>https://github.com/OneBusAway/onebusaway-android/pull/1178</t>
-  </si>
-  <si>
-    <t>https://github.com/OneBusAway/onebusaway-android/pull/1117</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/pull/1789</t>
-  </si>
-  <si>
-    <t>https://github.com/woocommerce/woocommerce-android/pull/4678</t>
-  </si>
-  <si>
-    <t>https://github.com/Sharingang/Sharingang-Android/pull/252</t>
-  </si>
-  <si>
-    <t>https://github.com/droidconKE/droidconKeKotlin/pull/205</t>
-  </si>
-  <si>
-    <t>https://github.com/JetBrains/jewel/pull/262</t>
-  </si>
-  <si>
-    <t>https://github.com/ankidroid/Anki-Android/pull/13961</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/pull/9225</t>
-  </si>
-  <si>
-    <t>2？</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7252</t>
-  </si>
-  <si>
-    <t>27.3k</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7578</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1301</t>
-  </si>
-  <si>
-    <t>https://github.com/AnySoftKeyboard/AnySoftKeyboard/issues/858</t>
-  </si>
-  <si>
-    <t>https://github.com/commons-app/apps-android-commons/issues/1948</t>
-  </si>
-  <si>
-    <t>https://github.com/commons-app/apps-android-commons/issues/2107</t>
-  </si>
-  <si>
-    <t>https://github.com/commons-app/apps-android-commons/issues/2573</t>
-  </si>
-  <si>
-    <t>xml:90</t>
-  </si>
-  <si>
-    <t>https://github.com/Etar-Group/Etar-Calendar/issues/489</t>
-  </si>
-  <si>
-    <t>kt:58</t>
-  </si>
-  <si>
-    <t>2.3k</t>
-  </si>
-  <si>
-    <t>https://github.com/grote/Transportr/issues/491</t>
-  </si>
-  <si>
-    <t>sum:54</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/issues/1930</t>
-  </si>
-  <si>
-    <t>https://github.com/thunderbird/thunderbird-android/issues/2065</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1047</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1531</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1573</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1702</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1707</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1748</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/1792</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/424</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/425</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/472</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/532</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/552</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/618</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/pull/542</t>
-  </si>
-  <si>
-    <t>https://github.com/laurent22/joplin/issues/2695</t>
-  </si>
-  <si>
-    <t>50.4k</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-contrib-android-client/pull/620</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/5387</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/5759</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7024</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7036</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7614</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7644</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7705</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/7821</t>
-  </si>
-  <si>
     <t>https://github.com/signalapp/Signal-Android/issues/8151</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/8253</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/8266</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/8758</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/8995</t>
-  </si>
-  <si>
-    <t>https://github.com/signalapp/Signal-Android/issues/9054</t>
-  </si>
-  <si>
-    <t>https://github.com/woocommerce/woocommerce-android/issues/2313</t>
-  </si>
-  <si>
-    <t>https://github.com/woocommerce/woocommerce-android/issues/2384</t>
-  </si>
-  <si>
-    <t>https://github.com/yeriomin/YalpStore/issues/372</t>
-  </si>
-  <si>
-    <t>2.5k</t>
-  </si>
-  <si>
-    <t>https://github.com/kiwix/kiwix-android/issues/630</t>
   </si>
 </sst>
 </file>
@@ -1704,126 +1671,99 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
-        <v>2</v>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
       <c r="C1">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
       <c r="J1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1">
+        <v>382040</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2">
         <v>273644</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>1.2</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="4">
-        <v>138</v>
-      </c>
-      <c r="K2">
-        <v>141724</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>273644</v>
+        <v>146939</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>306479</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4">
-        <v>18</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>273644</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>273644</v>
+        <v>143120</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>1.2</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>273644</v>
@@ -1831,139 +1771,135 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K7">
-        <v>273644</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4">
-        <v>159</v>
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="K8">
-        <v>320962</v>
+        <v>168638</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4">
-        <v>654</v>
+        <v>836</v>
       </c>
       <c r="K9">
-        <v>6932</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>1.2</v>
       </c>
       <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
-        <f>COUNTIF(B:B,2)</f>
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K10">
-        <v>273644</v>
+        <v>80752</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>273644</v>
+        <v>146939</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>273644</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
       <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="J13" s="4">
-        <v>294</v>
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="K13">
-        <v>715765</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>1.2</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <v>273644</v>
@@ -1971,53 +1907,53 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K15">
-        <v>273644</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
+      <c r="A16" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>26</v>
+      <c r="J16" s="4">
+        <v>836</v>
       </c>
       <c r="K16">
-        <v>80752</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17">
-        <v>1.2</v>
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>168638</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2028,44 +1964,44 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18">
+        <v>750760</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K18">
-        <v>9951</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="K19">
-        <v>273644</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B20">
-        <v>1.2</v>
+      <c r="B20" t="s">
+        <v>8</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>273644</v>
@@ -2076,13 +2012,13 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <v>273644</v>
@@ -2093,101 +2029,101 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="J22" s="4">
+        <v>160</v>
       </c>
       <c r="K22">
-        <v>382040</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K23">
-        <v>273644</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K24">
-        <v>273644</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="K25">
-        <v>273644</v>
+        <v>900774</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B26">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K26">
-        <v>152797</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27">
+        <v>1.1</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="K27">
-        <v>273644</v>
+        <v>40036</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2195,234 +2131,234 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>28</v>
+        <v>1</v>
+      </c>
+      <c r="J28" s="4">
+        <v>836</v>
       </c>
       <c r="K28">
-        <v>168638</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B29">
-        <v>3</v>
+      <c r="B29" t="s">
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>516</v>
       </c>
       <c r="K29">
-        <v>273644</v>
+        <v>119284</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B30">
-        <v>2</v>
+      <c r="B30" t="s">
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="J30" s="4">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K30">
-        <v>164048</v>
+        <v>184252</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31">
-        <v>1.2</v>
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K31">
+        <v>303600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32">
         <v>273644</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="J32" s="4">
-        <v>477</v>
-      </c>
-      <c r="K32">
-        <v>428009</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33">
-        <v>3</v>
+        <v>49</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>35</v>
+      <c r="J33" s="4">
+        <v>208</v>
       </c>
       <c r="K33">
-        <v>382040</v>
+        <v>47602</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="J34" s="4">
-        <v>320</v>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="K34">
-        <v>326855</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" t="s">
-        <v>11</v>
+      <c r="A35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="K35">
-        <v>273644</v>
+        <v>342821</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" t="s">
-        <v>11</v>
+        <v>53</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="J36" s="4">
-        <v>294</v>
+        <v>2</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K36">
-        <v>715765</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>145271</v>
+        <v>382040</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="J38" s="4">
+        <v>836</v>
       </c>
       <c r="K38">
-        <v>273644</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="J39" s="4">
+        <v>477</v>
       </c>
       <c r="K39">
-        <v>382040</v>
+        <v>428009</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" t="s">
-        <v>11</v>
+        <v>57</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K40">
-        <v>273644</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41">
         <v>273644</v>
@@ -2430,67 +2366,67 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K42">
-        <v>273644</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43">
-        <v>1.2</v>
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="J43" s="4">
-        <v>437</v>
+        <v>1</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="K43">
-        <v>181814</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="J44" s="4">
+        <v>294</v>
       </c>
       <c r="K44">
-        <v>273644</v>
+        <v>715765</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45">
         <v>273644</v>
@@ -2498,158 +2434,156 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K46">
-        <v>273644</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="J47" s="4">
-        <v>416</v>
+        <v>2</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>108107</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" t="s">
-        <v>11</v>
+        <v>65</v>
+      </c>
+      <c r="B48">
+        <v>1.1</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>3</v>
+      <c r="J48" s="4">
+        <v>351</v>
       </c>
       <c r="K48">
-        <v>273644</v>
+        <v>417757</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49" t="s">
-        <v>11</v>
+        <v>66</v>
+      </c>
+      <c r="B49">
+        <v>1.2</v>
       </c>
       <c r="C49">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E49" s="3"/>
       <c r="J49" s="4" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>361663</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="2" t="s">
-        <v>66</v>
+      <c r="A50" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50">
         <v>273644</v>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B51">
-        <v>2</v>
+      <c r="A51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
       </c>
       <c r="C51">
         <v>2</v>
       </c>
-      <c r="J51" s="4">
-        <v>491</v>
+      <c r="J51" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>42193</v>
+        <v>382040</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="K52">
-        <v>382040</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>2</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J53" s="4">
+        <v>836</v>
       </c>
       <c r="K53">
+        <v>543830</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54">
         <v>273644</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B54">
-        <v>3</v>
-      </c>
-      <c r="C54">
-        <v>2</v>
-      </c>
-      <c r="E54" t="s">
-        <v>71</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K54">
-        <v>146939</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2657,16 +2591,16 @@
         <v>72</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="C55">
         <v>2</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="K55">
-        <v>146939</v>
+        <v>152797</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2674,7 +2608,7 @@
         <v>73</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2683,32 +2617,32 @@
         <v>74</v>
       </c>
       <c r="K56">
-        <v>184252</v>
+        <v>371029</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B57" t="s">
-        <v>11</v>
+      <c r="B57">
+        <v>1.1</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="K57">
-        <v>184252</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B58">
-        <v>1.1</v>
+      <c r="B58" t="s">
+        <v>1</v>
       </c>
       <c r="C58">
         <v>3</v>
@@ -2717,7 +2651,7 @@
         <v>77</v>
       </c>
       <c r="K58">
-        <v>750760</v>
+        <v>88762</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2728,51 +2662,51 @@
         <v>1.1</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="K59">
-        <v>750760</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B60" t="s">
-        <v>11</v>
+      <c r="B60">
+        <v>1.1</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
-      <c r="J60" s="4" t="s">
-        <v>65</v>
+      <c r="J60" s="4">
+        <v>363</v>
       </c>
       <c r="K60">
-        <v>146939</v>
+        <v>92101</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B61" t="s">
-        <v>11</v>
+      <c r="B61">
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>2</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="J61" s="4">
+        <v>405</v>
       </c>
       <c r="K61">
-        <v>750760</v>
+        <v>19396</v>
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B62">
@@ -2782,30 +2716,27 @@
         <v>1</v>
       </c>
       <c r="J62" s="4">
-        <v>155</v>
+        <v>516</v>
       </c>
       <c r="K62">
-        <v>63107</v>
+        <v>119284</v>
       </c>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>71</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>77</v>
+        <v>2</v>
+      </c>
+      <c r="J63" s="4">
+        <v>132</v>
       </c>
       <c r="K63">
-        <v>750760</v>
+        <v>164048</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -2813,89 +2744,90 @@
         <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="K64">
-        <v>184252</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B65" t="s">
-        <v>11</v>
+      <c r="B65">
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K65">
-        <v>750760</v>
+        <v>446442</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B66" t="s">
-        <v>11</v>
+        <v>86</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="K66">
-        <v>750760</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B67">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G67" s="5"/>
       <c r="J67" s="4" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="K67">
-        <v>303600</v>
+        <v>145271</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B68" t="s">
-        <v>89</v>
+      <c r="B68">
+        <v>1.1</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
-      <c r="J68" s="4" t="s">
-        <v>3</v>
+      <c r="J68" s="4">
+        <v>155</v>
       </c>
       <c r="K68">
-        <v>273644</v>
+        <v>63107</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B69">
         <v>1.1</v>
@@ -2904,32 +2836,32 @@
         <v>1</v>
       </c>
       <c r="J69" s="4">
-        <v>717</v>
+        <v>836</v>
       </c>
       <c r="K69">
-        <v>10514</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
-      <c r="J70" s="4" t="s">
-        <v>77</v>
+      <c r="J70" s="4">
+        <v>416</v>
       </c>
       <c r="K70">
-        <v>750760</v>
+        <v>108107</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B71">
         <v>1.1</v>
@@ -2938,41 +2870,41 @@
         <v>1</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K71">
-        <v>88762</v>
+        <v>90748</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B72" t="s">
-        <v>11</v>
+        <v>93</v>
+      </c>
+      <c r="B72">
+        <v>1.1</v>
       </c>
       <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>77</v>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4">
+        <v>181</v>
       </c>
       <c r="K72">
-        <v>750760</v>
+        <v>39197</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B73">
-        <v>3</v>
+        <v>94</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="K73">
         <v>750760</v>
@@ -2980,10 +2912,10 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" t="s">
-        <v>11</v>
+        <v>95</v>
+      </c>
+      <c r="B74">
+        <v>1.1</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -2992,80 +2924,80 @@
         <v>77</v>
       </c>
       <c r="K74">
-        <v>750760</v>
+        <v>88762</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75" t="s">
-        <v>11</v>
+        <v>96</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="J75" s="4">
+        <v>836</v>
       </c>
       <c r="K75">
-        <v>273644</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="K76">
-        <v>371029</v>
+        <v>361663</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77">
-        <v>1.1</v>
+        <v>98</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>306479</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
+        <v>99</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>900774</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B79">
         <v>1.1</v>
@@ -3073,93 +3005,93 @@
       <c r="C79">
         <v>3</v>
       </c>
-      <c r="J79" s="4" t="s">
-        <v>99</v>
+      <c r="J79" s="4">
+        <v>836</v>
       </c>
       <c r="K79">
-        <v>371029</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>105</v>
+      <c r="J80" s="4">
+        <v>351</v>
       </c>
       <c r="K80">
-        <v>79258</v>
+        <v>417757</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B81">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="K81">
-        <v>146939</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B82" t="s">
-        <v>11</v>
+        <v>103</v>
+      </c>
+      <c r="B82">
+        <v>1.1</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
-      <c r="J82" s="4">
-        <v>270</v>
+      <c r="J82" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K82">
-        <v>434997</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="K83">
-        <v>750760</v>
+        <v>110253</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B84">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K84">
         <v>273644</v>
@@ -3167,296 +3099,296 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
-      <c r="J85" s="4">
-        <v>632</v>
+      <c r="J85" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K85">
-        <v>126889</v>
+        <v>110253</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B86" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="K86">
-        <v>306479</v>
+        <v>446442</v>
       </c>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B87">
-        <v>1.1</v>
+      <c r="A87" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="J87" s="4">
-        <v>368</v>
+        <v>3</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="K87">
-        <v>11953</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B88">
-        <v>3</v>
+        <v>110</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="K88">
-        <v>33430</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B89">
-        <v>1.1</v>
+        <v>111</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="K89">
-        <v>900774</v>
+        <v>184252</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B90">
-        <v>1.1</v>
+        <v>112</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
-      <c r="J90" s="4">
-        <v>363</v>
+      <c r="J90" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K90">
-        <v>92101</v>
+        <v>146939</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B91" t="s">
-        <v>11</v>
+        <v>113</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="K91">
-        <v>900774</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="K92">
-        <v>303600</v>
+        <v>145271</v>
       </c>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="1" t="s">
-        <v>119</v>
+      <c r="A93" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B93">
         <v>1.1</v>
       </c>
       <c r="C93">
-        <v>3</v>
-      </c>
-      <c r="J93" s="4" t="s">
-        <v>87</v>
+        <v>2</v>
+      </c>
+      <c r="J93" s="4">
+        <v>851</v>
       </c>
       <c r="K93">
-        <v>303600</v>
+        <v>54894</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B94">
         <v>1.1</v>
       </c>
       <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="J94" s="4">
-        <v>351</v>
+        <v>3</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="K94">
-        <v>417757</v>
+        <v>371029</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="K95">
-        <v>303600</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B96" t="s">
-        <v>11</v>
+        <v>118</v>
+      </c>
+      <c r="B96">
+        <v>1.1</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="K96">
-        <v>143120</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B97" t="s">
-        <v>11</v>
+        <v>119</v>
+      </c>
+      <c r="B97">
+        <v>1.1</v>
       </c>
       <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="J97" s="4">
-        <v>351</v>
+        <v>3</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="K97">
-        <v>417757</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J98" s="4">
-        <v>988</v>
+        <v>351</v>
       </c>
       <c r="K98">
-        <v>9347</v>
+        <v>417757</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B99">
-        <v>1.1</v>
+        <v>121</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
-      <c r="J99" s="4">
-        <v>212</v>
+      <c r="J99" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K99">
-        <v>89542</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="K100">
-        <v>88762</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B101">
-        <v>2</v>
+        <v>123</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
-      <c r="J101" s="4" t="s">
-        <v>77</v>
+      <c r="J101" s="4">
+        <v>181</v>
       </c>
       <c r="K101">
-        <v>750760</v>
+        <v>203060</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -3464,433 +3396,433 @@
       <c r="C102">
         <v>1</v>
       </c>
-      <c r="J102" s="4">
-        <v>628</v>
+      <c r="J102" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="K102">
-        <v>51513</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="103" spans="1:11">
-      <c r="A103" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B103">
-        <v>1.1</v>
+      <c r="A103" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="K103">
-        <v>750760</v>
+        <v>382040</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="K104">
-        <v>303600</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
-      </c>
-      <c r="J105" s="4">
-        <v>294</v>
+        <v>2</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="K105">
-        <v>715765</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B106">
-        <v>1.1</v>
+        <v>128</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
-      <c r="J106" s="4" t="s">
-        <v>134</v>
+      <c r="J106" s="4">
+        <v>593</v>
       </c>
       <c r="K106">
-        <v>212043</v>
+        <v>36366</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="C107">
-        <v>1</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>77</v>
+        <v>2</v>
+      </c>
+      <c r="J107" s="4">
+        <v>138</v>
       </c>
       <c r="K107">
-        <v>750760</v>
+        <v>141724</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B108" t="s">
-        <v>11</v>
+        <v>130</v>
+      </c>
+      <c r="B108">
+        <v>1.1</v>
       </c>
       <c r="C108">
-        <v>2</v>
-      </c>
-      <c r="J108" s="4">
-        <v>181</v>
+        <v>1</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="K108">
-        <v>203060</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B109">
-        <v>1.1</v>
+        <v>131</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1</v>
       </c>
       <c r="C109">
         <v>1</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="K109">
-        <v>110253</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="K110">
-        <v>750760</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B111" t="s">
-        <v>11</v>
+        <v>133</v>
+      </c>
+      <c r="B111">
+        <v>1.1</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
       <c r="J111" s="4">
-        <v>208</v>
+        <v>836</v>
       </c>
       <c r="K111">
-        <v>47602</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="K112">
-        <v>273644</v>
+        <v>212043</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="K113">
-        <v>110253</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B114">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="K114">
-        <v>303600</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B115">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
-      <c r="J115" s="4">
-        <v>110</v>
+      <c r="J115" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="K115">
-        <v>12918</v>
+        <v>33430</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B116">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="K116">
-        <v>110253</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="K117">
-        <v>382040</v>
+        <v>371029</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B118">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>1</v>
-      </c>
-      <c r="J118" s="4">
-        <v>836</v>
+        <v>2</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K118">
-        <v>543830</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K119">
-        <v>382040</v>
+        <v>168638</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B120" t="s">
-        <v>11</v>
+        <v>144</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K120">
-        <v>273644</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B121">
-        <v>3</v>
+        <v>145</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1</v>
       </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="K121">
-        <v>750760</v>
+        <v>900774</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B122">
-        <v>2</v>
+        <v>146</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1</v>
       </c>
       <c r="C122">
         <v>1</v>
       </c>
-      <c r="J122" s="4">
-        <v>351</v>
+      <c r="J122" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="K122">
-        <v>417757</v>
+        <v>145271</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B123">
-        <v>2</v>
+        <v>147</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="J123" s="4">
-        <v>351</v>
+        <v>836</v>
       </c>
       <c r="K123">
-        <v>417757</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B124">
-        <v>2</v>
+        <v>148</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="K124">
-        <v>446442</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B125">
-        <v>2</v>
+        <v>149</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>3</v>
-      </c>
-      <c r="J125" s="4">
-        <v>294</v>
+        <v>1</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K125">
-        <v>715765</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B126" t="s">
-        <v>11</v>
+        <v>150</v>
+      </c>
+      <c r="B126">
+        <v>1.2</v>
       </c>
       <c r="C126">
         <v>2</v>
       </c>
       <c r="J126" s="4">
-        <v>274</v>
+        <v>437</v>
       </c>
       <c r="K126">
-        <v>105449</v>
+        <v>181814</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B127" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C127">
         <v>3</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="K127">
         <v>110253</v>
@@ -3898,526 +3830,526 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B128" t="s">
-        <v>11</v>
+        <v>152</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>3</v>
-      </c>
-      <c r="J128" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="J128" s="4">
+        <v>110</v>
       </c>
       <c r="K128">
-        <v>273644</v>
+        <v>16185</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B129">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C129">
-        <v>1</v>
-      </c>
-      <c r="J129" s="4">
-        <v>836</v>
+        <v>2</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K129">
-        <v>543830</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="C130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="K130">
-        <v>446442</v>
+        <v>110253</v>
       </c>
     </row>
     <row r="131" spans="1:11">
-      <c r="A131" s="1" t="s">
-        <v>161</v>
+      <c r="A131" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C131">
         <v>3</v>
       </c>
-      <c r="J131" s="4" t="s">
-        <v>154</v>
+      <c r="J131" s="4">
+        <v>836</v>
       </c>
       <c r="K131">
-        <v>446442</v>
+        <v>543830</v>
       </c>
     </row>
     <row r="132" spans="1:11">
-      <c r="A132" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B132">
-        <v>2</v>
+      <c r="A132" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
-      <c r="J132" s="4">
-        <v>836</v>
+      <c r="J132" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K132">
-        <v>543830</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>1</v>
-      </c>
-      <c r="J133" s="4">
-        <v>836</v>
+        <v>3</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="K133">
-        <v>543830</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B134">
-        <v>1.1</v>
+        <v>158</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J134" s="4">
-        <v>836</v>
+        <v>320</v>
       </c>
       <c r="K134">
-        <v>543830</v>
+        <v>326855</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>3</v>
-      </c>
-      <c r="J135" s="4">
-        <v>836</v>
+        <v>1</v>
+      </c>
+      <c r="J135" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="K135">
-        <v>543830</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B136">
-        <v>3</v>
+        <v>160</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>2</v>
-      </c>
-      <c r="J136" s="4" t="s">
-        <v>40</v>
+        <v>1</v>
+      </c>
+      <c r="J136" s="4">
+        <v>294</v>
       </c>
       <c r="K136">
-        <v>342821</v>
+        <v>715765</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B137" t="s">
-        <v>11</v>
+        <v>161</v>
+      </c>
+      <c r="B137">
+        <v>1.1</v>
       </c>
       <c r="C137">
-        <v>3</v>
-      </c>
-      <c r="J137" s="4">
-        <v>836</v>
+        <v>2</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K137">
-        <v>543830</v>
+        <v>146939</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B138">
-        <v>3</v>
+        <v>162</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1</v>
       </c>
       <c r="C138">
         <v>3</v>
       </c>
-      <c r="J138" s="4">
-        <v>836</v>
+      <c r="J138" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="K138">
-        <v>543830</v>
+        <v>31584</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B139">
-        <v>1.1</v>
+        <v>164</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1</v>
       </c>
       <c r="C139">
         <v>3</v>
       </c>
       <c r="J139" s="4">
-        <v>836</v>
+        <v>294</v>
       </c>
       <c r="K139">
-        <v>543830</v>
+        <v>715765</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="J140" s="4">
-        <v>160</v>
+        <v>2</v>
+      </c>
+      <c r="J140" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="K140">
-        <v>15801</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="141" spans="1:11">
-      <c r="A141" s="1" t="s">
-        <v>171</v>
+      <c r="A141" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141">
-        <v>1</v>
-      </c>
-      <c r="J141" s="4">
-        <v>836</v>
+        <v>3</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K141">
-        <v>543830</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B142" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>2</v>
-      </c>
-      <c r="J142" s="4">
-        <v>593</v>
+        <v>1</v>
+      </c>
+      <c r="J142" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K142">
-        <v>36366</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B143">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J143" s="4">
-        <v>405</v>
+        <v>110</v>
       </c>
       <c r="K143">
-        <v>19396</v>
+        <v>12918</v>
       </c>
     </row>
     <row r="144" spans="1:11">
-      <c r="A144" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B144" t="s">
-        <v>11</v>
+      <c r="A144" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B144">
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>3</v>
-      </c>
-      <c r="J144" s="4">
-        <v>836</v>
+        <v>1</v>
+      </c>
+      <c r="J144" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K144">
-        <v>543830</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="145" spans="1:11">
-      <c r="A145" s="2" t="s">
-        <v>175</v>
+      <c r="A145" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="B145">
         <v>3</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="K145">
-        <v>154610</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="146" spans="1:11">
-      <c r="A146" s="2" t="s">
-        <v>177</v>
+      <c r="A146" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="J146" s="4" t="s">
-        <v>176</v>
+        <v>2</v>
+      </c>
+      <c r="J146" s="4">
+        <v>632</v>
       </c>
       <c r="K146">
-        <v>154610</v>
+        <v>126889</v>
       </c>
     </row>
     <row r="147" spans="1:11">
-      <c r="A147" s="2" t="s">
-        <v>178</v>
+      <c r="A147" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="B147">
         <v>2</v>
       </c>
       <c r="C147">
-        <v>3</v>
-      </c>
-      <c r="J147" s="4" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="J147" s="4">
+        <v>628</v>
       </c>
       <c r="K147">
-        <v>79258</v>
+        <v>51513</v>
       </c>
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B148">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
-      <c r="J148" s="4">
-        <v>516</v>
+      <c r="J148" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="K148">
-        <v>119284</v>
+        <v>154610</v>
       </c>
     </row>
     <row r="149" spans="1:11">
-      <c r="A149" s="2" t="s">
-        <v>180</v>
+      <c r="A149" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J149" s="4">
-        <v>516</v>
+        <v>274</v>
       </c>
       <c r="K149">
-        <v>119284</v>
+        <v>105449</v>
       </c>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B150">
-        <v>2</v>
+        <v>176</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
-      <c r="J150" s="4" t="s">
-        <v>105</v>
+      <c r="J150" s="4">
+        <v>294</v>
       </c>
       <c r="K150">
-        <v>79258</v>
+        <v>715765</v>
       </c>
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B151" t="s">
-        <v>11</v>
+        <v>177</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
-      <c r="J151" s="4">
-        <v>294</v>
+      <c r="J151" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K151">
-        <v>715765</v>
+        <v>184252</v>
       </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="K152">
-        <v>371029</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="153" spans="1:11">
-      <c r="A153" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B153">
-        <v>3</v>
+      <c r="A153" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>2</v>
-      </c>
-      <c r="J153" s="4">
-        <v>110</v>
+        <v>3</v>
+      </c>
+      <c r="J153" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K153">
-        <v>16185</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="154" spans="1:11">
-      <c r="A154" s="2" t="s">
-        <v>185</v>
+      <c r="A154" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="B154">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J154" s="4">
-        <v>851</v>
+        <v>351</v>
       </c>
       <c r="K154">
-        <v>54894</v>
+        <v>417757</v>
       </c>
     </row>
     <row r="155" spans="1:11">
-      <c r="A155" s="2" t="s">
-        <v>186</v>
+      <c r="A155" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="B155" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K155">
         <v>273644</v>
       </c>
     </row>
     <row r="156" spans="1:11">
-      <c r="A156" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B156" t="s">
-        <v>188</v>
+      <c r="A156" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B156">
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="K156">
-        <v>303600</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="157" spans="1:11">
-      <c r="A157" s="2" t="s">
-        <v>86</v>
+      <c r="A157" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="B157" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>3</v>
-      </c>
-      <c r="J157" s="4" t="s">
-        <v>87</v>
+        <v>1</v>
+      </c>
+      <c r="J157" s="4">
+        <v>294</v>
       </c>
       <c r="K157">
-        <v>303600</v>
+        <v>715765</v>
       </c>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B158">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="K158">
         <v>1026294</v>
@@ -4425,270 +4357,254 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B159">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C159">
-        <v>1</v>
-      </c>
-      <c r="J159" s="4" t="s">
-        <v>190</v>
+        <v>3</v>
+      </c>
+      <c r="J159" s="4">
+        <v>294</v>
       </c>
       <c r="K159">
-        <v>1026294</v>
+        <v>715765</v>
       </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B160">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="K160">
-        <v>79258</v>
+        <v>306479</v>
       </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B161" t="s">
-        <v>11</v>
+        <v>187</v>
+      </c>
+      <c r="B161">
+        <v>1.1</v>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="K161">
-        <v>1890734</v>
+        <v>1026294</v>
       </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B162" t="s">
-        <v>11</v>
+        <v>188</v>
+      </c>
+      <c r="B162">
+        <v>1.1</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="K162">
-        <v>145271</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C163">
         <v>2</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="K163">
-        <v>145271</v>
+        <v>1890734</v>
       </c>
     </row>
     <row r="164" spans="1:11">
-      <c r="A164" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B164">
-        <v>2</v>
+      <c r="A164" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1</v>
       </c>
       <c r="C164">
-        <v>1</v>
-      </c>
-      <c r="E164">
-        <f>COUNTIF(C:C,1)</f>
-        <v>90</v>
-      </c>
-      <c r="F164" t="s">
-        <v>197</v>
-      </c>
-      <c r="G164" s="5">
-        <v>0.7129</v>
+        <v>2</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="K164">
-        <v>145271</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B165">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
-      <c r="F165" t="s">
-        <v>199</v>
-      </c>
       <c r="J165" s="4" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="K165">
-        <v>90748</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B166">
-        <v>1.1</v>
+        <v>192</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1</v>
       </c>
       <c r="C166">
-        <v>1</v>
-      </c>
-      <c r="F166" t="s">
-        <v>202</v>
+        <v>2</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="K166">
-        <v>40036</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B167" t="s">
-        <v>89</v>
+        <v>193</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="K167">
-        <v>303600</v>
+        <v>9951</v>
       </c>
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B168" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C168">
         <v>2</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="K168">
-        <v>303600</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B169" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="K169">
-        <v>79258</v>
+        <v>1074744</v>
       </c>
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B170" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C170">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="K170">
-        <v>79258</v>
+        <v>145271</v>
       </c>
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B171" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C171">
-        <v>3</v>
-      </c>
-      <c r="J171" s="4" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="J171" s="4">
+        <v>270</v>
       </c>
       <c r="K171">
-        <v>79258</v>
+        <v>434997</v>
       </c>
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B172" t="s">
-        <v>11</v>
+        <v>200</v>
+      </c>
+      <c r="B172">
+        <v>1.1</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
-      <c r="J172" s="4" t="s">
-        <v>105</v>
+      <c r="J172" s="4">
+        <v>717</v>
       </c>
       <c r="K172">
-        <v>79258</v>
+        <v>10514</v>
       </c>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B173" t="s">
-        <v>11</v>
+        <v>201</v>
+      </c>
+      <c r="B173">
+        <v>1.1</v>
       </c>
       <c r="C173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="K173">
         <v>79258</v>
@@ -4696,50 +4612,50 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="1" t="s">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="C174">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="K174">
-        <v>79258</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B175" t="s">
-        <v>11</v>
+        <v>202</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="K175">
-        <v>79258</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B176">
-        <v>2</v>
+        <v>203</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1</v>
       </c>
       <c r="C176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="K176">
         <v>79258</v>
@@ -4747,67 +4663,67 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B177" t="s">
-        <v>11</v>
+        <v>204</v>
+      </c>
+      <c r="B177">
+        <v>3</v>
       </c>
       <c r="C177">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="K177">
-        <v>79258</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B178">
-        <v>1.1</v>
+        <v>205</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="K178">
-        <v>79258</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B179">
         <v>2</v>
       </c>
       <c r="C179">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="K179">
-        <v>79258</v>
+        <v>382040</v>
       </c>
     </row>
     <row r="180" spans="1:11">
-      <c r="A180" s="1" t="s">
-        <v>216</v>
+      <c r="A180" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="B180">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C180">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="K180">
         <v>79258</v>
@@ -4815,101 +4731,101 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B181" t="s">
-        <v>11</v>
+        <v>208</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
       </c>
       <c r="C181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="K181">
-        <v>79258</v>
+        <v>446442</v>
       </c>
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B182">
-        <v>2</v>
+        <v>209</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="K182">
-        <v>79258</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B183" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C183">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="K183">
-        <v>1074744</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B184">
         <v>1.1</v>
       </c>
       <c r="C184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J184" s="4">
-        <v>181</v>
+        <v>368</v>
       </c>
       <c r="K184">
-        <v>39197</v>
+        <v>11953</v>
       </c>
     </row>
     <row r="185" spans="1:11">
-      <c r="A185" s="1" t="s">
-        <v>222</v>
+      <c r="A185" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="B185">
         <v>1.1</v>
       </c>
       <c r="C185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="K185">
-        <v>1026294</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="1" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B186" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="K186">
         <v>1026294</v>
@@ -4917,152 +4833,152 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B187">
         <v>1.1</v>
       </c>
       <c r="C187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="K187">
-        <v>1026294</v>
+        <v>900774</v>
       </c>
     </row>
     <row r="188" spans="1:11">
-      <c r="A188" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B188" t="s">
-        <v>11</v>
+      <c r="A188" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="K188">
-        <v>1026294</v>
+        <v>750760</v>
       </c>
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B189">
-        <v>1.1</v>
+        <v>216</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1</v>
       </c>
       <c r="C189">
-        <v>3</v>
-      </c>
-      <c r="J189" s="4" t="s">
-        <v>190</v>
+        <v>2</v>
+      </c>
+      <c r="J189" s="4">
+        <v>654</v>
       </c>
       <c r="K189">
-        <v>1026294</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="190" spans="1:11">
-      <c r="A190" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B190">
-        <v>2</v>
+      <c r="A190" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1</v>
       </c>
       <c r="C190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="K190">
-        <v>1026294</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="1" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B191">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="C191">
-        <v>3</v>
-      </c>
-      <c r="J191" s="4" t="s">
-        <v>190</v>
+        <v>2</v>
+      </c>
+      <c r="J191" s="4">
+        <v>212</v>
       </c>
       <c r="K191">
-        <v>1026294</v>
+        <v>89542</v>
       </c>
     </row>
     <row r="192" spans="1:11">
-      <c r="A192" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B192" t="s">
-        <v>11</v>
+      <c r="A192" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="K192">
-        <v>1026294</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B193" t="s">
-        <v>11</v>
+        <v>220</v>
+      </c>
+      <c r="B193">
+        <v>3</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>190</v>
+        <v>2</v>
       </c>
       <c r="K193">
-        <v>1026294</v>
+        <v>382040</v>
       </c>
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="1" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B194">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C194">
-        <v>1</v>
-      </c>
-      <c r="J194" s="4" t="s">
-        <v>190</v>
+        <v>2</v>
+      </c>
+      <c r="J194" s="4">
+        <v>988</v>
       </c>
       <c r="K194">
-        <v>1026294</v>
+        <v>9347</v>
       </c>
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B195" t="s">
-        <v>89</v>
+        <v>222</v>
+      </c>
+      <c r="B195">
+        <v>1.1</v>
       </c>
       <c r="C195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="K195">
         <v>1026294</v>
@@ -5070,327 +4986,327 @@
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B196">
-        <v>1.1</v>
+        <v>223</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
-      <c r="J196" s="4" t="s">
-        <v>190</v>
+      <c r="J196" s="4">
+        <v>294</v>
       </c>
       <c r="K196">
-        <v>1026294</v>
+        <v>715765</v>
       </c>
     </row>
     <row r="197" spans="1:11">
-      <c r="A197" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B197">
-        <v>1.2</v>
+      <c r="A197" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1</v>
       </c>
       <c r="C197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="K197">
-        <v>1026294</v>
+        <v>154610</v>
       </c>
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B198" t="s">
-        <v>11</v>
+        <v>225</v>
+      </c>
+      <c r="B198">
+        <v>1.2</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="K198">
-        <v>1026294</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B199" t="s">
-        <v>11</v>
+        <v>226</v>
+      </c>
+      <c r="B199">
+        <v>2</v>
       </c>
       <c r="C199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J199" s="4">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="K199">
-        <v>715765</v>
+        <v>320962</v>
       </c>
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="1" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B200" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C200">
-        <v>1</v>
-      </c>
-      <c r="J200" s="4">
-        <v>294</v>
+        <v>3</v>
+      </c>
+      <c r="J200" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="K200">
-        <v>715765</v>
+        <v>273644</v>
       </c>
     </row>
     <row r="201" spans="1:11">
-      <c r="A201" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B201" t="s">
-        <v>11</v>
+      <c r="A201" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B201">
+        <v>2</v>
       </c>
       <c r="C201">
-        <v>3</v>
-      </c>
-      <c r="J201" s="4" t="s">
-        <v>239</v>
+        <v>2</v>
+      </c>
+      <c r="J201" s="4">
+        <v>491</v>
       </c>
       <c r="K201">
-        <v>31584</v>
+        <v>42193</v>
       </c>
     </row>
     <row r="202" spans="1:11">
-      <c r="A202" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B202">
-        <v>1.2</v>
+      <c r="A202" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="K202">
-        <v>79258</v>
+        <v>1026294</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A156" r:id="rId1" display="https://github.com/thunderbird/thunderbird-android/pull/9225"/>
-    <hyperlink ref="A5" r:id="rId2" display="https://github.com/ankidroid/Anki-Android/pull/17165"/>
-    <hyperlink ref="A35" r:id="rId3" display="https://github.com/ankidroid/Anki-Android/pull/15014"/>
-    <hyperlink ref="A51" r:id="rId4" display="https://github.com/DroidKaigi/conference-app-2024/pull/640"/>
-    <hyperlink ref="A50" r:id="rId5" display="https://github.com/ankidroid/Anki-Android/pull/6807/files"/>
-    <hyperlink ref="A65" r:id="rId6" display="https://github.com/wordpress-mobile/WordPress-Android/pull/13467"/>
-    <hyperlink ref="A202" r:id="rId7" display="https://github.com/kiwix/kiwix-android/issues/630"/>
-    <hyperlink ref="A157" r:id="rId8" display="https://github.com/thunderbird/thunderbird-android/pull/7872"/>
-    <hyperlink ref="A158" r:id="rId9" display="https://github.com/signalapp/Signal-Android/issues/7252"/>
-    <hyperlink ref="A159" r:id="rId10" display="https://github.com/signalapp/Signal-Android/issues/7578"/>
-    <hyperlink ref="A160" r:id="rId11" display="https://github.com/kiwix/kiwix-android/issues/1301"/>
-    <hyperlink ref="A161" r:id="rId12" display="https://github.com/AnySoftKeyboard/AnySoftKeyboard/issues/858"/>
-    <hyperlink ref="A162" r:id="rId13" display="https://github.com/commons-app/apps-android-commons/issues/1948"/>
-    <hyperlink ref="A163" r:id="rId14" display="https://github.com/commons-app/apps-android-commons/issues/2107"/>
-    <hyperlink ref="A164" r:id="rId15" display="https://github.com/commons-app/apps-android-commons/issues/2573"/>
-    <hyperlink ref="A165" r:id="rId16" display="https://github.com/Etar-Group/Etar-Calendar/issues/489"/>
-    <hyperlink ref="A166" r:id="rId17" display="https://github.com/grote/Transportr/issues/491"/>
-    <hyperlink ref="A167" r:id="rId18" display="https://github.com/thunderbird/thunderbird-android/issues/1930"/>
-    <hyperlink ref="A168" r:id="rId19" display="https://github.com/thunderbird/thunderbird-android/issues/2065"/>
-    <hyperlink ref="A169" r:id="rId20" display="https://github.com/kiwix/kiwix-android/issues/1047"/>
-    <hyperlink ref="A170" r:id="rId21" display="https://github.com/kiwix/kiwix-android/issues/1531"/>
-    <hyperlink ref="A171" r:id="rId22" display="https://github.com/kiwix/kiwix-android/issues/1573"/>
-    <hyperlink ref="A172" r:id="rId23" display="https://github.com/kiwix/kiwix-android/issues/1702"/>
-    <hyperlink ref="A173" r:id="rId24" display="https://github.com/kiwix/kiwix-android/issues/1707"/>
-    <hyperlink ref="A174" r:id="rId25" display="https://github.com/kiwix/kiwix-android/issues/1748"/>
-    <hyperlink ref="A175" r:id="rId26" display="https://github.com/kiwix/kiwix-android/issues/1792"/>
-    <hyperlink ref="A176" r:id="rId27" display="https://github.com/kiwix/kiwix-android/issues/424"/>
-    <hyperlink ref="A177" r:id="rId28" display="https://github.com/kiwix/kiwix-android/issues/425"/>
-    <hyperlink ref="A178" r:id="rId29" display="https://github.com/kiwix/kiwix-android/issues/472"/>
-    <hyperlink ref="A179" r:id="rId30" display="https://github.com/kiwix/kiwix-android/issues/532"/>
-    <hyperlink ref="A180" r:id="rId31" display="https://github.com/kiwix/kiwix-android/issues/552"/>
-    <hyperlink ref="A181" r:id="rId32" display="https://github.com/kiwix/kiwix-android/issues/618"/>
-    <hyperlink ref="A182" r:id="rId33" display="https://github.com/kiwix/kiwix-android/pull/542"/>
-    <hyperlink ref="A183" r:id="rId34" display="https://github.com/laurent22/joplin/issues/2695"/>
-    <hyperlink ref="A184" r:id="rId35" display="https://github.com/openmrs/openmrs-contrib-android-client/pull/620"/>
-    <hyperlink ref="A185" r:id="rId36" display="https://github.com/signalapp/Signal-Android/issues/5387"/>
-    <hyperlink ref="A186" r:id="rId37" display="https://github.com/signalapp/Signal-Android/issues/5759"/>
-    <hyperlink ref="A187" r:id="rId38" display="https://github.com/signalapp/Signal-Android/issues/7024"/>
-    <hyperlink ref="A188" r:id="rId39" display="https://github.com/signalapp/Signal-Android/issues/7036"/>
-    <hyperlink ref="A189" r:id="rId40" display="https://github.com/signalapp/Signal-Android/issues/7614"/>
-    <hyperlink ref="A190" r:id="rId41" display="https://github.com/signalapp/Signal-Android/issues/7644"/>
-    <hyperlink ref="A191" r:id="rId42" display="https://github.com/signalapp/Signal-Android/issues/7705"/>
-    <hyperlink ref="A192" r:id="rId43" display="https://github.com/signalapp/Signal-Android/issues/7821"/>
-    <hyperlink ref="A193" r:id="rId44" display="https://github.com/signalapp/Signal-Android/issues/8151"/>
-    <hyperlink ref="A194" r:id="rId45" display="https://github.com/signalapp/Signal-Android/issues/8253"/>
-    <hyperlink ref="A195" r:id="rId46" display="https://github.com/signalapp/Signal-Android/issues/8266"/>
-    <hyperlink ref="A196" r:id="rId47" display="https://github.com/signalapp/Signal-Android/issues/8758"/>
-    <hyperlink ref="A197" r:id="rId48" display="https://github.com/signalapp/Signal-Android/issues/8995"/>
-    <hyperlink ref="A198" r:id="rId49" display="https://github.com/signalapp/Signal-Android/issues/9054"/>
-    <hyperlink ref="A199" r:id="rId50" display="https://github.com/woocommerce/woocommerce-android/issues/2313"/>
-    <hyperlink ref="A200" r:id="rId51" display="https://github.com/woocommerce/woocommerce-android/issues/2384"/>
-    <hyperlink ref="A201" r:id="rId52" display="https://github.com/yeriomin/YalpStore/issues/372"/>
-    <hyperlink ref="A154" r:id="rId53" display="https://github.com/JetBrains/jewel/pull/262"/>
-    <hyperlink ref="A155" r:id="rId54" display="https://github.com/ankidroid/Anki-Android/pull/13961"/>
-    <hyperlink ref="A1" r:id="rId55" display="https://github.com/ankidroid/Anki-Android/pull/17743"/>
-    <hyperlink ref="A2" r:id="rId56" display="https://github.com/HedvigInsurance/android/pull/2464"/>
-    <hyperlink ref="A3" r:id="rId57" display="https://github.com/ankidroid/Anki-Android/pull/17672"/>
-    <hyperlink ref="A4" r:id="rId58" display="https://github.com/ankidroid/Anki-Android/pull/16775"/>
-    <hyperlink ref="A6" r:id="rId59" display="https://github.com/ankidroid/Anki-Android/pull/16568"/>
-    <hyperlink ref="A7" r:id="rId60" display="https://github.com/ankidroid/Anki-Android/pull/16549"/>
-    <hyperlink ref="A8" r:id="rId61" display="https://github.com/Catappult/appcoins-wallet-android/pull/1207"/>
-    <hyperlink ref="A9" r:id="rId62" display="https://github.com/ehsannarmani/ComposeCharts/pull/73"/>
-    <hyperlink ref="A10" r:id="rId63" display="https://github.com/ankidroid/Anki-Android/pull/14879"/>
-    <hyperlink ref="A11" r:id="rId64" display="https://github.com/ankidroid/Anki-Android/pull/17985"/>
-    <hyperlink ref="A12" r:id="rId65" display="https://github.com/ankidroid/Anki-Android/pull/18022"/>
-    <hyperlink ref="A13" r:id="rId66" display="https://github.com/woocommerce/woocommerce-android/pull/13486"/>
-    <hyperlink ref="A14" r:id="rId67" display="https://github.com/ankidroid/Anki-Android/pull/15333"/>
-    <hyperlink ref="A15" r:id="rId68" display="https://github.com/ankidroid/Anki-Android/pull/17932"/>
-    <hyperlink ref="A16" r:id="rId69" display="https://github.com/mostafaalagamy/Metrolist/pull/327"/>
-    <hyperlink ref="A17" r:id="rId70" display="https://github.com/tuskyapp/Tusky/pull/1286"/>
-    <hyperlink ref="A18" r:id="rId71" display="https://github.com/simondankelmann/Bluetooth-LE-Spam/pull/356"/>
-    <hyperlink ref="A19" r:id="rId72" display="https://github.com/ankidroid/Anki-Android/pull/15842"/>
-    <hyperlink ref="A20" r:id="rId73" display="https://github.com/ankidroid/Anki-Android/pull/15683"/>
-    <hyperlink ref="A21" r:id="rId74" display="https://github.com/ankidroid/Anki-Android/pull/14894"/>
-    <hyperlink ref="A22" r:id="rId75" display="https://github.com/Automattic/pocket-casts-android/pull/3698"/>
-    <hyperlink ref="A23" r:id="rId76" display="https://github.com/ankidroid/Anki-Android/pull/17724"/>
-    <hyperlink ref="A24" r:id="rId77" display="https://github.com/ankidroid/Anki-Android/pull/17204"/>
-    <hyperlink ref="A25" r:id="rId78" display="https://github.com/ankidroid/Anki-Android/pull/13844"/>
-    <hyperlink ref="A26" r:id="rId79" display="https://github.com/HabitRPG/habitica-android/issues/2104"/>
-    <hyperlink ref="A27" r:id="rId80" display="https://github.com/ankidroid/Anki-Android/pull/14041"/>
-    <hyperlink ref="A28" r:id="rId81" display="https://github.com/tuskyapp/Tusky/pull/4864"/>
-    <hyperlink ref="A29" r:id="rId82" display="https://github.com/ankidroid/Anki-Android/pull/14805"/>
-    <hyperlink ref="A30" r:id="rId83" display="https://github.com/Infomaniak/android-kDrive/pull/1507"/>
-    <hyperlink ref="A31" r:id="rId84" display="https://github.com/ankidroid/Anki-Android/pull/13737"/>
-    <hyperlink ref="A32" r:id="rId85" display="https://github.com/MixinNetwork/android-app/pull/5165"/>
-    <hyperlink ref="A33" r:id="rId86" display="https://github.com/Automattic/pocket-casts-android/pull/3154"/>
-    <hyperlink ref="A34" r:id="rId87" display="https://github.com/PhilKes/NotallyX/pull/349"/>
-    <hyperlink ref="A36" r:id="rId88" display="https://github.com/woocommerce/woocommerce-android/pull/13316"/>
-    <hyperlink ref="A37" r:id="rId89" display="https://github.com/commons-app/apps-android-commons/pull/6120"/>
-    <hyperlink ref="A38" r:id="rId90" display="https://github.com/ankidroid/Anki-Android/pull/13123"/>
-    <hyperlink ref="A39" r:id="rId91" display="https://github.com/Automattic/pocket-casts-android/pull/3460"/>
-    <hyperlink ref="A40" r:id="rId92" display="https://github.com/ankidroid/Anki-Android/pull/10727"/>
-    <hyperlink ref="A41" r:id="rId93" display="https://github.com/ankidroid/Anki-Android/pull/11479"/>
-    <hyperlink ref="A42" r:id="rId94" display="https://github.com/ankidroid/Anki-Android/pull/16648"/>
-    <hyperlink ref="A43" r:id="rId95" display="https://github.com/hannibal002/SkyHanni/pull/2257"/>
-    <hyperlink ref="A44" r:id="rId96" display="https://github.com/ankidroid/Anki-Android/pull/8168"/>
+    <hyperlink ref="A13" r:id="rId1" display="https://github.com/thunderbird/thunderbird-android/pull/9225"/>
+    <hyperlink ref="A32" r:id="rId2" display="https://github.com/ankidroid/Anki-Android/pull/17165"/>
+    <hyperlink ref="A132" r:id="rId3" display="https://github.com/ankidroid/Anki-Android/pull/15014"/>
+    <hyperlink ref="A201" r:id="rId4" display="https://github.com/DroidKaigi/conference-app-2024/pull/640"/>
+    <hyperlink ref="A141" r:id="rId5" display="https://github.com/ankidroid/Anki-Android/pull/6807/files"/>
+    <hyperlink ref="A164" r:id="rId6" display="https://github.com/wordpress-mobile/WordPress-Android/pull/13467"/>
+    <hyperlink ref="A180" r:id="rId7" display="https://github.com/kiwix/kiwix-android/issues/630"/>
+    <hyperlink ref="A87" r:id="rId8" display="https://github.com/thunderbird/thunderbird-android/pull/7872"/>
+    <hyperlink ref="A19" r:id="rId9" display="https://github.com/signalapp/Signal-Android/issues/7252"/>
+    <hyperlink ref="A158" r:id="rId10" display="https://github.com/signalapp/Signal-Android/issues/7578"/>
+    <hyperlink ref="A156" r:id="rId11" display="https://github.com/kiwix/kiwix-android/issues/1301"/>
+    <hyperlink ref="A163" r:id="rId12" display="https://github.com/AnySoftKeyboard/AnySoftKeyboard/issues/858"/>
+    <hyperlink ref="A122" r:id="rId13" display="https://github.com/commons-app/apps-android-commons/issues/1948"/>
+    <hyperlink ref="A92" r:id="rId14" display="https://github.com/commons-app/apps-android-commons/issues/2107"/>
+    <hyperlink ref="A67" r:id="rId15" display="https://github.com/commons-app/apps-android-commons/issues/2573"/>
+    <hyperlink ref="A71" r:id="rId16" display="https://github.com/Etar-Group/Etar-Calendar/issues/489"/>
+    <hyperlink ref="A27" r:id="rId17" display="https://github.com/grote/Transportr/issues/491"/>
+    <hyperlink ref="A110" r:id="rId18" display="https://github.com/thunderbird/thunderbird-android/issues/1930"/>
+    <hyperlink ref="A105" r:id="rId19" display="https://github.com/thunderbird/thunderbird-android/issues/2065"/>
+    <hyperlink ref="A176" r:id="rId20" display="https://github.com/kiwix/kiwix-android/issues/1047"/>
+    <hyperlink ref="A133" r:id="rId21" display="https://github.com/kiwix/kiwix-android/issues/1531"/>
+    <hyperlink ref="A23" r:id="rId22" display="https://github.com/kiwix/kiwix-android/issues/1573"/>
+    <hyperlink ref="A43" r:id="rId23" display="https://github.com/kiwix/kiwix-android/issues/1702"/>
+    <hyperlink ref="A34" r:id="rId24" display="https://github.com/kiwix/kiwix-android/issues/1707"/>
+    <hyperlink ref="A91" r:id="rId25" display="https://github.com/kiwix/kiwix-android/issues/1748"/>
+    <hyperlink ref="A135" r:id="rId26" display="https://github.com/kiwix/kiwix-android/issues/1792"/>
+    <hyperlink ref="A81" r:id="rId27" display="https://github.com/kiwix/kiwix-android/issues/424"/>
+    <hyperlink ref="A190" r:id="rId28" display="https://github.com/kiwix/kiwix-android/issues/425"/>
+    <hyperlink ref="A108" r:id="rId29" display="https://github.com/kiwix/kiwix-android/issues/472"/>
+    <hyperlink ref="A66" r:id="rId30" display="https://github.com/kiwix/kiwix-android/issues/532"/>
+    <hyperlink ref="A173" r:id="rId31" display="https://github.com/kiwix/kiwix-android/issues/552"/>
+    <hyperlink ref="A166" r:id="rId32" display="https://github.com/kiwix/kiwix-android/issues/618"/>
+    <hyperlink ref="A165" r:id="rId33" display="https://github.com/kiwix/kiwix-android/pull/542"/>
+    <hyperlink ref="A169" r:id="rId34" display="https://github.com/laurent22/joplin/issues/2695"/>
+    <hyperlink ref="A72" r:id="rId35" display="https://github.com/openmrs/openmrs-contrib-android-client/pull/620"/>
+    <hyperlink ref="A161" r:id="rId36" display="https://github.com/signalapp/Signal-Android/issues/5387"/>
+    <hyperlink ref="A113" r:id="rId37" display="https://github.com/signalapp/Signal-Android/issues/5759"/>
+    <hyperlink ref="A195" r:id="rId38" display="https://github.com/signalapp/Signal-Android/issues/7024"/>
+    <hyperlink ref="A186" r:id="rId39" display="https://github.com/signalapp/Signal-Android/issues/7036"/>
+    <hyperlink ref="A24" r:id="rId40" display="https://github.com/signalapp/Signal-Android/issues/7614"/>
+    <hyperlink ref="A26" r:id="rId41" display="https://github.com/signalapp/Signal-Android/issues/7644"/>
+    <hyperlink ref="A40" r:id="rId42" display="https://github.com/signalapp/Signal-Android/issues/7705"/>
+    <hyperlink ref="A42" r:id="rId43" display="https://github.com/signalapp/Signal-Android/issues/7821"/>
+    <hyperlink ref="A202" r:id="rId44" display="https://github.com/signalapp/Signal-Android/issues/8151"/>
+    <hyperlink ref="A96" r:id="rId45" display="https://github.com/signalapp/Signal-Android/issues/8253"/>
+    <hyperlink ref="A46" r:id="rId46" display="https://github.com/signalapp/Signal-Android/issues/8266"/>
+    <hyperlink ref="A82" r:id="rId47" display="https://github.com/signalapp/Signal-Android/issues/8758"/>
+    <hyperlink ref="A116" r:id="rId48" display="https://github.com/signalapp/Signal-Android/issues/8995"/>
+    <hyperlink ref="A125" r:id="rId49" display="https://github.com/signalapp/Signal-Android/issues/9054"/>
+    <hyperlink ref="A139" r:id="rId50" display="https://github.com/woocommerce/woocommerce-android/issues/2313"/>
+    <hyperlink ref="A196" r:id="rId51" display="https://github.com/woocommerce/woocommerce-android/issues/2384"/>
+    <hyperlink ref="A138" r:id="rId52" display="https://github.com/yeriomin/YalpStore/issues/372"/>
+    <hyperlink ref="A93" r:id="rId53" display="https://github.com/JetBrains/jewel/pull/262"/>
+    <hyperlink ref="A153" r:id="rId54" display="https://github.com/ankidroid/Anki-Android/pull/13961"/>
+    <hyperlink ref="A36" r:id="rId55" display="https://github.com/ankidroid/Anki-Android/pull/17743"/>
+    <hyperlink ref="A107" r:id="rId56" display="https://github.com/HedvigInsurance/android/pull/2464"/>
+    <hyperlink ref="A198" r:id="rId57" display="https://github.com/ankidroid/Anki-Android/pull/17672"/>
+    <hyperlink ref="A99" r:id="rId58" display="https://github.com/ankidroid/Anki-Android/pull/16775"/>
+    <hyperlink ref="A129" r:id="rId59" display="https://github.com/ankidroid/Anki-Android/pull/16568"/>
+    <hyperlink ref="A17" r:id="rId60" display="https://github.com/ankidroid/Anki-Android/pull/16549"/>
+    <hyperlink ref="A199" r:id="rId61" display="https://github.com/Catappult/appcoins-wallet-android/pull/1207"/>
+    <hyperlink ref="A189" r:id="rId62" display="https://github.com/ehsannarmani/ComposeCharts/pull/73"/>
+    <hyperlink ref="A49" r:id="rId63" display="https://github.com/ankidroid/Anki-Android/pull/14879"/>
+    <hyperlink ref="A183" r:id="rId64" display="https://github.com/ankidroid/Anki-Android/pull/17985"/>
+    <hyperlink ref="A21" r:id="rId65" display="https://github.com/ankidroid/Anki-Android/pull/18022"/>
+    <hyperlink ref="A44" r:id="rId66" display="https://github.com/woocommerce/woocommerce-android/pull/13486"/>
+    <hyperlink ref="A182" r:id="rId67" display="https://github.com/ankidroid/Anki-Android/pull/15333"/>
+    <hyperlink ref="A50" r:id="rId68" display="https://github.com/ankidroid/Anki-Android/pull/17932"/>
+    <hyperlink ref="A10" r:id="rId69" display="https://github.com/mostafaalagamy/Metrolist/pull/327"/>
+    <hyperlink ref="A119" r:id="rId70" display="https://github.com/tuskyapp/Tusky/pull/1286"/>
+    <hyperlink ref="A167" r:id="rId71" display="https://github.com/simondankelmann/Bluetooth-LE-Spam/pull/356"/>
+    <hyperlink ref="A168" r:id="rId72" display="https://github.com/ankidroid/Anki-Android/pull/15842"/>
+    <hyperlink ref="A6" r:id="rId73" display="https://github.com/ankidroid/Anki-Android/pull/15683"/>
+    <hyperlink ref="A12" r:id="rId74" display="https://github.com/ankidroid/Anki-Android/pull/14894"/>
+    <hyperlink ref="A37" r:id="rId75" display="https://github.com/Automattic/pocket-casts-android/pull/3698"/>
+    <hyperlink ref="A200" r:id="rId76" display="https://github.com/ankidroid/Anki-Android/pull/17724"/>
+    <hyperlink ref="A14" r:id="rId77" display="https://github.com/ankidroid/Anki-Android/pull/17204"/>
+    <hyperlink ref="A54" r:id="rId78" display="https://github.com/ankidroid/Anki-Android/pull/13844"/>
+    <hyperlink ref="A55" r:id="rId79" display="https://github.com/HabitRPG/habitica-android/issues/2104"/>
+    <hyperlink ref="A2" r:id="rId80" display="https://github.com/ankidroid/Anki-Android/pull/14041"/>
+    <hyperlink ref="A8" r:id="rId81" display="https://github.com/tuskyapp/Tusky/pull/4864"/>
+    <hyperlink ref="A84" r:id="rId82" display="https://github.com/ankidroid/Anki-Android/pull/14805"/>
+    <hyperlink ref="A63" r:id="rId83" display="https://github.com/Infomaniak/android-kDrive/pull/1507"/>
+    <hyperlink ref="A114" r:id="rId84" display="https://github.com/ankidroid/Anki-Android/pull/13737"/>
+    <hyperlink ref="A39" r:id="rId85" display="https://github.com/MixinNetwork/android-app/pull/5165"/>
+    <hyperlink ref="A193" r:id="rId86" display="https://github.com/Automattic/pocket-casts-android/pull/3154"/>
+    <hyperlink ref="A134" r:id="rId87" display="https://github.com/PhilKes/NotallyX/pull/349"/>
+    <hyperlink ref="A157" r:id="rId88" display="https://github.com/woocommerce/woocommerce-android/pull/13316"/>
+    <hyperlink ref="A170" r:id="rId89" display="https://github.com/commons-app/apps-android-commons/pull/6120"/>
+    <hyperlink ref="A124" r:id="rId90" display="https://github.com/ankidroid/Anki-Android/pull/13123"/>
+    <hyperlink ref="A51" r:id="rId91" display="https://github.com/Automattic/pocket-casts-android/pull/3460"/>
+    <hyperlink ref="A47" r:id="rId92" display="https://github.com/ankidroid/Anki-Android/pull/10727"/>
+    <hyperlink ref="A78" r:id="rId93" display="https://github.com/ankidroid/Anki-Android/pull/11479"/>
+    <hyperlink ref="A41" r:id="rId94" display="https://github.com/ankidroid/Anki-Android/pull/16648"/>
+    <hyperlink ref="A126" r:id="rId95" display="https://github.com/hannibal002/SkyHanni/pull/2257"/>
+    <hyperlink ref="A144" r:id="rId96" display="https://github.com/ankidroid/Anki-Android/pull/8168"/>
     <hyperlink ref="A45" r:id="rId97" display="https://github.com/ankidroid/Anki-Android/pull/13235"/>
-    <hyperlink ref="A46" r:id="rId98" display="https://github.com/ankidroid/Anki-Android/pull/17146"/>
-    <hyperlink ref="A47" r:id="rId99" display="https://github.com/Visual-Code-Space/Visual-Code-Space/pull/130"/>
-    <hyperlink ref="A48" r:id="rId100" display="https://github.com/ankidroid/Anki-Android/pull/11687"/>
-    <hyperlink ref="A49" r:id="rId101" display="https://github.com/bitwarden/android/pull/4065"/>
-    <hyperlink ref="A52" r:id="rId102" display="https://github.com/Automattic/pocket-casts-android/pull/2432"/>
-    <hyperlink ref="A53" r:id="rId103" display="https://github.com/ankidroid/Anki-Android/pull/5128"/>
-    <hyperlink ref="A54" r:id="rId104" display="https://github.com/breezy-weather/breezy-weather/pull/938"/>
-    <hyperlink ref="A55" r:id="rId105" display="https://github.com/breezy-weather/breezy-weather/pull/931"/>
-    <hyperlink ref="A56" r:id="rId106" display="https://github.com/kickstarter/android-oss/pull/1054"/>
-    <hyperlink ref="A57" r:id="rId107" display="https://github.com/kickstarter/android-oss/pull/603"/>
-    <hyperlink ref="A58" r:id="rId108" display="https://github.com/wordpress-mobile/WordPress-Android/pull/9761"/>
-    <hyperlink ref="A59" r:id="rId109" display="https://github.com/wordpress-mobile/WordPress-Android/pull/19771"/>
-    <hyperlink ref="A60" r:id="rId110" display="https://github.com/breezy-weather/breezy-weather/pull/981"/>
-    <hyperlink ref="A61" r:id="rId111" display="https://github.com/wordpress-mobile/WordPress-Android/pull/17086"/>
-    <hyperlink ref="A62" r:id="rId112" display="https://github.com/Infomaniak/android-kMail/pull/1938"/>
-    <hyperlink ref="A63" r:id="rId113" display="https://github.com/wordpress-mobile/WordPress-Android/pull/14849"/>
-    <hyperlink ref="A64" r:id="rId114" display="https://github.com/kickstarter/android-oss/pull/2017"/>
-    <hyperlink ref="A66" r:id="rId115" display="https://github.com/wordpress-mobile/WordPress-Android/issues/10923"/>
-    <hyperlink ref="A67" r:id="rId8" display="https://github.com/thunderbird/thunderbird-android/pull/7872"/>
-    <hyperlink ref="A68" r:id="rId116" display="https://github.com/ankidroid/Anki-Android/pull/4242"/>
-    <hyperlink ref="A69" r:id="rId117" display="https://github.com/SagerNet/sing-box-for-android/pull/25/files"/>
-    <hyperlink ref="A70" r:id="rId118" display="https://github.com/wordpress-mobile/WordPress-Android/pull/20561"/>
-    <hyperlink ref="A71" r:id="rId119" display="https://github.com/libre-tube/LibreTube/pull/5761#discussioncomment-8787935"/>
-    <hyperlink ref="A72" r:id="rId120" display="https://github.com/wordpress-mobile/WordPress-Android/pull/9711"/>
-    <hyperlink ref="A73" r:id="rId121" display="https://github.com/wordpress-mobile/WordPress-Android/pull/9546"/>
-    <hyperlink ref="A74" r:id="rId122" display="https://github.com/wordpress-mobile/WordPress-Android/pull/20482"/>
-    <hyperlink ref="A75" r:id="rId123" display="https://github.com/ankidroid/Anki-Android/pull/14208"/>
-    <hyperlink ref="A76" r:id="rId124" display="https://github.com/whitescent/Mastify/pull/39"/>
-    <hyperlink ref="A77" r:id="rId125" display="https://github.com/wikimedia/apps-android-wikipedia/pull/4442"/>
-    <hyperlink ref="A78" r:id="rId126" display="https://github.com/mozilla-mobile/firefox-android/pull/6077"/>
-    <hyperlink ref="A79" r:id="rId127" display="https://github.com/whitescent/Mastify/pull/33"/>
-    <hyperlink ref="A80" r:id="rId128" display="https://github.com/kiwix/kiwix-android/pull/3823"/>
-    <hyperlink ref="A81" r:id="rId129" display="https://github.com/breezy-weather/breezy-weather/pull/713"/>
-    <hyperlink ref="A82" r:id="rId130" display="https://github.com/openMF/mobile-wallet/pull/1515"/>
-    <hyperlink ref="A83" r:id="rId131" display="https://github.com/wordpress-mobile/WordPress-Android/pull/7999"/>
-    <hyperlink ref="A84" r:id="rId132" display="https://github.com/ankidroid/Anki-Android/pull/15151"/>
-    <hyperlink ref="A85" r:id="rId133" display="https://github.com/microsoft/fluentui-android/pull/539"/>
-    <hyperlink ref="A86" r:id="rId134" display="https://github.com/wikimedia/apps-android-wikipedia/pull/573"/>
-    <hyperlink ref="A87" r:id="rId135" display="https://github.com/jkuester/unlauncher/pull/195"/>
-    <hyperlink ref="A88" r:id="rId136" display="https://github.com/osfans/trime/pull/1193"/>
-    <hyperlink ref="A89" r:id="rId137" display="https://github.com/mozilla-mobile/firefox-android/pull/3826"/>
-    <hyperlink ref="A90" r:id="rId138" display="https://github.com/SimpleMobileTools/Simple-Commons/pull/1787"/>
-    <hyperlink ref="A91" r:id="rId139" display="https://github.com/mozilla-mobile/firefox-android/pull/1868"/>
-    <hyperlink ref="A92" r:id="rId140" display="https://github.com/thunderbird/thunderbird-android/pull/7876"/>
-    <hyperlink ref="A93" r:id="rId141" display="https://github.com/thunderbird/thunderbird-android/pull/6723"/>
-    <hyperlink ref="A94" r:id="rId142" display="https://github.com/oppia/oppia-android/pull/5116"/>
-    <hyperlink ref="A95" r:id="rId143" display="https://github.com/thunderbird/thunderbird-android/pull/5865"/>
-    <hyperlink ref="A96" r:id="rId144" display="https://github.com/ismartcoding/plain-app/pull/82"/>
-    <hyperlink ref="A97" r:id="rId145" display="https://github.com/oppia/oppia-android/pull/5144"/>
-    <hyperlink ref="A98" r:id="rId146" display="https://github.com/dinbtechit/vscode-theme/pull/68"/>
-    <hyperlink ref="A99" r:id="rId147" display="https://github.com/openMF/android-client/pull/1957"/>
-    <hyperlink ref="A100" r:id="rId148" display="https://github.com/libre-tube/LibreTube/pull/4043"/>
-    <hyperlink ref="A101" r:id="rId149" display="https://github.com/wordpress-mobile/WordPress-Android/pull/18098"/>
-    <hyperlink ref="A102" r:id="rId150" display="https://github.com/openhab/openhab-android/pull/3227"/>
-    <hyperlink ref="A103" r:id="rId151" display="https://github.com/wordpress-mobile/WordPress-Android/pull/18145"/>
-    <hyperlink ref="A104" r:id="rId152" display="https://github.com/thunderbird/thunderbird-android/pull/3456"/>
-    <hyperlink ref="A105" r:id="rId153" display="https://github.com/woocommerce/woocommerce-android/pull/8844"/>
-    <hyperlink ref="A106" r:id="rId154" display="https://github.com/vitorpamplona/amethyst/pull/90"/>
-    <hyperlink ref="A107" r:id="rId155" display="https://github.com/wordpress-mobile/WordPress-Android/pull/17863"/>
-    <hyperlink ref="A108" r:id="rId156" display="https://github.com/wireapp/wire-android/pull/1777"/>
-    <hyperlink ref="A109" r:id="rId157" display="https://github.com/home-assistant/android/pull/2988"/>
-    <hyperlink ref="A110" r:id="rId158" display="https://github.com/wordpress-mobile/WordPress-Android/pull/16812"/>
-    <hyperlink ref="A111" r:id="rId159" display="https://github.com/TUM-Dev/Campus-Android/pull/1496"/>
-    <hyperlink ref="A112" r:id="rId160" display="https://github.com/ankidroid/Anki-Android/pull/12971"/>
-    <hyperlink ref="A113" r:id="rId161" display="https://github.com/home-assistant/android/pull/1994"/>
-    <hyperlink ref="A114" r:id="rId162" display="https://github.com/thunderbird/thunderbird-android/pull/6489"/>
-    <hyperlink ref="A115" r:id="rId163" display="https://github.com/iTaysonLab/jetisteam/pull/2"/>
-    <hyperlink ref="A116" r:id="rId164" display="https://github.com/home-assistant/android/pull/1043"/>
-    <hyperlink ref="A117" r:id="rId165" display="https://github.com/Automattic/pocket-casts-android/pull/432"/>
-    <hyperlink ref="A118" r:id="rId166" display="https://github.com/nightscout/AndroidAPS/pull/1847"/>
-    <hyperlink ref="A119" r:id="rId167" display="https://github.com/Automattic/pocket-casts-android/pull/215/files"/>
-    <hyperlink ref="A120" r:id="rId168" display="https://github.com/ankidroid/Anki-Android/pull/5417"/>
-    <hyperlink ref="A121" r:id="rId169" display="https://github.com/wordpress-mobile/WordPress-Android/pull/17286"/>
-    <hyperlink ref="A122" r:id="rId170" display="https://github.com/oppia/oppia-android/pull/4617"/>
-    <hyperlink ref="A123" r:id="rId171" display="https://github.com/oppia/oppia-android/pull/4616/files"/>
-    <hyperlink ref="A124" r:id="rId172" display="https://github.com/element-hq/element-android/pull/7015/files"/>
-    <hyperlink ref="A125" r:id="rId173" display="https://github.com/woocommerce/woocommerce-android/pull/7188/files"/>
-    <hyperlink ref="A126" r:id="rId174" display="https://github.com/Decathlon/vitamin-compose/pull/39"/>
+    <hyperlink ref="A52" r:id="rId98" display="https://github.com/ankidroid/Anki-Android/pull/17146"/>
+    <hyperlink ref="A70" r:id="rId99" display="https://github.com/Visual-Code-Space/Visual-Code-Space/pull/130"/>
+    <hyperlink ref="A178" r:id="rId100" display="https://github.com/ankidroid/Anki-Android/pull/11687"/>
+    <hyperlink ref="A76" r:id="rId101" display="https://github.com/bitwarden/android/pull/4065"/>
+    <hyperlink ref="A103" r:id="rId102" display="https://github.com/Automattic/pocket-casts-android/pull/2432"/>
+    <hyperlink ref="A118" r:id="rId103" display="https://github.com/ankidroid/Anki-Android/pull/5128"/>
+    <hyperlink ref="A11" r:id="rId104" display="https://github.com/breezy-weather/breezy-weather/pull/938"/>
+    <hyperlink ref="A3" r:id="rId105" display="https://github.com/breezy-weather/breezy-weather/pull/931"/>
+    <hyperlink ref="A151" r:id="rId106" display="https://github.com/kickstarter/android-oss/pull/1054"/>
+    <hyperlink ref="A89" r:id="rId107" display="https://github.com/kickstarter/android-oss/pull/603"/>
+    <hyperlink ref="A97" r:id="rId108" display="https://github.com/wordpress-mobile/WordPress-Android/pull/9761"/>
+    <hyperlink ref="A152" r:id="rId109" display="https://github.com/wordpress-mobile/WordPress-Android/pull/19771"/>
+    <hyperlink ref="A90" r:id="rId110" display="https://github.com/breezy-weather/breezy-weather/pull/981"/>
+    <hyperlink ref="A140" r:id="rId111" display="https://github.com/wordpress-mobile/WordPress-Android/pull/17086"/>
+    <hyperlink ref="A68" r:id="rId112" display="https://github.com/Infomaniak/android-kMail/pull/1938"/>
+    <hyperlink ref="A188" r:id="rId113" display="https://github.com/wordpress-mobile/WordPress-Android/pull/14849"/>
+    <hyperlink ref="A30" r:id="rId114" display="https://github.com/kickstarter/android-oss/pull/2017"/>
+    <hyperlink ref="A100" r:id="rId115" display="https://github.com/wordpress-mobile/WordPress-Android/issues/10923"/>
+    <hyperlink ref="A174" r:id="rId8" display="https://github.com/thunderbird/thunderbird-android/pull/7872"/>
+    <hyperlink ref="A20" r:id="rId116" display="https://github.com/ankidroid/Anki-Android/pull/4242"/>
+    <hyperlink ref="A172" r:id="rId117" display="https://github.com/SagerNet/sing-box-for-android/pull/25/files"/>
+    <hyperlink ref="A64" r:id="rId118" display="https://github.com/wordpress-mobile/WordPress-Android/pull/20561"/>
+    <hyperlink ref="A74" r:id="rId119" display="https://github.com/libre-tube/LibreTube/pull/5761#discussioncomment-8787935"/>
+    <hyperlink ref="A15" r:id="rId120" display="https://github.com/wordpress-mobile/WordPress-Android/pull/9711"/>
+    <hyperlink ref="A145" r:id="rId121" display="https://github.com/wordpress-mobile/WordPress-Android/pull/9546"/>
+    <hyperlink ref="A104" r:id="rId122" display="https://github.com/wordpress-mobile/WordPress-Android/pull/20482"/>
+    <hyperlink ref="A88" r:id="rId123" display="https://github.com/ankidroid/Anki-Android/pull/14208"/>
+    <hyperlink ref="A117" r:id="rId124" display="https://github.com/whitescent/Mastify/pull/39"/>
+    <hyperlink ref="A160" r:id="rId125" display="https://github.com/wikimedia/apps-android-wikipedia/pull/4442"/>
+    <hyperlink ref="A25" r:id="rId126" display="https://github.com/mozilla-mobile/firefox-android/pull/6077"/>
+    <hyperlink ref="A94" r:id="rId127" display="https://github.com/whitescent/Mastify/pull/33"/>
+    <hyperlink ref="A7" r:id="rId128" display="https://github.com/kiwix/kiwix-android/pull/3823"/>
+    <hyperlink ref="A137" r:id="rId129" display="https://github.com/breezy-weather/breezy-weather/pull/713"/>
+    <hyperlink ref="A171" r:id="rId130" display="https://github.com/openMF/mobile-wallet/pull/1515"/>
+    <hyperlink ref="A18" r:id="rId131" display="https://github.com/wordpress-mobile/WordPress-Android/pull/7999"/>
+    <hyperlink ref="A162" r:id="rId132" display="https://github.com/ankidroid/Anki-Android/pull/15151"/>
+    <hyperlink ref="A146" r:id="rId133" display="https://github.com/microsoft/fluentui-android/pull/539"/>
+    <hyperlink ref="A4" r:id="rId134" display="https://github.com/wikimedia/apps-android-wikipedia/pull/573"/>
+    <hyperlink ref="A184" r:id="rId135" display="https://github.com/jkuester/unlauncher/pull/195"/>
+    <hyperlink ref="A115" r:id="rId136" display="https://github.com/osfans/trime/pull/1193"/>
+    <hyperlink ref="A187" r:id="rId137" display="https://github.com/mozilla-mobile/firefox-android/pull/3826"/>
+    <hyperlink ref="A60" r:id="rId138" display="https://github.com/SimpleMobileTools/Simple-Commons/pull/1787"/>
+    <hyperlink ref="A121" r:id="rId139" display="https://github.com/mozilla-mobile/firefox-android/pull/1868"/>
+    <hyperlink ref="A31" r:id="rId140" display="https://github.com/thunderbird/thunderbird-android/pull/7876"/>
+    <hyperlink ref="A57" r:id="rId141" display="https://github.com/thunderbird/thunderbird-android/pull/6723"/>
+    <hyperlink ref="A48" r:id="rId142" display="https://github.com/oppia/oppia-android/pull/5116"/>
+    <hyperlink ref="A120" r:id="rId143" display="https://github.com/thunderbird/thunderbird-android/pull/5865"/>
+    <hyperlink ref="A5" r:id="rId144" display="https://github.com/ismartcoding/plain-app/pull/82"/>
+    <hyperlink ref="A80" r:id="rId145" display="https://github.com/oppia/oppia-android/pull/5144"/>
+    <hyperlink ref="A194" r:id="rId146" display="https://github.com/dinbtechit/vscode-theme/pull/68"/>
+    <hyperlink ref="A191" r:id="rId147" display="https://github.com/openMF/android-client/pull/1957"/>
+    <hyperlink ref="A58" r:id="rId148" display="https://github.com/libre-tube/LibreTube/pull/4043"/>
+    <hyperlink ref="A175" r:id="rId149" display="https://github.com/wordpress-mobile/WordPress-Android/pull/18098"/>
+    <hyperlink ref="A147" r:id="rId150" display="https://github.com/openhab/openhab-android/pull/3227"/>
+    <hyperlink ref="A185" r:id="rId151" display="https://github.com/wordpress-mobile/WordPress-Android/pull/18145"/>
+    <hyperlink ref="A109" r:id="rId152" display="https://github.com/thunderbird/thunderbird-android/pull/3456"/>
+    <hyperlink ref="A150" r:id="rId153" display="https://github.com/woocommerce/woocommerce-android/pull/8844"/>
+    <hyperlink ref="A112" r:id="rId154" display="https://github.com/vitorpamplona/amethyst/pull/90"/>
+    <hyperlink ref="A95" r:id="rId155" display="https://github.com/wordpress-mobile/WordPress-Android/pull/17863"/>
+    <hyperlink ref="A101" r:id="rId156" display="https://github.com/wireapp/wire-android/pull/1777"/>
+    <hyperlink ref="A130" r:id="rId157" display="https://github.com/home-assistant/android/pull/2988"/>
+    <hyperlink ref="A73" r:id="rId158" display="https://github.com/wordpress-mobile/WordPress-Android/pull/16812"/>
+    <hyperlink ref="A33" r:id="rId159" display="https://github.com/TUM-Dev/Campus-Android/pull/1496"/>
+    <hyperlink ref="A142" r:id="rId160" display="https://github.com/ankidroid/Anki-Android/pull/12971"/>
+    <hyperlink ref="A85" r:id="rId161" display="https://github.com/home-assistant/android/pull/1994"/>
+    <hyperlink ref="A59" r:id="rId162" display="https://github.com/thunderbird/thunderbird-android/pull/6489"/>
+    <hyperlink ref="A143" r:id="rId163" display="https://github.com/iTaysonLab/jetisteam/pull/2"/>
+    <hyperlink ref="A83" r:id="rId164" display="https://github.com/home-assistant/android/pull/1043"/>
+    <hyperlink ref="A1" r:id="rId165" display="https://github.com/Automattic/pocket-casts-android/pull/432"/>
+    <hyperlink ref="A69" r:id="rId166" display="https://github.com/nightscout/AndroidAPS/pull/1847"/>
+    <hyperlink ref="A179" r:id="rId167" display="https://github.com/Automattic/pocket-casts-android/pull/215/files"/>
+    <hyperlink ref="A155" r:id="rId168" display="https://github.com/ankidroid/Anki-Android/pull/5417"/>
+    <hyperlink ref="A177" r:id="rId169" display="https://github.com/wordpress-mobile/WordPress-Android/pull/17286"/>
+    <hyperlink ref="A154" r:id="rId170" display="https://github.com/oppia/oppia-android/pull/4617"/>
+    <hyperlink ref="A98" r:id="rId171" display="https://github.com/oppia/oppia-android/pull/4616/files"/>
+    <hyperlink ref="A65" r:id="rId172" display="https://github.com/element-hq/element-android/pull/7015/files"/>
+    <hyperlink ref="A159" r:id="rId173" display="https://github.com/woocommerce/woocommerce-android/pull/7188/files"/>
+    <hyperlink ref="A149" r:id="rId174" display="https://github.com/Decathlon/vitamin-compose/pull/39"/>
     <hyperlink ref="A127" r:id="rId175" display="https://github.com/home-assistant/android/pull/749"/>
-    <hyperlink ref="A128" r:id="rId176" display="https://github.com/ankidroid/Anki-Android/pull/11659"/>
-    <hyperlink ref="A129" r:id="rId177" display="https://github.com/nightscout/AndroidAPS/pull/1907"/>
-    <hyperlink ref="A130" r:id="rId178" display="https://github.com/element-hq/element-android/pull/7436"/>
-    <hyperlink ref="A131" r:id="rId179" display="https://github.com/element-hq/element-android/pull/5456"/>
-    <hyperlink ref="A132" r:id="rId180" display="https://github.com/nightscout/AndroidAPS/pull/1705"/>
-    <hyperlink ref="A133" r:id="rId181" display="https://github.com/nightscout/AndroidAPS/pull/1740"/>
-    <hyperlink ref="A134" r:id="rId182" display="https://github.com/nightscout/AndroidAPS/pull/1525"/>
-    <hyperlink ref="A135" r:id="rId183" display="https://github.com/nightscout/AndroidAPS/pull/1559"/>
-    <hyperlink ref="A136" r:id="rId184" display="https://github.com/GetStream/stream-chat-android/pull/2716"/>
-    <hyperlink ref="A137" r:id="rId185" display="https://github.com/nightscout/AndroidAPS/pull/1503"/>
-    <hyperlink ref="A138" r:id="rId186" display="https://github.com/nightscout/AndroidAPS/pull/1412"/>
-    <hyperlink ref="A139" r:id="rId187" display="https://github.com/nightscout/AndroidAPS/pull/1607"/>
-    <hyperlink ref="A140" r:id="rId188" display="https://github.com/kirmanak/Mealient/pull/20"/>
-    <hyperlink ref="A141" r:id="rId189" display="https://github.com/nightscout/AndroidAPS/pull/1611"/>
-    <hyperlink ref="A142" r:id="rId190" display="https://github.com/shosetsuorg/shosetsu/pull/169"/>
-    <hyperlink ref="A143" r:id="rId191" display="https://github.com/rozPierog/Cofi/pull/21"/>
-    <hyperlink ref="A144" r:id="rId192" display="https://github.com/nightscout/AndroidAPS/pull/351"/>
-    <hyperlink ref="A145" r:id="rId193" display="https://github.com/kylecorry31/Trail-Sense/pull/947"/>
-    <hyperlink ref="A146" r:id="rId194" display="https://github.com/kylecorry31/Trail-Sense/pull/948"/>
-    <hyperlink ref="A147" r:id="rId195" display="https://github.com/kiwix/kiwix-android/pull/1975"/>
-    <hyperlink ref="A148" r:id="rId196" display="https://github.com/OneBusAway/onebusaway-android/pull/1178"/>
-    <hyperlink ref="A149" r:id="rId197" display="https://github.com/OneBusAway/onebusaway-android/pull/1117"/>
-    <hyperlink ref="A150" r:id="rId198" display="https://github.com/kiwix/kiwix-android/pull/1789"/>
-    <hyperlink ref="A151" r:id="rId199" display="https://github.com/woocommerce/woocommerce-android/pull/4678"/>
-    <hyperlink ref="A152" r:id="rId200" display="https://github.com/Sharingang/Sharingang-Android/pull/252"/>
-    <hyperlink ref="A153" r:id="rId201" display="https://github.com/droidconKE/droidconKeKotlin/pull/205"/>
+    <hyperlink ref="A77" r:id="rId176" display="https://github.com/ankidroid/Anki-Android/pull/11659"/>
+    <hyperlink ref="A111" r:id="rId177" display="https://github.com/nightscout/AndroidAPS/pull/1907"/>
+    <hyperlink ref="A181" r:id="rId178" display="https://github.com/element-hq/element-android/pull/7436"/>
+    <hyperlink ref="A86" r:id="rId179" display="https://github.com/element-hq/element-android/pull/5456"/>
+    <hyperlink ref="A53" r:id="rId180" display="https://github.com/nightscout/AndroidAPS/pull/1705"/>
+    <hyperlink ref="A123" r:id="rId181" display="https://github.com/nightscout/AndroidAPS/pull/1740"/>
+    <hyperlink ref="A16" r:id="rId182" display="https://github.com/nightscout/AndroidAPS/pull/1525"/>
+    <hyperlink ref="A38" r:id="rId183" display="https://github.com/nightscout/AndroidAPS/pull/1559"/>
+    <hyperlink ref="A35" r:id="rId184" display="https://github.com/GetStream/stream-chat-android/pull/2716"/>
+    <hyperlink ref="A9" r:id="rId185" display="https://github.com/nightscout/AndroidAPS/pull/1503"/>
+    <hyperlink ref="A75" r:id="rId186" display="https://github.com/nightscout/AndroidAPS/pull/1412"/>
+    <hyperlink ref="A79" r:id="rId187" display="https://github.com/nightscout/AndroidAPS/pull/1607"/>
+    <hyperlink ref="A22" r:id="rId188" display="https://github.com/kirmanak/Mealient/pull/20"/>
+    <hyperlink ref="A28" r:id="rId189" display="https://github.com/nightscout/AndroidAPS/pull/1611"/>
+    <hyperlink ref="A106" r:id="rId190" display="https://github.com/shosetsuorg/shosetsu/pull/169"/>
+    <hyperlink ref="A61" r:id="rId191" display="https://github.com/rozPierog/Cofi/pull/21"/>
+    <hyperlink ref="A131" r:id="rId192" display="https://github.com/nightscout/AndroidAPS/pull/351"/>
+    <hyperlink ref="A148" r:id="rId193" display="https://github.com/kylecorry31/Trail-Sense/pull/947"/>
+    <hyperlink ref="A197" r:id="rId194" display="https://github.com/kylecorry31/Trail-Sense/pull/948"/>
+    <hyperlink ref="A192" r:id="rId195" display="https://github.com/kiwix/kiwix-android/pull/1975"/>
+    <hyperlink ref="A62" r:id="rId196" display="https://github.com/OneBusAway/onebusaway-android/pull/1178"/>
+    <hyperlink ref="A29" r:id="rId197" display="https://github.com/OneBusAway/onebusaway-android/pull/1117"/>
+    <hyperlink ref="A102" r:id="rId198" display="https://github.com/kiwix/kiwix-android/pull/1789"/>
+    <hyperlink ref="A136" r:id="rId199" display="https://github.com/woocommerce/woocommerce-android/pull/4678"/>
+    <hyperlink ref="A56" r:id="rId200" display="https://github.com/Sharingang/Sharingang-Android/pull/252"/>
+    <hyperlink ref="A128" r:id="rId201" display="https://github.com/droidconKE/droidconKeKotlin/pull/205"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
